--- a/uploads/invoice-product-missing.xlsx
+++ b/uploads/invoice-product-missing.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251031\eksport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251114\Eksport\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Invoice Product" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="342">
   <si>
     <t>nomor_invoice</t>
   </si>
@@ -63,7 +63,655 @@
     <t>ex: 2025/08/01</t>
   </si>
   <si>
-    <t>05ASB25010683</t>
+    <t>07ASB24028161</t>
+  </si>
+  <si>
+    <t>013008</t>
+  </si>
+  <si>
+    <t>NUTRISALIN 200 GR</t>
+  </si>
+  <si>
+    <t>290708</t>
+  </si>
+  <si>
+    <t>013010</t>
+  </si>
+  <si>
+    <t>NUTRIGARAM 300 GR</t>
+  </si>
+  <si>
+    <t>290613</t>
+  </si>
+  <si>
+    <t>290714</t>
+  </si>
+  <si>
+    <t>290609</t>
+  </si>
+  <si>
+    <t>07ASB25034549</t>
+  </si>
+  <si>
+    <t>012963</t>
+  </si>
+  <si>
+    <t>RUPAFIN</t>
+  </si>
+  <si>
+    <t>A001</t>
+  </si>
+  <si>
+    <t>017544</t>
+  </si>
+  <si>
+    <t>SEROQUEL 25 MG</t>
+  </si>
+  <si>
+    <t>60049359</t>
+  </si>
+  <si>
+    <t>000999</t>
+  </si>
+  <si>
+    <t>PHENYTOIN 100 CAP.</t>
+  </si>
+  <si>
+    <t>J25010D</t>
+  </si>
+  <si>
+    <t>000689</t>
+  </si>
+  <si>
+    <t>LACTULAX SYRUP 120</t>
+  </si>
+  <si>
+    <t>E25004A</t>
+  </si>
+  <si>
+    <t>003482</t>
+  </si>
+  <si>
+    <t>BACTODERM CREAM</t>
+  </si>
+  <si>
+    <t>G25016G</t>
+  </si>
+  <si>
+    <t>07ASB25034824</t>
+  </si>
+  <si>
+    <t>000112</t>
+  </si>
+  <si>
+    <t>BACTODERM OINTMENT</t>
+  </si>
+  <si>
+    <t>A25011G</t>
+  </si>
+  <si>
+    <t>015167</t>
+  </si>
+  <si>
+    <t>HP PRO PLUS.</t>
+  </si>
+  <si>
+    <t>07213111</t>
+  </si>
+  <si>
+    <t>004849</t>
+  </si>
+  <si>
+    <t>FERRIZ DROPS 15 ML</t>
+  </si>
+  <si>
+    <t>5G 1089</t>
+  </si>
+  <si>
+    <t>07ASB25034950</t>
+  </si>
+  <si>
+    <t>000629</t>
+  </si>
+  <si>
+    <t>INPEPSA SUSPENSI</t>
+  </si>
+  <si>
+    <t>1EG203</t>
+  </si>
+  <si>
+    <t>07ASB25034968</t>
+  </si>
+  <si>
+    <t>015026</t>
+  </si>
+  <si>
+    <t>PEINLOS 400</t>
+  </si>
+  <si>
+    <t>3EF089</t>
+  </si>
+  <si>
+    <t>07ASB25035316</t>
+  </si>
+  <si>
+    <t>015442</t>
+  </si>
+  <si>
+    <t>NEO HP PRO.</t>
+  </si>
+  <si>
+    <t>08343311</t>
+  </si>
+  <si>
+    <t>013660</t>
+  </si>
+  <si>
+    <t>DUOXAL</t>
+  </si>
+  <si>
+    <t>X624</t>
+  </si>
+  <si>
+    <t>07ASB25035953</t>
+  </si>
+  <si>
+    <t>010042</t>
+  </si>
+  <si>
+    <t>LIP ICE C ROSSY KISS</t>
+  </si>
+  <si>
+    <t>OKCR004</t>
+  </si>
+  <si>
+    <t>015406</t>
+  </si>
+  <si>
+    <t>HL SHIROJYUN STARTER PACK 20GR</t>
+  </si>
+  <si>
+    <t>PHJZ008</t>
+  </si>
+  <si>
+    <t>015392</t>
+  </si>
+  <si>
+    <t>HL GOKUJYUN ULT MOIST FW 100GR</t>
+  </si>
+  <si>
+    <t>PITJ201</t>
+  </si>
+  <si>
+    <t>12ASB25021890</t>
+  </si>
+  <si>
+    <t>016476</t>
+  </si>
+  <si>
+    <t>GLICLAZIDE MR</t>
+  </si>
+  <si>
+    <t>1EG159</t>
+  </si>
+  <si>
+    <t>12ASB25022059</t>
+  </si>
+  <si>
+    <t>003430</t>
+  </si>
+  <si>
+    <t>AMITRIPTILINE 25 MG</t>
+  </si>
+  <si>
+    <t>A 12503 FC1</t>
+  </si>
+  <si>
+    <t>12ASB25022087</t>
+  </si>
+  <si>
+    <t>001196</t>
+  </si>
+  <si>
+    <t>SIMARC - 2</t>
+  </si>
+  <si>
+    <t>1EB196</t>
+  </si>
+  <si>
+    <t>015563</t>
+  </si>
+  <si>
+    <t>WARFARIN SODIUM CLATHRATE</t>
+  </si>
+  <si>
+    <t>1EG173</t>
+  </si>
+  <si>
+    <t>12ASB25022431</t>
+  </si>
+  <si>
+    <t>5G 1096</t>
+  </si>
+  <si>
+    <t>004848</t>
+  </si>
+  <si>
+    <t>FERRIZ SIRUP 100 ML</t>
+  </si>
+  <si>
+    <t>5K 1213</t>
+  </si>
+  <si>
+    <t>008664</t>
+  </si>
+  <si>
+    <t>CALLUSOL</t>
+  </si>
+  <si>
+    <t>1EE150</t>
+  </si>
+  <si>
+    <t>011957</t>
+  </si>
+  <si>
+    <t>POLYCROL FORTE SUSP -BTL 100 ML</t>
+  </si>
+  <si>
+    <t>5G 1079</t>
+  </si>
+  <si>
+    <t>12ASB25022464</t>
+  </si>
+  <si>
+    <t>000654</t>
+  </si>
+  <si>
+    <t>ISOTIC ADRETOR 0,50 %</t>
+  </si>
+  <si>
+    <t>2EG027</t>
+  </si>
+  <si>
+    <t>012123</t>
+  </si>
+  <si>
+    <t>LAKTULOSA GENERIK 60ML</t>
+  </si>
+  <si>
+    <t>H25014A</t>
+  </si>
+  <si>
+    <t>001013</t>
+  </si>
+  <si>
+    <t>POLYCROL SUSPENSI - BTL 100 ML</t>
+  </si>
+  <si>
+    <t>5H 1135</t>
+  </si>
+  <si>
+    <t>13ASB25016823</t>
+  </si>
+  <si>
+    <t>014962</t>
+  </si>
+  <si>
+    <t>Y - RINS 10 X 12 ML ( MO )</t>
+  </si>
+  <si>
+    <t>2RJ114</t>
+  </si>
+  <si>
+    <t>18BSB25000214</t>
+  </si>
+  <si>
+    <t>017655</t>
+  </si>
+  <si>
+    <t>ACEMED REUSABLE BIPOLAR FORCEPS 200MM, TIP SIZE 0,</t>
+  </si>
+  <si>
+    <t>NZ20241234</t>
+  </si>
+  <si>
+    <t>25ASB24015854</t>
+  </si>
+  <si>
+    <t>290806</t>
+  </si>
+  <si>
+    <t>25ASB25014626</t>
+  </si>
+  <si>
+    <t>013009</t>
+  </si>
+  <si>
+    <t>NUTRISALIN 400 GR</t>
+  </si>
+  <si>
+    <t>300716</t>
+  </si>
+  <si>
+    <t>25ASB25016769</t>
+  </si>
+  <si>
+    <t>000652</t>
+  </si>
+  <si>
+    <t>ISOSORBIDE DINITRATE 5 MG</t>
+  </si>
+  <si>
+    <t>A 02380 GC</t>
+  </si>
+  <si>
+    <t>25ASB25017546</t>
+  </si>
+  <si>
+    <t>016627</t>
+  </si>
+  <si>
+    <t>TRAMADOL 50 MG ( GF )</t>
+  </si>
+  <si>
+    <t>B5I317</t>
+  </si>
+  <si>
+    <t>25ASB25017826</t>
+  </si>
+  <si>
+    <t>017181</t>
+  </si>
+  <si>
+    <t>EYEBOST 160 GRAM</t>
+  </si>
+  <si>
+    <t>EY0825083</t>
+  </si>
+  <si>
+    <t>H25006A</t>
+  </si>
+  <si>
+    <t>000596</t>
+  </si>
+  <si>
+    <t>IKADRYL SYR. 100 ML</t>
+  </si>
+  <si>
+    <t>F25008A</t>
+  </si>
+  <si>
+    <t>J25005A</t>
+  </si>
+  <si>
+    <t>25ASB25017911</t>
+  </si>
+  <si>
+    <t>000032</t>
+  </si>
+  <si>
+    <t>ALPARA KAPLET</t>
+  </si>
+  <si>
+    <t>A06HS218</t>
+  </si>
+  <si>
+    <t>25ASB25017920</t>
+  </si>
+  <si>
+    <t>25ASB25017934</t>
+  </si>
+  <si>
+    <t>011472</t>
+  </si>
+  <si>
+    <t>FIXACEP ORAL DROPS</t>
+  </si>
+  <si>
+    <t>8EG001 2</t>
+  </si>
+  <si>
+    <t>014714</t>
+  </si>
+  <si>
+    <t>PROFERRO</t>
+  </si>
+  <si>
+    <t>1EG099</t>
+  </si>
+  <si>
+    <t>25ASB25017970</t>
+  </si>
+  <si>
+    <t>000449</t>
+  </si>
+  <si>
+    <t>FARBION-5000 INJEKSI</t>
+  </si>
+  <si>
+    <t>3EB075</t>
+  </si>
+  <si>
+    <t>000578</t>
+  </si>
+  <si>
+    <t>IBUPROFEN 400 MG</t>
+  </si>
+  <si>
+    <t>A 02225 IC</t>
+  </si>
+  <si>
+    <t>A 02392 HC</t>
+  </si>
+  <si>
+    <t>006978</t>
+  </si>
+  <si>
+    <t>SALBUTAMOL 4 MG</t>
+  </si>
+  <si>
+    <t>A 08362 JC</t>
+  </si>
+  <si>
+    <t>012139</t>
+  </si>
+  <si>
+    <t>TRACETATE SUSPENSI ORAL</t>
+  </si>
+  <si>
+    <t>1EF041T</t>
+  </si>
+  <si>
+    <t>25ASB25017971</t>
+  </si>
+  <si>
+    <t>014441</t>
+  </si>
+  <si>
+    <t>INVICLOT ( 5 VIAL )</t>
+  </si>
+  <si>
+    <t>3EE094</t>
+  </si>
+  <si>
+    <t>25ASB25017994</t>
+  </si>
+  <si>
+    <t>012704</t>
+  </si>
+  <si>
+    <t>FARMADOL INFUS 50 ML</t>
+  </si>
+  <si>
+    <t>3EG102</t>
+  </si>
+  <si>
+    <t>25ASB25017995</t>
+  </si>
+  <si>
+    <t>000513</t>
+  </si>
+  <si>
+    <t>FUROSEMIDE 40 MG</t>
+  </si>
+  <si>
+    <t>A 00496 IC</t>
+  </si>
+  <si>
+    <t>25ASB25017996</t>
+  </si>
+  <si>
+    <t>004416</t>
+  </si>
+  <si>
+    <t>SALBUTAMOL 2 MG</t>
+  </si>
+  <si>
+    <t>A 08238 HC</t>
+  </si>
+  <si>
+    <t>013640</t>
+  </si>
+  <si>
+    <t>UMARONE</t>
+  </si>
+  <si>
+    <t>3EE130</t>
+  </si>
+  <si>
+    <t>25ASB25018023</t>
+  </si>
+  <si>
+    <t>010198</t>
+  </si>
+  <si>
+    <t>BACTODERM CREAM 10 MG</t>
+  </si>
+  <si>
+    <t>G25014G</t>
+  </si>
+  <si>
+    <t>C25014G</t>
+  </si>
+  <si>
+    <t>25ASB25018077</t>
+  </si>
+  <si>
+    <t>001130</t>
+  </si>
+  <si>
+    <t>RENAQUIL TABLET</t>
+  </si>
+  <si>
+    <t>1EF033</t>
+  </si>
+  <si>
+    <t>25ASB25018110</t>
+  </si>
+  <si>
+    <t>000363</t>
+  </si>
+  <si>
+    <t>ERYTHROMYCIN 500 MG</t>
+  </si>
+  <si>
+    <t>B 02529 IC</t>
+  </si>
+  <si>
+    <t>25ASB25018190</t>
+  </si>
+  <si>
+    <t>25ASB25018235</t>
+  </si>
+  <si>
+    <t>015193</t>
+  </si>
+  <si>
+    <t>SERTRALINE</t>
+  </si>
+  <si>
+    <t>1EH161</t>
+  </si>
+  <si>
+    <t>25ASB25018247</t>
+  </si>
+  <si>
+    <t>3EG140</t>
+  </si>
+  <si>
+    <t>25ASB25018254</t>
+  </si>
+  <si>
+    <t>000026</t>
+  </si>
+  <si>
+    <t>ALKOHOL 70%</t>
+  </si>
+  <si>
+    <t>J25001P</t>
+  </si>
+  <si>
+    <t>25BSB25001513</t>
+  </si>
+  <si>
+    <t>010325</t>
+  </si>
+  <si>
+    <t>TS50 SCRUBBRUSH W/CG4%&amp;SOAP</t>
+  </si>
+  <si>
+    <t>250824</t>
+  </si>
+  <si>
+    <t>26ASB24021414</t>
+  </si>
+  <si>
+    <t>290805</t>
+  </si>
+  <si>
+    <t>26ASB24022295</t>
+  </si>
+  <si>
+    <t>290610</t>
+  </si>
+  <si>
+    <t>290910</t>
+  </si>
+  <si>
+    <t>26ASB25020250</t>
+  </si>
+  <si>
+    <t>2ED043</t>
+  </si>
+  <si>
+    <t>26ASB25020251</t>
+  </si>
+  <si>
+    <t>014283</t>
+  </si>
+  <si>
+    <t>Y - RINS 2X12 ML ( MO )</t>
+  </si>
+  <si>
+    <t>2EC061</t>
+  </si>
+  <si>
+    <t>26ASB25021228</t>
+  </si>
+  <si>
+    <t>27ASB25014375</t>
+  </si>
+  <si>
+    <t>2ED090</t>
+  </si>
+  <si>
+    <t>27ASB25015642</t>
+  </si>
+  <si>
+    <t>300709</t>
+  </si>
+  <si>
+    <t>27ASB25017192</t>
   </si>
   <si>
     <t>016806</t>
@@ -72,331 +720,199 @@
     <t>ETAWALIN 200 GR</t>
   </si>
   <si>
-    <t>P110725051</t>
-  </si>
-  <si>
-    <t>05ASB25011052</t>
-  </si>
-  <si>
-    <t>000839</t>
-  </si>
-  <si>
-    <t>NEO-MERCAZOLE TABLET</t>
-  </si>
-  <si>
-    <t>5H 1106</t>
-  </si>
-  <si>
-    <t>001360</t>
-  </si>
-  <si>
-    <t>VITAMIN B1 INJEKSI 10 ML, 10`S A19024</t>
-  </si>
-  <si>
-    <t>0350525001</t>
-  </si>
-  <si>
-    <t>07ASB24028161</t>
-  </si>
-  <si>
-    <t>013008</t>
-  </si>
-  <si>
-    <t>NUTRISALIN 200 GR</t>
-  </si>
-  <si>
-    <t>290708</t>
-  </si>
-  <si>
-    <t>013010</t>
-  </si>
-  <si>
-    <t>NUTRIGARAM 300 GR</t>
-  </si>
-  <si>
-    <t>290613</t>
-  </si>
-  <si>
-    <t>290714</t>
-  </si>
-  <si>
-    <t>290609</t>
-  </si>
-  <si>
-    <t>07ASB25034438</t>
-  </si>
-  <si>
-    <t>014283</t>
-  </si>
-  <si>
-    <t>Y - RINS 2X12 ML ( MO )</t>
-  </si>
-  <si>
-    <t>2EF095</t>
-  </si>
-  <si>
-    <t>11ASB25030322</t>
-  </si>
-  <si>
-    <t>016837</t>
-  </si>
-  <si>
-    <t>ETAWALIN 200 GR ( CS )</t>
-  </si>
-  <si>
-    <t>P110825080</t>
-  </si>
-  <si>
-    <t>11ASB25030323</t>
-  </si>
-  <si>
-    <t>017016</t>
-  </si>
-  <si>
-    <t>ETAWAKU PLATINUM 200 GR (CS)</t>
-  </si>
-  <si>
-    <t>110925003A</t>
-  </si>
-  <si>
-    <t>016838</t>
-  </si>
-  <si>
-    <t>FRESHMAG 200 ML ( CS )</t>
-  </si>
-  <si>
-    <t>L210725010</t>
-  </si>
-  <si>
-    <t>016840</t>
-  </si>
-  <si>
-    <t>ZYMUNO 200 ML ( CS )</t>
-  </si>
-  <si>
-    <t>L110925044</t>
-  </si>
-  <si>
-    <t>11ASB25030324</t>
-  </si>
-  <si>
-    <t>11ASB25030325</t>
-  </si>
-  <si>
-    <t>L210825005</t>
-  </si>
-  <si>
-    <t>12ASB25021305</t>
-  </si>
-  <si>
-    <t>P110925120</t>
-  </si>
-  <si>
-    <t>004848</t>
-  </si>
-  <si>
-    <t>FERRIZ SIRUP 100 ML</t>
-  </si>
-  <si>
-    <t>5H 1119</t>
-  </si>
-  <si>
-    <t>010342</t>
-  </si>
-  <si>
-    <t>OSTEOCAL.</t>
-  </si>
-  <si>
-    <t>5J 1172</t>
-  </si>
-  <si>
-    <t>12ASB25021365</t>
-  </si>
-  <si>
-    <t>000999</t>
-  </si>
-  <si>
-    <t>PHENYTOIN 100 CAP.</t>
-  </si>
-  <si>
-    <t>J25010D</t>
-  </si>
-  <si>
-    <t>25ASB25016530</t>
-  </si>
-  <si>
-    <t>000032</t>
-  </si>
-  <si>
-    <t>ALPARA KAPLET</t>
-  </si>
-  <si>
-    <t>A06HG200</t>
-  </si>
-  <si>
-    <t>25ASB25017063</t>
+    <t>P110925025</t>
+  </si>
+  <si>
+    <t>27ASB25019812</t>
+  </si>
+  <si>
+    <t>014961</t>
+  </si>
+  <si>
+    <t>CALLUSOL ( MO )</t>
+  </si>
+  <si>
+    <t>1EF116</t>
+  </si>
+  <si>
+    <t>27ASB25019936</t>
+  </si>
+  <si>
+    <t>015618</t>
+  </si>
+  <si>
+    <t>CALITOZ</t>
+  </si>
+  <si>
+    <t>1EI086</t>
+  </si>
+  <si>
+    <t>27ASB25019937</t>
+  </si>
+  <si>
+    <t>1EF042T 2</t>
+  </si>
+  <si>
+    <t>27ASB25019949</t>
+  </si>
+  <si>
+    <t>3EG119</t>
+  </si>
+  <si>
+    <t>27ASB25019950</t>
+  </si>
+  <si>
+    <t>3EG138</t>
+  </si>
+  <si>
+    <t>27ASB25019951</t>
+  </si>
+  <si>
+    <t>3EG031</t>
+  </si>
+  <si>
+    <t>27ASB25019952</t>
+  </si>
+  <si>
+    <t>1EG097</t>
+  </si>
+  <si>
+    <t>27ASB25019953</t>
+  </si>
+  <si>
+    <t>013783</t>
+  </si>
+  <si>
+    <t>CALGAE</t>
+  </si>
+  <si>
+    <t>1EH001</t>
+  </si>
+  <si>
+    <t>004908</t>
+  </si>
+  <si>
+    <t>OBH IKA 200 ML</t>
+  </si>
+  <si>
+    <t>J25010A</t>
+  </si>
+  <si>
+    <t>27ASB25019954</t>
+  </si>
+  <si>
+    <t>27ASB25019955</t>
+  </si>
+  <si>
+    <t>27ASB25020020</t>
+  </si>
+  <si>
+    <t>27ASB25020038</t>
+  </si>
+  <si>
+    <t>016865</t>
+  </si>
+  <si>
+    <t>CLONASOL CREAM</t>
+  </si>
+  <si>
+    <t>4AR01</t>
+  </si>
+  <si>
+    <t>000305</t>
+  </si>
+  <si>
+    <t>DERMASOLON OINT.</t>
+  </si>
+  <si>
+    <t>J24011G</t>
+  </si>
+  <si>
+    <t>000517</t>
+  </si>
+  <si>
+    <t>GENTASOLON CREAM 5</t>
+  </si>
+  <si>
+    <t>G25009G</t>
+  </si>
+  <si>
+    <t>016884</t>
+  </si>
+  <si>
+    <t>NORTA BB SOOTH DIAPER RASH CREAM</t>
+  </si>
+  <si>
+    <t>4AO01</t>
+  </si>
+  <si>
+    <t>016879</t>
+  </si>
+  <si>
+    <t>NORTA DAY ADV MOIST LOTION</t>
+  </si>
+  <si>
+    <t>5AI01</t>
+  </si>
+  <si>
+    <t>016880</t>
+  </si>
+  <si>
+    <t>NORTA DAY MOIST RICH BODY WASH</t>
+  </si>
+  <si>
+    <t>4AL02</t>
+  </si>
+  <si>
+    <t>27ASB25020081</t>
+  </si>
+  <si>
+    <t>2ED091</t>
   </si>
   <si>
     <t>2EF039</t>
   </si>
   <si>
-    <t>25ASB25017112</t>
-  </si>
-  <si>
-    <t>015442</t>
-  </si>
-  <si>
-    <t>NEO HP PRO.</t>
-  </si>
-  <si>
-    <t>08413011</t>
-  </si>
-  <si>
-    <t>25ASB25017124</t>
-  </si>
-  <si>
-    <t>011472</t>
-  </si>
-  <si>
-    <t>FIXACEP ORAL DROPS</t>
-  </si>
-  <si>
-    <t>8EG001 1</t>
-  </si>
-  <si>
-    <t>014441</t>
-  </si>
-  <si>
-    <t>INVICLOT ( 5 VIAL )</t>
-  </si>
-  <si>
-    <t>3EE094</t>
-  </si>
-  <si>
-    <t>25ASB25017125</t>
-  </si>
-  <si>
-    <t>000513</t>
-  </si>
-  <si>
-    <t>FUROSEMIDE 40 MG</t>
-  </si>
-  <si>
-    <t>A 00490 HC</t>
-  </si>
-  <si>
-    <t>004908</t>
-  </si>
-  <si>
-    <t>OBH IKA 200 ML</t>
-  </si>
-  <si>
-    <t>J25002A</t>
-  </si>
-  <si>
-    <t>014714</t>
-  </si>
-  <si>
-    <t>PROFERRO</t>
-  </si>
-  <si>
-    <t>1EG097</t>
-  </si>
-  <si>
-    <t>013640</t>
-  </si>
-  <si>
-    <t>UMARONE</t>
-  </si>
-  <si>
-    <t>3EE130</t>
-  </si>
-  <si>
-    <t>25ASB25017150</t>
-  </si>
-  <si>
-    <t>015618</t>
-  </si>
-  <si>
-    <t>CALITOZ</t>
-  </si>
-  <si>
-    <t>1EH087</t>
-  </si>
-  <si>
-    <t>25ASB25017193</t>
-  </si>
-  <si>
-    <t>012704</t>
-  </si>
-  <si>
-    <t>FARMADOL INFUS 50 ML</t>
-  </si>
-  <si>
-    <t>3EG102</t>
-  </si>
-  <si>
-    <t>25ASB25017210</t>
-  </si>
-  <si>
-    <t>015495</t>
-  </si>
-  <si>
-    <t>ROSUVASTATIN 10 MG</t>
-  </si>
-  <si>
-    <t>1EB063</t>
-  </si>
-  <si>
-    <t>015496</t>
-  </si>
-  <si>
-    <t>ROSUVASTATIN 20 MG</t>
-  </si>
-  <si>
-    <t>1ED184</t>
-  </si>
-  <si>
-    <t>1ED186</t>
-  </si>
-  <si>
-    <t>25ASB25017214</t>
-  </si>
-  <si>
-    <t>015026</t>
-  </si>
-  <si>
-    <t>PEINLOS 400</t>
-  </si>
-  <si>
-    <t>3EG031</t>
-  </si>
-  <si>
-    <t>25ASB25017237</t>
-  </si>
-  <si>
-    <t>P110925023</t>
-  </si>
-  <si>
-    <t>017290</t>
-  </si>
-  <si>
-    <t>ETAWALIN DELICATE 200 GR</t>
-  </si>
-  <si>
-    <t>P310925001</t>
-  </si>
-  <si>
-    <t>25ASB25017318</t>
-  </si>
-  <si>
-    <t>016768</t>
-  </si>
-  <si>
-    <t>AMIODARONE INJEKSI</t>
-  </si>
-  <si>
-    <t>3EF104</t>
+    <t>27ASB25020087</t>
+  </si>
+  <si>
+    <t>27ASB25020089</t>
+  </si>
+  <si>
+    <t>27ASB25020092</t>
+  </si>
+  <si>
+    <t>P111025112</t>
+  </si>
+  <si>
+    <t>27ASB25020095</t>
+  </si>
+  <si>
+    <t>300815</t>
+  </si>
+  <si>
+    <t>27ASB25020128</t>
+  </si>
+  <si>
+    <t>27ASB25020129</t>
+  </si>
+  <si>
+    <t>27ASB25020143</t>
+  </si>
+  <si>
+    <t>300804</t>
+  </si>
+  <si>
+    <t>300906</t>
+  </si>
+  <si>
+    <t>27ASB25020179</t>
+  </si>
+  <si>
+    <t>27ASB25020216</t>
+  </si>
+  <si>
+    <t>27ASB25020217</t>
   </si>
   <si>
     <t>009216</t>
@@ -405,448 +921,130 @@
     <t>FARMADOL INFUS</t>
   </si>
   <si>
-    <t>3EG086</t>
-  </si>
-  <si>
-    <t>25ASB25017319</t>
-  </si>
-  <si>
-    <t>000319</t>
-  </si>
-  <si>
-    <t>DIGOXIN 0.25 MG</t>
-  </si>
-  <si>
-    <t>A 08614 HC</t>
-  </si>
-  <si>
-    <t>000363</t>
-  </si>
-  <si>
-    <t>ERYTHROMYCIN 500 MG</t>
-  </si>
-  <si>
-    <t>B 02529 IC</t>
-  </si>
-  <si>
-    <t>000449</t>
-  </si>
-  <si>
-    <t>FARBION-5000 INJEKSI</t>
-  </si>
-  <si>
-    <t>3EB075</t>
-  </si>
-  <si>
-    <t>012903</t>
-  </si>
-  <si>
-    <t>FARPRESIN</t>
-  </si>
-  <si>
-    <t>3EC043</t>
-  </si>
-  <si>
-    <t>A 00496 IC</t>
-  </si>
-  <si>
-    <t>016476</t>
-  </si>
-  <si>
-    <t>GLICLAZIDE MR</t>
-  </si>
-  <si>
-    <t>1EH063</t>
-  </si>
-  <si>
-    <t>015155</t>
-  </si>
-  <si>
-    <t>ISOSORBIDE DINITRATE INJ</t>
-  </si>
-  <si>
-    <t>3EF146</t>
-  </si>
-  <si>
-    <t>000652</t>
-  </si>
-  <si>
-    <t>ISOSORBIDE DINITRATE 5 MG</t>
-  </si>
-  <si>
-    <t>A 02392 HC</t>
-  </si>
-  <si>
-    <t>H25010D</t>
-  </si>
-  <si>
-    <t>006978</t>
-  </si>
-  <si>
-    <t>SALBUTAMOL 4 MG</t>
-  </si>
-  <si>
-    <t>A 08358 IC</t>
-  </si>
-  <si>
-    <t>25ASB25017320</t>
-  </si>
-  <si>
-    <t>25ASB25017326</t>
-  </si>
-  <si>
-    <t>300803</t>
-  </si>
-  <si>
-    <t>25ASB25017341</t>
-  </si>
-  <si>
-    <t>003430</t>
-  </si>
-  <si>
-    <t>AMITRIPTILINE 25 MG</t>
-  </si>
-  <si>
-    <t>A 12509 GC</t>
-  </si>
-  <si>
-    <t>25ASB25017342</t>
-  </si>
-  <si>
-    <t>8EG001 2</t>
-  </si>
-  <si>
-    <t>017431</t>
-  </si>
-  <si>
-    <t>IBUPROFEN 200</t>
-  </si>
-  <si>
-    <t>A 08502 JB</t>
-  </si>
-  <si>
-    <t>25ASB25017343</t>
-  </si>
-  <si>
-    <t>25ASB25017344</t>
-  </si>
-  <si>
-    <t>016650</t>
-  </si>
-  <si>
-    <t>COLCHICINE</t>
-  </si>
-  <si>
-    <t>1EF122</t>
-  </si>
-  <si>
-    <t>25ASB25017358</t>
-  </si>
-  <si>
-    <t>25ASB25017359</t>
-  </si>
-  <si>
-    <t>010441</t>
-  </si>
-  <si>
-    <t>MONECTO 20 - TAB</t>
-  </si>
-  <si>
-    <t>1EC094</t>
-  </si>
-  <si>
-    <t>25ASB25017396</t>
-  </si>
-  <si>
-    <t>25ASB25017439</t>
-  </si>
-  <si>
-    <t>014962</t>
-  </si>
-  <si>
-    <t>Y - RINS 10 X 12 ML ( MO )</t>
+    <t>3EG123</t>
+  </si>
+  <si>
+    <t>27ASB25020218</t>
+  </si>
+  <si>
+    <t>27ASB25020219</t>
+  </si>
+  <si>
+    <t>27ASB25020220</t>
+  </si>
+  <si>
+    <t>27ASB25020221</t>
+  </si>
+  <si>
+    <t>J25011D</t>
+  </si>
+  <si>
+    <t>27ASB25020222</t>
+  </si>
+  <si>
+    <t>27ASB25020253</t>
+  </si>
+  <si>
+    <t>015564</t>
+  </si>
+  <si>
+    <t>OSELTAMIVIR 75 MG 10`S</t>
+  </si>
+  <si>
+    <t>25OV2001</t>
+  </si>
+  <si>
+    <t>27ASB25020265</t>
+  </si>
+  <si>
+    <t>012671</t>
+  </si>
+  <si>
+    <t>LUPRED TABLET</t>
+  </si>
+  <si>
+    <t>1EF169</t>
+  </si>
+  <si>
+    <t>27ASB25020284</t>
+  </si>
+  <si>
+    <t>27ASB25020285</t>
+  </si>
+  <si>
+    <t>27ASB25020299</t>
+  </si>
+  <si>
+    <t>300626</t>
+  </si>
+  <si>
+    <t>27ASB25020314</t>
+  </si>
+  <si>
+    <t>27ASB25020316</t>
   </si>
   <si>
     <t>2ED082</t>
   </si>
   <si>
-    <t>2EE043</t>
-  </si>
-  <si>
-    <t>25ASB25017488</t>
-  </si>
-  <si>
-    <t>25ASB25017489</t>
-  </si>
-  <si>
-    <t>004416</t>
-  </si>
-  <si>
-    <t>SALBUTAMOL 2 MG</t>
-  </si>
-  <si>
-    <t>A 08240 HC</t>
-  </si>
-  <si>
-    <t>25ASB25017490</t>
-  </si>
-  <si>
-    <t>015193</t>
-  </si>
-  <si>
-    <t>SERTRALINE</t>
-  </si>
-  <si>
-    <t>1EH160</t>
-  </si>
-  <si>
-    <t>015563</t>
-  </si>
-  <si>
-    <t>WARFARIN SODIUM CLATHRATE</t>
-  </si>
-  <si>
-    <t>1EG171</t>
-  </si>
-  <si>
-    <t>1EH192</t>
-  </si>
-  <si>
-    <t>1EH161</t>
-  </si>
-  <si>
-    <t>25ASB25017491</t>
-  </si>
-  <si>
-    <t>25ASB25017588</t>
-  </si>
-  <si>
-    <t>A 12503 FC1</t>
-  </si>
-  <si>
-    <t>25BSB25001468</t>
-  </si>
-  <si>
-    <t>010325</t>
-  </si>
-  <si>
-    <t>TS50 SCRUBBRUSH W/CG4%&amp;SOAP</t>
-  </si>
-  <si>
-    <t>250824</t>
-  </si>
-  <si>
-    <t>27ASB25018473</t>
-  </si>
-  <si>
-    <t>3EE030</t>
-  </si>
-  <si>
-    <t>27ASB25018758</t>
-  </si>
-  <si>
-    <t>3EC102</t>
-  </si>
-  <si>
-    <t>016824</t>
-  </si>
-  <si>
-    <t>FARTISON TABLET</t>
-  </si>
-  <si>
-    <t>1EG122</t>
-  </si>
-  <si>
-    <t>27ASB25018759</t>
-  </si>
-  <si>
-    <t>3EG052</t>
-  </si>
-  <si>
-    <t>27ASB25018760</t>
-  </si>
-  <si>
-    <t>3EF086</t>
-  </si>
-  <si>
-    <t>27ASB25018761</t>
-  </si>
-  <si>
-    <t>27ASB25018763</t>
-  </si>
-  <si>
-    <t>27ASB25018764</t>
-  </si>
-  <si>
-    <t>27ASB25018765</t>
-  </si>
-  <si>
-    <t>014680</t>
-  </si>
-  <si>
-    <t>INDOP 200 INJ ( 5 VIAL )</t>
-  </si>
-  <si>
-    <t>3EB026</t>
-  </si>
-  <si>
-    <t>27ASB25018767</t>
-  </si>
-  <si>
-    <t>27ASB25018901</t>
-  </si>
-  <si>
-    <t>27ASB25018912</t>
-  </si>
-  <si>
-    <t>2ED091</t>
-  </si>
-  <si>
-    <t>27ASB25018981</t>
-  </si>
-  <si>
-    <t>004228</t>
-  </si>
-  <si>
-    <t>IRBOSYD FILM COATED TABLET</t>
-  </si>
-  <si>
-    <t>1EA030</t>
-  </si>
-  <si>
-    <t>27ASB25018982</t>
-  </si>
-  <si>
-    <t>27ASB25018983</t>
-  </si>
-  <si>
-    <t>27ASB25018984</t>
-  </si>
-  <si>
-    <t>27ASB25018985</t>
-  </si>
-  <si>
-    <t>012739</t>
-  </si>
-  <si>
-    <t>XOLMETRAS 350 ( 50ML )</t>
-  </si>
-  <si>
-    <t>3EF056</t>
-  </si>
-  <si>
-    <t>27ASB25019097</t>
-  </si>
-  <si>
-    <t>27ASB25019114</t>
-  </si>
-  <si>
-    <t>P111025009</t>
-  </si>
-  <si>
-    <t>27ASB25019137</t>
-  </si>
-  <si>
-    <t>3EG087</t>
-  </si>
-  <si>
-    <t>27ASB25019139</t>
-  </si>
-  <si>
-    <t>27ASB25019141</t>
-  </si>
-  <si>
-    <t>017418</t>
-  </si>
-  <si>
-    <t>GAMMADEX</t>
-  </si>
-  <si>
-    <t>3EG056</t>
-  </si>
-  <si>
-    <t>27ASB25019142</t>
-  </si>
-  <si>
-    <t>27ASB25019164</t>
-  </si>
-  <si>
-    <t>300807</t>
-  </si>
-  <si>
-    <t>300619</t>
-  </si>
-  <si>
-    <t>300626</t>
-  </si>
-  <si>
-    <t>27ASB25019198</t>
-  </si>
-  <si>
-    <t>27ASB25019201</t>
-  </si>
-  <si>
-    <t>3EC044</t>
-  </si>
-  <si>
-    <t>27ASB25019209</t>
-  </si>
-  <si>
-    <t>013783</t>
-  </si>
-  <si>
-    <t>CALGAE</t>
-  </si>
-  <si>
-    <t>1EF003</t>
-  </si>
-  <si>
-    <t>3EG119</t>
-  </si>
-  <si>
-    <t>27ASB25019210</t>
-  </si>
-  <si>
-    <t>27ASB25019211</t>
-  </si>
-  <si>
-    <t>27ASB25019212</t>
-  </si>
-  <si>
-    <t>27ASB25019242</t>
-  </si>
-  <si>
-    <t>27ASB25019297</t>
-  </si>
-  <si>
-    <t>27ASB25019307</t>
-  </si>
-  <si>
-    <t>27ASB25019308</t>
-  </si>
-  <si>
-    <t>27ASB25019384</t>
-  </si>
-  <si>
-    <t>012139</t>
-  </si>
-  <si>
-    <t>TRACETATE SUSPENSI ORAL</t>
-  </si>
-  <si>
-    <t>1EF042T 2</t>
-  </si>
-  <si>
-    <t>016799</t>
-  </si>
-  <si>
-    <t>VOLTERI</t>
-  </si>
-  <si>
-    <t>1EF167</t>
-  </si>
-  <si>
-    <t>27ASB25019462</t>
+    <t>27ASB25020419</t>
+  </si>
+  <si>
+    <t>000780</t>
+  </si>
+  <si>
+    <t>MOLAGIT</t>
+  </si>
+  <si>
+    <t>M11HG038</t>
+  </si>
+  <si>
+    <t>27ASB25020428</t>
+  </si>
+  <si>
+    <t>011970</t>
+  </si>
+  <si>
+    <t>DOTAREM 10 ML</t>
+  </si>
+  <si>
+    <t>24GD1199</t>
+  </si>
+  <si>
+    <t>27ASB25020451</t>
+  </si>
+  <si>
+    <t>3EH061</t>
+  </si>
+  <si>
+    <t>27ASB25020452</t>
+  </si>
+  <si>
+    <t>1EG235</t>
+  </si>
+  <si>
+    <t>27ASB25020453</t>
+  </si>
+  <si>
+    <t>27ASB25020454</t>
+  </si>
+  <si>
+    <t>3EG141</t>
+  </si>
+  <si>
+    <t>27ASB25020455</t>
+  </si>
+  <si>
+    <t>1EF042T 1</t>
+  </si>
+  <si>
+    <t>27ASB25020635</t>
+  </si>
+  <si>
+    <t>27BSB25000643</t>
+  </si>
+  <si>
+    <t>27BSB25000650</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1324,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -1210,118 +1408,118 @@
         <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>81081</v>
+        <v>41732</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="3">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3">
-        <v>168851</v>
+        <v>5842</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="4">
-        <v>46599</v>
+        <v>47330</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>55858</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>8937</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>150000</v>
-      </c>
-      <c r="G5" s="3">
-        <v>21.922000000000001</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>32883</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="K5" s="4">
-        <v>46996</v>
+        <v>47299</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>86000</v>
+        <v>41732</v>
       </c>
       <c r="G6" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>94600</v>
+        <v>14189</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K6" s="4">
-        <v>46356</v>
+        <v>47330</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>41732</v>
+        <v>55858</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
@@ -1330,234 +1528,234 @@
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>5842</v>
+        <v>4469</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K7" s="4">
-        <v>47330</v>
+        <v>47299</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D8" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>55858</v>
+        <v>87846</v>
       </c>
       <c r="G8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I8" s="3">
-        <v>8937</v>
+        <v>13177</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K8" s="4">
-        <v>47299</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>41732</v>
+        <v>1140119</v>
       </c>
       <c r="G9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>14189</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K9" s="4">
-        <v>47330</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>55858</v>
+        <v>70000</v>
       </c>
       <c r="G10" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I10" s="3">
-        <v>4469</v>
+        <v>10500</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K10" s="4">
-        <v>47299</v>
+        <v>47003</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>66400</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>15</v>
+      </c>
+      <c r="I11" s="3">
+        <v>49800</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="3">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <v>18150</v>
-      </c>
-      <c r="G11" s="3">
-        <v>2</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>3630</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="K11" s="4">
-        <v>46934</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="3">
+        <v>12</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>41000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3">
+        <v>49200</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="3">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>85586</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>5</v>
-      </c>
-      <c r="I12" s="3">
-        <v>12838</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="K12" s="4">
-        <v>46630</v>
+        <v>46596</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="3">
+        <v>24</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>56700</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>10</v>
+      </c>
+      <c r="I13" s="3">
+        <v>136080</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>81081</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>5</v>
-      </c>
-      <c r="I13" s="3">
-        <v>4054</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K13" s="4">
-        <v>46660</v>
+        <v>46774</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -1566,27 +1764,27 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>85586</v>
+        <v>850000</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4279</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K14" s="4">
-        <v>46630</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>46</v>
@@ -1595,22 +1793,22 @@
         <v>47</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>130631</v>
+        <v>37500</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>6532</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>48</v>
@@ -1621,107 +1819,107 @@
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>130631</v>
+        <v>87846</v>
       </c>
       <c r="G16" s="3">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I16" s="3">
-        <v>13063</v>
+        <v>105415</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="K16" s="4">
-        <v>46660</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D17" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>85586</v>
+        <v>66400</v>
       </c>
       <c r="G17" s="3">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I17" s="3">
-        <v>8559</v>
+        <v>49800</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K17" s="4">
-        <v>46630</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D18" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>130631</v>
+        <v>120000</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I18" s="3">
-        <v>6532</v>
+        <v>144000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K18" s="4">
-        <v>46630</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -1729,815 +1927,815 @@
         <v>53</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
       </c>
       <c r="F19" s="3">
-        <v>130631</v>
+        <v>320000</v>
       </c>
       <c r="G19" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19" s="3">
         <v>5</v>
       </c>
       <c r="I19" s="3">
-        <v>6532</v>
+        <v>128000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K19" s="4">
-        <v>46660</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D20" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>85586</v>
+        <v>120000</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I20" s="3">
-        <v>12838</v>
+        <v>432000</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K20" s="4">
-        <v>46660</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>37500</v>
+        <v>87846</v>
       </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>84332</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="K21" s="4">
-        <v>46996</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>905000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>62400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>44.906500000000001</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>28022</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K22" s="4">
-        <v>47026</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D23" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>70000</v>
+        <v>850000</v>
       </c>
       <c r="G23" s="3">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>117600</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="K23" s="4">
-        <v>47003</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="D24" s="3">
+        <v>12</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>56700</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>10</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>120000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="H24" s="3">
-        <v>19.18</v>
-      </c>
       <c r="I24" s="3">
-        <v>308160</v>
+        <v>68040</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="K24" s="4">
-        <v>46630</v>
+        <v>46774</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="3">
+        <v>5</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>66400</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>15</v>
+      </c>
+      <c r="I25" s="3">
+        <v>49800</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="3">
-        <v>30</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3">
-        <v>18150</v>
-      </c>
-      <c r="G25" s="3">
-        <v>2</v>
-      </c>
-      <c r="H25" s="3">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
-        <v>10890</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K25" s="4">
-        <v>46934</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D26" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>905000</v>
+        <v>114950</v>
       </c>
       <c r="G26" s="3">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>18392</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="K26" s="4">
-        <v>46965</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D27" s="3">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F27" s="3">
-        <v>90000</v>
+        <v>26100</v>
       </c>
       <c r="G27" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H27" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>126000</v>
+        <v>324162</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="K27" s="4">
-        <v>46418</v>
+        <v>46713</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D28" s="3">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="E28" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F28" s="3">
-        <v>330000</v>
+        <v>41400</v>
       </c>
       <c r="G28" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H28" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3">
-        <v>148500</v>
+        <v>1028376</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K28" s="4">
-        <v>46538</v>
+        <v>46978</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D29" s="3">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F29" s="3">
-        <v>90000</v>
+        <v>39870</v>
       </c>
       <c r="G29" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H29" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>126000</v>
+        <v>990371</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K29" s="4">
-        <v>46418</v>
+        <v>47013</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D30" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E30" s="3">
         <v>0</v>
       </c>
       <c r="F30" s="3">
-        <v>25000</v>
+        <v>90000</v>
       </c>
       <c r="G30" s="3">
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I30" s="3">
-        <v>13750</v>
+        <v>135000</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K30" s="4">
-        <v>46996</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D31" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E31" s="3">
         <v>0</v>
       </c>
       <c r="F31" s="3">
-        <v>19500</v>
+        <v>30000</v>
       </c>
       <c r="G31" s="3">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3">
-        <v>12675</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K31" s="4">
-        <v>46998</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="D32" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>240000</v>
+        <v>155000</v>
       </c>
       <c r="G32" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I32" s="3">
-        <v>48000</v>
+        <v>193750</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K32" s="4">
-        <v>46599</v>
+        <v>46812</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D33" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>183000</v>
+        <v>122000</v>
       </c>
       <c r="G33" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>15</v>
+        <v>59.02</v>
       </c>
       <c r="I33" s="3">
-        <v>183000</v>
+        <v>72004</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K33" s="4">
-        <v>46538</v>
+        <v>46965</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="D34" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>57000</v>
+        <v>37500</v>
       </c>
       <c r="G34" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>5700</v>
+        <v>5625</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K34" s="4">
-        <v>46630</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D35" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>80000</v>
+        <v>37500</v>
       </c>
       <c r="G35" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H35" s="3">
-        <v>40.625</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>455000</v>
+        <v>3750</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="K35" s="4">
-        <v>46599</v>
+        <v>47057</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D36" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E36" s="3">
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>90000</v>
+        <v>28000</v>
       </c>
       <c r="G36" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>441000</v>
+        <v>1680</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="K36" s="4">
-        <v>46446</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D37" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="3">
         <v>0</v>
       </c>
       <c r="F37" s="3">
-        <v>120000</v>
+        <v>25000</v>
       </c>
       <c r="G37" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H37" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I37" s="3">
-        <v>84000</v>
+        <v>3750</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K37" s="4">
-        <v>46507</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D38" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E38" s="3">
         <v>0</v>
       </c>
       <c r="F38" s="3">
-        <v>120000</v>
+        <v>26000</v>
       </c>
       <c r="G38" s="3">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>35</v>
+        <v>58.07</v>
       </c>
       <c r="I38" s="3">
-        <v>546000</v>
+        <v>45295</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="K38" s="4">
-        <v>46507</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D39" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" s="3">
         <v>0</v>
       </c>
       <c r="F39" s="3">
-        <v>320000</v>
+        <v>28400</v>
       </c>
       <c r="G39" s="3">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="K39" s="4">
-        <v>46599</v>
+        <v>46621</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="D40" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E40" s="3">
         <v>0</v>
       </c>
       <c r="F40" s="3">
-        <v>81081</v>
+        <v>16500</v>
       </c>
       <c r="G40" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H40" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3">
-        <v>58378</v>
+        <v>2475</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="K40" s="4">
-        <v>46660</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D41" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>94595</v>
+        <v>58300</v>
       </c>
       <c r="G41" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>68108</v>
+        <v>6996</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K41" s="4">
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D42" s="3">
         <v>1</v>
@@ -2546,147 +2744,147 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>75000</v>
+        <v>2000000</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>29.14</v>
+        <v>15</v>
       </c>
       <c r="I42" s="3">
-        <v>21855</v>
+        <v>300000</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K42" s="4">
-        <v>46568</v>
+        <v>55153</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>127</v>
+        <v>16</v>
       </c>
       <c r="D43" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>125000</v>
+        <v>41732</v>
       </c>
       <c r="G43" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H43" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
-        <v>2250000</v>
+        <v>30047</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="K43" s="4">
-        <v>46599</v>
+        <v>47361</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D44" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>330000</v>
+        <v>72879</v>
       </c>
       <c r="G44" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H44" s="3">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="I44" s="3">
-        <v>1633500</v>
+        <v>43727</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="K44" s="4">
-        <v>46538</v>
+        <v>47695</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D45" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="I45" s="3">
-        <v>3000</v>
+        <v>17342</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K45" s="4">
-        <v>46630</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D46" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>144000</v>
+        <v>24116</v>
       </c>
       <c r="G46" s="3">
         <v>0</v>
@@ -2695,10 +2893,10 @@
         <v>10</v>
       </c>
       <c r="I46" s="3">
-        <v>14400</v>
+        <v>14470</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K46" s="4">
         <v>46660</v>
@@ -2706,314 +2904,314 @@
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="D47" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>50000</v>
+        <v>905000</v>
       </c>
       <c r="G47" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>87500</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="K47" s="4">
-        <v>46265</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D48" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>1200000</v>
+        <v>81081</v>
       </c>
       <c r="G48" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I48" s="3">
-        <v>180000</v>
+        <v>14595</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K48" s="4">
-        <v>46477</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="D49" s="3">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>25000</v>
+        <v>66400</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I49" s="3">
-        <v>12500</v>
+        <v>406368</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="K49" s="4">
-        <v>47026</v>
+        <v>46612</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D50" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E50" s="3">
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>90000</v>
+        <v>19500</v>
       </c>
       <c r="G50" s="3">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I50" s="3">
-        <v>135000</v>
+        <v>9945</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="K50" s="4">
-        <v>46630</v>
+        <v>46556</v>
       </c>
     </row>
     <row r="51" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D51" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E51" s="3">
         <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>105000</v>
+        <v>19500</v>
       </c>
       <c r="G51" s="3">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I51" s="3">
-        <v>37800</v>
+        <v>29835</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K51" s="4">
-        <v>46568</v>
+        <v>46641</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D52" s="3">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>25000</v>
+        <v>120000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="H52" s="3">
-        <v>10</v>
+        <v>22.93</v>
       </c>
       <c r="I52" s="3">
-        <v>2500</v>
+        <v>1130112</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K52" s="4">
-        <v>46630</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D53" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" s="3">
         <v>0</v>
       </c>
       <c r="F53" s="3">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="G53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I53" s="3">
-        <v>21000</v>
+        <v>6000</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="K53" s="4">
-        <v>46980</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="54" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D54" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" s="3">
         <v>0</v>
       </c>
       <c r="F54" s="3">
-        <v>20000</v>
+        <v>90000</v>
       </c>
       <c r="G54" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H54" s="3">
-        <v>7.5</v>
+        <v>30</v>
       </c>
       <c r="I54" s="3">
-        <v>1500</v>
+        <v>126000</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K54" s="4">
-        <v>46660</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="55" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D55" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E55" s="3">
         <v>0</v>
       </c>
       <c r="F55" s="3">
-        <v>125000</v>
+        <v>240000</v>
       </c>
       <c r="G55" s="3">
         <v>5</v>
       </c>
       <c r="H55" s="3">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I55" s="3">
-        <v>875000</v>
+        <v>96000</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="K55" s="4">
         <v>46599</v>
@@ -3021,398 +3219,398 @@
     </row>
     <row r="56" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
       <c r="D56" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E56" s="3">
         <v>0</v>
       </c>
       <c r="F56" s="3">
-        <v>41732</v>
+        <v>50000</v>
       </c>
       <c r="G56" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H56" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I56" s="3">
-        <v>30047</v>
+        <v>35000</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K56" s="4">
-        <v>47726</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>38000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="I57" s="3">
+        <v>950</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D57" s="3">
-        <v>9</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>30000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3">
-        <v>13500</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="K57" s="4">
-        <v>46599</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="58" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D58" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="G58" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I58" s="3">
-        <v>52500</v>
+        <v>2500</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="K58" s="4">
-        <v>46265</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D59" s="3">
+        <v>1</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>20000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J59" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="3">
-        <v>2</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>90000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>5</v>
-      </c>
-      <c r="H59" s="3">
-        <v>30</v>
-      </c>
-      <c r="I59" s="3">
-        <v>63000</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="K59" s="4">
-        <v>46418</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="D60" s="3">
+        <v>2</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>450000</v>
+      </c>
+      <c r="G60" s="3">
         <v>5</v>
       </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3">
-        <v>25000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
       <c r="H60" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I60" s="3">
-        <v>6250</v>
+        <v>189000</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="K60" s="4">
-        <v>47026</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D61" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>25000</v>
+        <v>330000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H61" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I61" s="3">
-        <v>2500</v>
+        <v>1039500</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K61" s="4">
-        <v>46326</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>95</v>
+        <v>165</v>
       </c>
       <c r="D62" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>183000</v>
+        <v>450000</v>
       </c>
       <c r="G62" s="3">
         <v>5</v>
       </c>
       <c r="H62" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I62" s="3">
-        <v>292800</v>
+        <v>94500</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="K62" s="4">
-        <v>46538</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="63" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="D63" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="3">
         <v>0</v>
       </c>
       <c r="F63" s="3">
-        <v>330000</v>
+        <v>50000</v>
       </c>
       <c r="G63" s="3">
         <v>5</v>
       </c>
       <c r="H63" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I63" s="3">
-        <v>445500</v>
+        <v>35000</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="K63" s="4">
-        <v>46538</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D64" s="3">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E64" s="3">
         <v>0</v>
       </c>
       <c r="F64" s="3">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="G64" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H64" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I64" s="3">
-        <v>22500</v>
+        <v>1088000</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K64" s="4">
-        <v>46934</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="D65" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="3">
         <v>0</v>
       </c>
       <c r="F65" s="3">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3">
         <v>5</v>
       </c>
-      <c r="H65" s="3">
-        <v>30</v>
-      </c>
       <c r="I65" s="3">
-        <v>35000</v>
+        <v>1250</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="K65" s="4">
-        <v>46265</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="66" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="D66" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E66" s="3">
         <v>0</v>
       </c>
       <c r="F66" s="3">
-        <v>50000</v>
+        <v>330000</v>
       </c>
       <c r="G66" s="3">
         <v>5</v>
       </c>
       <c r="H66" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I66" s="3">
-        <v>52500</v>
+        <v>1188000</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="K66" s="4">
-        <v>46265</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="D67" s="3">
         <v>1</v>
@@ -3421,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="3">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="G67" s="3">
         <v>5</v>
@@ -3430,48 +3628,48 @@
         <v>30</v>
       </c>
       <c r="I67" s="3">
-        <v>52500</v>
+        <v>17500</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="K67" s="4">
-        <v>46477</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D68" s="3">
+        <v>2</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3">
+        <v>25000</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3">
+        <v>5</v>
+      </c>
+      <c r="I68" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D68" s="3">
-        <v>10</v>
-      </c>
-      <c r="E68" s="3">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3">
-        <v>80000</v>
-      </c>
-      <c r="G68" s="3">
-        <v>0</v>
-      </c>
-      <c r="H68" s="3">
-        <v>40.625</v>
-      </c>
-      <c r="I68" s="3">
-        <v>325000</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K68" s="4">
-        <v>46599</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -3479,10 +3677,10 @@
         <v>179</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -3491,22 +3689,22 @@
         <v>0</v>
       </c>
       <c r="F69" s="3">
-        <v>58300</v>
+        <v>38000</v>
       </c>
       <c r="G69" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I69" s="3">
-        <v>2332</v>
+        <v>1900</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="K69" s="4">
-        <v>46873</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -3514,101 +3712,101 @@
         <v>179</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="D70" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>58300</v>
+        <v>240000</v>
       </c>
       <c r="G70" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I70" s="3">
-        <v>4664</v>
+        <v>96000</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="K70" s="4">
-        <v>46904</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="D71" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="3">
         <v>0</v>
       </c>
       <c r="F71" s="3">
-        <v>125000</v>
+        <v>18000</v>
       </c>
       <c r="G71" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>45</v>
+        <v>7.5</v>
       </c>
       <c r="I71" s="3">
-        <v>125000</v>
+        <v>1350</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="K71" s="4">
-        <v>46599</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D72" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E72" s="3">
         <v>0</v>
       </c>
       <c r="F72" s="3">
-        <v>330000</v>
+        <v>183000</v>
       </c>
       <c r="G72" s="3">
         <v>5</v>
       </c>
       <c r="H72" s="3">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I72" s="3">
-        <v>1633500</v>
+        <v>109800</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="K72" s="4">
         <v>46538</v>
@@ -3616,191 +3814,191 @@
     </row>
     <row r="73" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>124</v>
+        <v>188</v>
       </c>
       <c r="D73" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E73" s="3">
         <v>0</v>
       </c>
       <c r="F73" s="3">
-        <v>75000</v>
+        <v>66900</v>
       </c>
       <c r="G73" s="3">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>29.14</v>
+        <v>17</v>
       </c>
       <c r="I73" s="3">
-        <v>43710</v>
+        <v>170595</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="K73" s="4">
-        <v>46568</v>
+        <v>46590</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="D74" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="3">
         <v>0</v>
       </c>
       <c r="F74" s="3">
-        <v>50000</v>
+        <v>56700</v>
       </c>
       <c r="G74" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I74" s="3">
-        <v>17500</v>
+        <v>28917</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="K74" s="4">
-        <v>46265</v>
+        <v>46836</v>
       </c>
     </row>
     <row r="75" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="D75" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="3">
         <v>0</v>
       </c>
       <c r="F75" s="3">
-        <v>25000</v>
+        <v>262000</v>
       </c>
       <c r="G75" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" s="3">
-        <v>10</v>
+        <v>16.919</v>
       </c>
       <c r="I75" s="3">
-        <v>2500</v>
+        <v>99136</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="K75" s="4">
-        <v>46630</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D76" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" s="3">
         <v>0</v>
       </c>
       <c r="F76" s="3">
-        <v>18000</v>
+        <v>144000</v>
       </c>
       <c r="G76" s="3">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I76" s="3">
-        <v>4050</v>
+        <v>14400</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="K76" s="4">
-        <v>46996</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="D77" s="3">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E77" s="3">
         <v>0</v>
       </c>
       <c r="F77" s="3">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="G77" s="3">
         <v>5</v>
       </c>
       <c r="H77" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I77" s="3">
-        <v>70000</v>
+        <v>1600000</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="K77" s="4">
-        <v>46265</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="D78" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E78" s="3">
         <v>0</v>
@@ -3815,10 +4013,10 @@
         <v>5</v>
       </c>
       <c r="I78" s="3">
-        <v>17500</v>
+        <v>3750</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="K78" s="4">
         <v>47026</v>
@@ -3826,121 +4024,121 @@
     </row>
     <row r="79" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D79" s="3">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="E79" s="3">
         <v>0</v>
       </c>
       <c r="F79" s="3">
-        <v>90000</v>
+        <v>240000</v>
       </c>
       <c r="G79" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H79" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I79" s="3">
-        <v>612000</v>
+        <v>48000</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K79" s="4">
-        <v>46630</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D80" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" s="3">
         <v>0</v>
       </c>
       <c r="F80" s="3">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="G80" s="3">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I80" s="3">
-        <v>7500</v>
+        <v>1500</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="K80" s="4">
-        <v>46326</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="81" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>64</v>
+        <v>183</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>65</v>
+        <v>184</v>
       </c>
       <c r="D81" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
       </c>
       <c r="F81" s="3">
-        <v>70000</v>
+        <v>183000</v>
       </c>
       <c r="G81" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H81" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I81" s="3">
-        <v>21000</v>
+        <v>1134600</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="K81" s="4">
-        <v>46980</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D82" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E82" s="3">
         <v>0</v>
@@ -3955,10 +4153,10 @@
         <v>40</v>
       </c>
       <c r="I82" s="3">
-        <v>160000</v>
+        <v>1920000</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="K82" s="4">
         <v>46630</v>
@@ -3966,538 +4164,538 @@
     </row>
     <row r="83" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="D83" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>122000</v>
+        <v>50000</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H83" s="3">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I83" s="3">
-        <v>439200</v>
+        <v>35000</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="K83" s="4">
-        <v>46965</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="D84" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E84" s="3">
         <v>0</v>
       </c>
       <c r="F84" s="3">
-        <v>90000</v>
+        <v>18000</v>
       </c>
       <c r="G84" s="3">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I84" s="3">
-        <v>207000</v>
+        <v>1350</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="K84" s="4">
-        <v>46630</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="D85" s="3">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="E85" s="3">
         <v>0</v>
       </c>
       <c r="F85" s="3">
-        <v>200000</v>
+        <v>330000</v>
       </c>
       <c r="G85" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H85" s="3">
         <v>40</v>
       </c>
       <c r="I85" s="3">
-        <v>5520000</v>
+        <v>742500</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="K85" s="4">
-        <v>46630</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="D86" s="3">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="E86" s="3">
         <v>0</v>
       </c>
       <c r="F86" s="3">
-        <v>330000</v>
+        <v>16000</v>
       </c>
       <c r="G86" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I86" s="3">
-        <v>148500</v>
+        <v>497760</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="K86" s="4">
-        <v>46538</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>161</v>
+        <v>212</v>
       </c>
       <c r="D87" s="3">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E87" s="3">
         <v>0</v>
       </c>
       <c r="F87" s="3">
-        <v>30000</v>
+        <v>13500</v>
       </c>
       <c r="G87" s="3">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I87" s="3">
-        <v>34500</v>
+        <v>0</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="K87" s="4">
-        <v>46568</v>
+        <v>46977</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>202</v>
+        <v>15</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>203</v>
+        <v>16</v>
       </c>
       <c r="D88" s="3">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="E88" s="3">
         <v>0</v>
       </c>
       <c r="F88" s="3">
-        <v>13500</v>
+        <v>41732</v>
       </c>
       <c r="G88" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H88" s="3">
         <v>0</v>
       </c>
       <c r="I88" s="3">
-        <v>0</v>
+        <v>60094</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="K88" s="4">
-        <v>46977</v>
+        <v>47361</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D89" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>330000</v>
+        <v>55858</v>
       </c>
       <c r="G89" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H89" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>148500</v>
+        <v>20109</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="K89" s="4">
-        <v>46538</v>
+        <v>47299</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="D90" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E90" s="3">
         <v>0</v>
       </c>
       <c r="F90" s="3">
-        <v>50000</v>
+        <v>41732</v>
       </c>
       <c r="G90" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H90" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I90" s="3">
-        <v>17500</v>
+        <v>30047</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="K90" s="4">
-        <v>46295</v>
+        <v>47391</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>209</v>
+        <v>111</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="D91" s="3">
+        <v>6</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>58300</v>
+      </c>
+      <c r="G91" s="3">
         <v>2</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>180000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>5</v>
-      </c>
       <c r="H91" s="3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>63000</v>
+        <v>6996</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K91" s="4">
-        <v>46599</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>102</v>
+        <v>222</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>103</v>
+        <v>223</v>
       </c>
       <c r="D92" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E92" s="3">
         <v>0</v>
       </c>
       <c r="F92" s="3">
-        <v>80000</v>
+        <v>18150</v>
       </c>
       <c r="G92" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I92" s="3">
-        <v>512000</v>
+        <v>3630</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="K92" s="4">
-        <v>46599</v>
+        <v>46843</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D93" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E93" s="3">
         <v>0</v>
       </c>
       <c r="F93" s="3">
-        <v>320000</v>
+        <v>58300</v>
       </c>
       <c r="G93" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H93" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I93" s="3">
-        <v>240000</v>
+        <v>6996</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K93" s="4">
-        <v>46568</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>92</v>
+        <v>223</v>
       </c>
       <c r="D94" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>240000</v>
+        <v>18150</v>
       </c>
       <c r="G94" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H94" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>48000</v>
+        <v>3630</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>93</v>
+        <v>227</v>
       </c>
       <c r="K94" s="4">
-        <v>46599</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="D95" s="3">
+        <v>24</v>
+      </c>
+      <c r="E95" s="3">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3">
+        <v>41732</v>
+      </c>
+      <c r="G95" s="3">
         <v>2</v>
       </c>
-      <c r="E95" s="3">
-        <v>0</v>
-      </c>
-      <c r="F95" s="3">
-        <v>50000</v>
-      </c>
-      <c r="G95" s="3">
-        <v>5</v>
-      </c>
       <c r="H95" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I95" s="3">
-        <v>35000</v>
+        <v>50078</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="K95" s="4">
-        <v>46295</v>
+        <v>47695</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="D96" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>180000</v>
+        <v>81081</v>
       </c>
       <c r="G96" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>12.5</v>
+        <v>3</v>
       </c>
       <c r="I96" s="3">
-        <v>31500</v>
+        <v>58378</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="K96" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>102</v>
+        <v>235</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>103</v>
+        <v>236</v>
       </c>
       <c r="D97" s="3">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E97" s="3">
         <v>0</v>
       </c>
       <c r="F97" s="3">
-        <v>80000</v>
+        <v>30800</v>
       </c>
       <c r="G97" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I97" s="3">
-        <v>1248000</v>
+        <v>7392</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="K97" s="4">
-        <v>46599</v>
+        <v>46561</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="D98" s="3">
         <v>1</v>
@@ -4506,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="3">
-        <v>200000</v>
+        <v>57000</v>
       </c>
       <c r="G98" s="3">
         <v>0</v>
@@ -4515,24 +4713,24 @@
         <v>25</v>
       </c>
       <c r="I98" s="3">
-        <v>50000</v>
+        <v>14250</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="K98" s="4">
-        <v>46446</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="99" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="D99" s="3">
         <v>2</v>
@@ -4541,19 +4739,19 @@
         <v>0</v>
       </c>
       <c r="F99" s="3">
-        <v>320000</v>
+        <v>450000</v>
       </c>
       <c r="G99" s="3">
         <v>5</v>
       </c>
       <c r="H99" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I99" s="3">
-        <v>160000</v>
+        <v>189000</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="K99" s="4">
         <v>46568</v>
@@ -4561,118 +4759,118 @@
     </row>
     <row r="100" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D100" s="3">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H100" s="3">
-        <v>40.625</v>
+        <v>30</v>
       </c>
       <c r="I100" s="3">
-        <v>2632500</v>
+        <v>52500</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="K100" s="4">
-        <v>46599</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>36</v>
+        <v>169</v>
       </c>
       <c r="D101" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>18150</v>
+        <v>330000</v>
       </c>
       <c r="G101" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I101" s="3">
-        <v>3630</v>
+        <v>148500</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="K101" s="4">
-        <v>46873</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="D102" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>50000</v>
+        <v>320000</v>
       </c>
       <c r="G102" s="3">
         <v>5</v>
       </c>
       <c r="H102" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I102" s="3">
-        <v>17500</v>
+        <v>560000</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="K102" s="4">
-        <v>46295</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="103" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="D103" s="3">
         <v>1</v>
@@ -4681,19 +4879,19 @@
         <v>0</v>
       </c>
       <c r="F103" s="3">
-        <v>180000</v>
+        <v>240000</v>
       </c>
       <c r="G103" s="3">
         <v>5</v>
       </c>
       <c r="H103" s="3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="I103" s="3">
-        <v>31500</v>
+        <v>48000</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="K103" s="4">
         <v>46599</v>
@@ -4701,139 +4899,139 @@
     </row>
     <row r="104" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D104" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E104" s="3">
         <v>0</v>
       </c>
       <c r="F104" s="3">
-        <v>144000</v>
+        <v>195000</v>
       </c>
       <c r="G104" s="3">
         <v>5</v>
       </c>
       <c r="H104" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I104" s="3">
-        <v>50400</v>
+        <v>195000</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="K104" s="4">
-        <v>46418</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="105" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D105" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" s="3">
         <v>0</v>
       </c>
       <c r="F105" s="3">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="G105" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H105" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I105" s="3">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="K105" s="4">
-        <v>46599</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="106" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>115</v>
+        <v>257</v>
       </c>
       <c r="D106" s="3">
+        <v>2</v>
+      </c>
+      <c r="E106" s="3">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3">
+        <v>19500</v>
+      </c>
+      <c r="G106" s="3">
+        <v>0</v>
+      </c>
+      <c r="H106" s="3">
         <v>5</v>
       </c>
-      <c r="E106" s="3">
-        <v>0</v>
-      </c>
-      <c r="F106" s="3">
-        <v>320000</v>
-      </c>
-      <c r="G106" s="3">
-        <v>5</v>
-      </c>
-      <c r="H106" s="3">
-        <v>20</v>
-      </c>
       <c r="I106" s="3">
-        <v>400000</v>
+        <v>1950</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="K106" s="4">
-        <v>46568</v>
+        <v>47012</v>
       </c>
     </row>
     <row r="107" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="D107" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" s="3">
         <v>0</v>
       </c>
       <c r="F107" s="3">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G107" s="3">
         <v>5</v>
       </c>
       <c r="H107" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I107" s="3">
-        <v>144000</v>
+        <v>80000</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>93</v>
+        <v>249</v>
       </c>
       <c r="K107" s="4">
         <v>46599</v>
@@ -4841,258 +5039,258 @@
     </row>
     <row r="108" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>236</v>
+        <v>151</v>
       </c>
       <c r="D108" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E108" s="3">
         <v>0</v>
       </c>
       <c r="F108" s="3">
-        <v>315000</v>
+        <v>240000</v>
       </c>
       <c r="G108" s="3">
         <v>5</v>
       </c>
       <c r="H108" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I108" s="3">
-        <v>94500</v>
+        <v>240000</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="K108" s="4">
-        <v>46568</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D109" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E109" s="3">
         <v>0</v>
       </c>
       <c r="F109" s="3">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="G109" s="3">
         <v>0</v>
       </c>
       <c r="H109" s="3">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="I109" s="3">
-        <v>3200000</v>
+        <v>1500</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>213</v>
+        <v>81</v>
       </c>
       <c r="K109" s="4">
-        <v>46599</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="110" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>15</v>
+        <v>263</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>16</v>
+        <v>264</v>
       </c>
       <c r="D110" s="3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E110" s="3">
         <v>0</v>
       </c>
       <c r="F110" s="3">
-        <v>81081</v>
+        <v>33000</v>
       </c>
       <c r="G110" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I110" s="3">
-        <v>58378</v>
+        <v>51150</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="K110" s="4">
-        <v>46691</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="111" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>120</v>
+        <v>267</v>
       </c>
       <c r="D111" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E111" s="3">
         <v>0</v>
       </c>
       <c r="F111" s="3">
-        <v>94595</v>
+        <v>24200</v>
       </c>
       <c r="G111" s="3">
         <v>0</v>
       </c>
       <c r="H111" s="3">
-        <v>3.0011000000000001</v>
+        <v>0</v>
       </c>
       <c r="I111" s="3">
-        <v>68133</v>
+        <v>0</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>121</v>
+        <v>268</v>
       </c>
       <c r="K111" s="4">
-        <v>46660</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="112" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>126</v>
+        <v>269</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="D112" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E112" s="3">
         <v>0</v>
       </c>
       <c r="F112" s="3">
-        <v>125000</v>
+        <v>25000</v>
       </c>
       <c r="G112" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H112" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I112" s="3">
-        <v>62500</v>
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="K112" s="4">
-        <v>46599</v>
+        <v>47133</v>
       </c>
     </row>
     <row r="113" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>136</v>
+        <v>272</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>137</v>
+        <v>273</v>
       </c>
       <c r="D113" s="3">
+        <v>3</v>
+      </c>
+      <c r="E113" s="3">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3">
+        <v>140000</v>
+      </c>
+      <c r="G113" s="3">
         <v>1</v>
       </c>
-      <c r="E113" s="3">
-        <v>0</v>
-      </c>
-      <c r="F113" s="3">
-        <v>50000</v>
-      </c>
-      <c r="G113" s="3">
-        <v>5</v>
-      </c>
       <c r="H113" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I113" s="3">
-        <v>17500</v>
+        <v>21000</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="K113" s="4">
-        <v>46295</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="114" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D114" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E114" s="3">
         <v>0</v>
       </c>
       <c r="F114" s="3">
-        <v>4000000</v>
+        <v>380000</v>
       </c>
       <c r="G114" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H114" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I114" s="3">
-        <v>1600000</v>
+        <v>247000</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="K114" s="4">
-        <v>46599</v>
+        <v>46783</v>
       </c>
     </row>
     <row r="115" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>114</v>
+        <v>278</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>115</v>
+        <v>279</v>
       </c>
       <c r="D115" s="3">
         <v>10</v>
@@ -5101,243 +5299,243 @@
         <v>0</v>
       </c>
       <c r="F115" s="3">
-        <v>320000</v>
+        <v>230000</v>
       </c>
       <c r="G115" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H115" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I115" s="3">
-        <v>800000</v>
+        <v>115000</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="K115" s="4">
-        <v>46568</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="116" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>26</v>
+        <v>222</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="D116" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E116" s="3">
         <v>0</v>
       </c>
       <c r="F116" s="3">
-        <v>41732</v>
+        <v>18150</v>
       </c>
       <c r="G116" s="3">
         <v>2</v>
       </c>
       <c r="H116" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" s="3">
-        <v>30047</v>
+        <v>2904</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="K116" s="4">
-        <v>47726</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="117" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="D117" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E117" s="3">
         <v>0</v>
       </c>
       <c r="F117" s="3">
-        <v>55858</v>
+        <v>18150</v>
       </c>
       <c r="G117" s="3">
         <v>2</v>
       </c>
       <c r="H117" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" s="3">
-        <v>8379</v>
+        <v>726</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="K117" s="4">
-        <v>47664</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="118" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="D118" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E118" s="3">
         <v>0</v>
       </c>
       <c r="F118" s="3">
-        <v>55858</v>
+        <v>18150</v>
       </c>
       <c r="G118" s="3">
         <v>2</v>
       </c>
       <c r="H118" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="3">
-        <v>31839</v>
+        <v>3630</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="K118" s="4">
-        <v>47664</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="119" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>81</v>
+        <v>222</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="D119" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E119" s="3">
         <v>0</v>
       </c>
       <c r="F119" s="3">
-        <v>330000</v>
+        <v>18150</v>
       </c>
       <c r="G119" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H119" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I119" s="3">
-        <v>148500</v>
+        <v>3630</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>206</v>
+        <v>283</v>
       </c>
       <c r="K119" s="4">
-        <v>46538</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="120" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>64</v>
+        <v>231</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>65</v>
+        <v>232</v>
       </c>
       <c r="D120" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E120" s="3">
         <v>0</v>
       </c>
       <c r="F120" s="3">
-        <v>70000</v>
+        <v>81081</v>
       </c>
       <c r="G120" s="3">
         <v>0</v>
       </c>
       <c r="H120" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I120" s="3">
-        <v>7000</v>
+        <v>58378</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>66</v>
+        <v>287</v>
       </c>
       <c r="K120" s="4">
-        <v>47003</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="121" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D121" s="3">
+        <v>12</v>
+      </c>
+      <c r="E121" s="3">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3">
+        <v>72879</v>
+      </c>
+      <c r="G121" s="3">
+        <v>2</v>
+      </c>
+      <c r="H121" s="3">
         <v>1</v>
       </c>
-      <c r="E121" s="3">
-        <v>0</v>
-      </c>
-      <c r="F121" s="3">
-        <v>1200000</v>
-      </c>
-      <c r="G121" s="3">
-        <v>5</v>
-      </c>
-      <c r="H121" s="3">
-        <v>10</v>
-      </c>
       <c r="I121" s="3">
-        <v>180000</v>
+        <v>26236</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="K121" s="4">
-        <v>46477</v>
+        <v>47726</v>
       </c>
     </row>
     <row r="122" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D122" s="3">
         <v>1</v>
@@ -5346,33 +5544,33 @@
         <v>0</v>
       </c>
       <c r="F122" s="3">
-        <v>195000</v>
+        <v>57000</v>
       </c>
       <c r="G122" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H122" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I122" s="3">
-        <v>39000</v>
+        <v>14250</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="K122" s="4">
-        <v>46568</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="123" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="D123" s="3">
         <v>2</v>
@@ -5393,7 +5591,7 @@
         <v>35000</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="K123" s="4">
         <v>46418</v>
@@ -5401,13 +5599,13 @@
     </row>
     <row r="124" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="D124" s="3">
         <v>1</v>
@@ -5416,54 +5614,54 @@
         <v>0</v>
       </c>
       <c r="F124" s="3">
-        <v>240000</v>
+        <v>90000</v>
       </c>
       <c r="G124" s="3">
         <v>5</v>
       </c>
       <c r="H124" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I124" s="3">
-        <v>48000</v>
+        <v>31500</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="K124" s="4">
-        <v>46599</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="D125" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" s="3">
         <v>0</v>
       </c>
       <c r="F125" s="3">
-        <v>320000</v>
+        <v>450000</v>
       </c>
       <c r="G125" s="3">
         <v>5</v>
       </c>
       <c r="H125" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I125" s="3">
-        <v>240000</v>
+        <v>189000</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="K125" s="4">
         <v>46568</v>
@@ -5471,92 +5669,92 @@
     </row>
     <row r="126" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>235</v>
+        <v>15</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="D126" s="3">
+        <v>8</v>
+      </c>
+      <c r="E126" s="3">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3">
+        <v>41732</v>
+      </c>
+      <c r="G126" s="3">
         <v>2</v>
       </c>
-      <c r="E126" s="3">
-        <v>0</v>
-      </c>
-      <c r="F126" s="3">
-        <v>315000</v>
-      </c>
-      <c r="G126" s="3">
-        <v>5</v>
-      </c>
       <c r="H126" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I126" s="3">
-        <v>189000</v>
+        <v>10016</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="K126" s="4">
-        <v>46568</v>
+        <v>47726</v>
       </c>
     </row>
     <row r="127" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>127</v>
+        <v>16</v>
       </c>
       <c r="D127" s="3">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E127" s="3">
         <v>0</v>
       </c>
       <c r="F127" s="3">
-        <v>125000</v>
+        <v>41732</v>
       </c>
       <c r="G127" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H127" s="3">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="I127" s="3">
-        <v>3750000</v>
+        <v>20031</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
       <c r="K127" s="4">
-        <v>46599</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>36</v>
+        <v>236</v>
       </c>
       <c r="D128" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E128" s="3">
         <v>0</v>
       </c>
       <c r="F128" s="3">
-        <v>18150</v>
+        <v>30800</v>
       </c>
       <c r="G128" s="3">
         <v>2</v>
@@ -5565,188 +5763,993 @@
         <v>0</v>
       </c>
       <c r="I128" s="3">
-        <v>3630</v>
+        <v>7392</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="K128" s="4">
-        <v>46873</v>
+        <v>46561</v>
       </c>
     </row>
     <row r="129" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D129" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E129" s="3">
         <v>0</v>
       </c>
       <c r="F129" s="3">
-        <v>55858</v>
+        <v>320000</v>
       </c>
       <c r="G129" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H129" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I129" s="3">
-        <v>16757</v>
+        <v>560000</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K129" s="4">
-        <v>47664</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="130" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>26</v>
+        <v>298</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>27</v>
+        <v>299</v>
       </c>
       <c r="D130" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E130" s="3">
         <v>0</v>
       </c>
       <c r="F130" s="3">
-        <v>41732</v>
+        <v>125000</v>
       </c>
       <c r="G130" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H130" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="I130" s="3">
-        <v>6260</v>
+        <v>500000</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="K130" s="4">
-        <v>47726</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="131" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>269</v>
+        <v>54</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>270</v>
+        <v>55</v>
       </c>
       <c r="D131" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" s="3">
         <v>0</v>
       </c>
       <c r="F131" s="3">
-        <v>450000</v>
+        <v>320000</v>
       </c>
       <c r="G131" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H131" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I131" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="K131" s="4">
-        <v>46568</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="132" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="D132" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E132" s="3">
         <v>0</v>
       </c>
       <c r="F132" s="3">
-        <v>360000</v>
+        <v>195000</v>
       </c>
       <c r="G132" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H132" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I132" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="K132" s="4">
-        <v>46568</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="133" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
       <c r="C133" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D133" s="3">
+        <v>4</v>
+      </c>
+      <c r="E133" s="3">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3">
+        <v>50000</v>
+      </c>
+      <c r="G133" s="3">
+        <v>5</v>
+      </c>
+      <c r="H133" s="3">
         <v>30</v>
       </c>
-      <c r="D133" s="3">
-        <v>24</v>
-      </c>
-      <c r="E133" s="3">
-        <v>0</v>
-      </c>
-      <c r="F133" s="3">
+      <c r="I133" s="3">
+        <v>70000</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K133" s="4">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D134" s="3">
+        <v>2</v>
+      </c>
+      <c r="E134" s="3">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3">
+        <v>125000</v>
+      </c>
+      <c r="G134" s="3">
+        <v>5</v>
+      </c>
+      <c r="H134" s="3">
+        <v>45</v>
+      </c>
+      <c r="I134" s="3">
+        <v>125000</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="K134" s="4">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D135" s="3">
+        <v>2</v>
+      </c>
+      <c r="E135" s="3">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3">
+        <v>19500</v>
+      </c>
+      <c r="G135" s="3">
+        <v>0</v>
+      </c>
+      <c r="H135" s="3">
+        <v>5</v>
+      </c>
+      <c r="I135" s="3">
+        <v>1950</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K135" s="4">
+        <v>47012</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D136" s="3">
+        <v>1</v>
+      </c>
+      <c r="E136" s="3">
+        <v>0</v>
+      </c>
+      <c r="F136" s="3">
+        <v>70000</v>
+      </c>
+      <c r="G136" s="3">
+        <v>0</v>
+      </c>
+      <c r="H136" s="3">
+        <v>10</v>
+      </c>
+      <c r="I136" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="K136" s="4">
+        <v>47008</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A137" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D137" s="3">
+        <v>4</v>
+      </c>
+      <c r="E137" s="3">
+        <v>0</v>
+      </c>
+      <c r="F137" s="3">
+        <v>50000</v>
+      </c>
+      <c r="G137" s="3">
+        <v>5</v>
+      </c>
+      <c r="H137" s="3">
+        <v>30</v>
+      </c>
+      <c r="I137" s="3">
+        <v>70000</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K137" s="4">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A138" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D138" s="3">
+        <v>12</v>
+      </c>
+      <c r="E138" s="3">
+        <v>0</v>
+      </c>
+      <c r="F138" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G138" s="3">
+        <v>0</v>
+      </c>
+      <c r="H138" s="3">
+        <v>5</v>
+      </c>
+      <c r="I138" s="3">
+        <v>96000</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K138" s="4">
+        <v>47422</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D139" s="3">
+        <v>1</v>
+      </c>
+      <c r="E139" s="3">
+        <v>0</v>
+      </c>
+      <c r="F139" s="3">
+        <v>120000</v>
+      </c>
+      <c r="G139" s="3">
+        <v>0</v>
+      </c>
+      <c r="H139" s="3">
+        <v>0</v>
+      </c>
+      <c r="I139" s="3">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="K139" s="4">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A140" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D140" s="3">
+        <v>10</v>
+      </c>
+      <c r="E140" s="3">
+        <v>0</v>
+      </c>
+      <c r="F140" s="3">
+        <v>18150</v>
+      </c>
+      <c r="G140" s="3">
+        <v>2</v>
+      </c>
+      <c r="H140" s="3">
+        <v>0</v>
+      </c>
+      <c r="I140" s="3">
+        <v>3630</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="K140" s="4">
+        <v>46934</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D141" s="3">
+        <v>10</v>
+      </c>
+      <c r="E141" s="3">
+        <v>0</v>
+      </c>
+      <c r="F141" s="3">
+        <v>18150</v>
+      </c>
+      <c r="G141" s="3">
+        <v>2</v>
+      </c>
+      <c r="H141" s="3">
+        <v>0</v>
+      </c>
+      <c r="I141" s="3">
+        <v>3630</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="K141" s="4">
+        <v>46934</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D142" s="3">
+        <v>3</v>
+      </c>
+      <c r="E142" s="3">
+        <v>0</v>
+      </c>
+      <c r="F142" s="3">
+        <v>41732</v>
+      </c>
+      <c r="G142" s="3">
+        <v>2</v>
+      </c>
+      <c r="H142" s="3">
+        <v>3</v>
+      </c>
+      <c r="I142" s="3">
+        <v>6260</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K142" s="4">
+        <v>47756</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" s="3">
+        <v>3</v>
+      </c>
+      <c r="E143" s="3">
+        <v>0</v>
+      </c>
+      <c r="F143" s="3">
         <v>55858</v>
       </c>
-      <c r="G133" s="3">
-        <v>0</v>
-      </c>
-      <c r="H133" s="3">
-        <v>0</v>
-      </c>
-      <c r="I133" s="3">
-        <v>0</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="K133" s="4">
+      <c r="G143" s="3">
+        <v>2</v>
+      </c>
+      <c r="H143" s="3">
+        <v>3</v>
+      </c>
+      <c r="I143" s="3">
+        <v>8378</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="K143" s="4">
         <v>47664</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D144" s="3">
+        <v>1</v>
+      </c>
+      <c r="E144" s="3">
+        <v>0</v>
+      </c>
+      <c r="F144" s="3">
+        <v>30000</v>
+      </c>
+      <c r="G144" s="3">
+        <v>0</v>
+      </c>
+      <c r="H144" s="3">
+        <v>5</v>
+      </c>
+      <c r="I144" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K144" s="4">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D145" s="3">
+        <v>6</v>
+      </c>
+      <c r="E145" s="3">
+        <v>0</v>
+      </c>
+      <c r="F145" s="3">
+        <v>58300</v>
+      </c>
+      <c r="G145" s="3">
+        <v>2</v>
+      </c>
+      <c r="H145" s="3">
+        <v>0</v>
+      </c>
+      <c r="I145" s="3">
+        <v>6996</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K145" s="4">
+        <v>46873</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D146" s="3">
+        <v>2</v>
+      </c>
+      <c r="E146" s="3">
+        <v>0</v>
+      </c>
+      <c r="F146" s="3">
+        <v>85000</v>
+      </c>
+      <c r="G146" s="3">
+        <v>7</v>
+      </c>
+      <c r="H146" s="3">
+        <v>34.764699999999998</v>
+      </c>
+      <c r="I146" s="3">
+        <v>71000</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K146" s="4">
+        <v>47726</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D147" s="3">
+        <v>1</v>
+      </c>
+      <c r="E147" s="3">
+        <v>0</v>
+      </c>
+      <c r="F147" s="3">
+        <v>553430</v>
+      </c>
+      <c r="G147" s="3">
+        <v>2</v>
+      </c>
+      <c r="H147" s="3">
+        <v>28</v>
+      </c>
+      <c r="I147" s="3">
+        <v>166029</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K147" s="4">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D148" s="3">
+        <v>2</v>
+      </c>
+      <c r="E148" s="3">
+        <v>0</v>
+      </c>
+      <c r="F148" s="3">
+        <v>125000</v>
+      </c>
+      <c r="G148" s="3">
+        <v>5</v>
+      </c>
+      <c r="H148" s="3">
+        <v>45</v>
+      </c>
+      <c r="I148" s="3">
+        <v>125000</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="K148" s="4">
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D149" s="3">
+        <v>3</v>
+      </c>
+      <c r="E149" s="3">
+        <v>0</v>
+      </c>
+      <c r="F149" s="3">
+        <v>240000</v>
+      </c>
+      <c r="G149" s="3">
+        <v>5</v>
+      </c>
+      <c r="H149" s="3">
+        <v>15</v>
+      </c>
+      <c r="I149" s="3">
+        <v>144000</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K149" s="4">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D150" s="3">
+        <v>31</v>
+      </c>
+      <c r="E150" s="3">
+        <v>0</v>
+      </c>
+      <c r="F150" s="3">
+        <v>125000</v>
+      </c>
+      <c r="G150" s="3">
+        <v>5</v>
+      </c>
+      <c r="H150" s="3">
+        <v>45</v>
+      </c>
+      <c r="I150" s="3">
+        <v>1937500</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="K150" s="4">
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D151" s="3">
+        <v>1</v>
+      </c>
+      <c r="E151" s="3">
+        <v>0</v>
+      </c>
+      <c r="F151" s="3">
+        <v>330000</v>
+      </c>
+      <c r="G151" s="3">
+        <v>5</v>
+      </c>
+      <c r="H151" s="3">
+        <v>40</v>
+      </c>
+      <c r="I151" s="3">
+        <v>148500</v>
+      </c>
+      <c r="J151" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="K151" s="4">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D152" s="3">
+        <v>1</v>
+      </c>
+      <c r="E152" s="3">
+        <v>0</v>
+      </c>
+      <c r="F152" s="3">
+        <v>19500</v>
+      </c>
+      <c r="G152" s="3">
+        <v>0</v>
+      </c>
+      <c r="H152" s="3">
+        <v>5</v>
+      </c>
+      <c r="I152" s="3">
+        <v>975</v>
+      </c>
+      <c r="J152" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K152" s="4">
+        <v>47012</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D153" s="3">
+        <v>1</v>
+      </c>
+      <c r="E153" s="3">
+        <v>0</v>
+      </c>
+      <c r="F153" s="3">
+        <v>450000</v>
+      </c>
+      <c r="G153" s="3">
+        <v>5</v>
+      </c>
+      <c r="H153" s="3">
+        <v>16</v>
+      </c>
+      <c r="I153" s="3">
+        <v>94500</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="K153" s="4">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A154" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D154" s="3">
+        <v>2</v>
+      </c>
+      <c r="E154" s="3">
+        <v>0</v>
+      </c>
+      <c r="F154" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G154" s="3">
+        <v>0</v>
+      </c>
+      <c r="H154" s="3">
+        <v>0</v>
+      </c>
+      <c r="I154" s="3">
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K154" s="4">
+        <v>47422</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A155" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D155" s="3">
+        <v>7</v>
+      </c>
+      <c r="E155" s="3">
+        <v>0</v>
+      </c>
+      <c r="F155" s="3">
+        <v>13500</v>
+      </c>
+      <c r="G155" s="3">
+        <v>0</v>
+      </c>
+      <c r="H155" s="3">
+        <v>0</v>
+      </c>
+      <c r="I155" s="3">
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K155" s="4">
+        <v>46977</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D156" s="3">
+        <v>15</v>
+      </c>
+      <c r="E156" s="3">
+        <v>0</v>
+      </c>
+      <c r="F156" s="3">
+        <v>13500</v>
+      </c>
+      <c r="G156" s="3">
+        <v>0</v>
+      </c>
+      <c r="H156" s="3">
+        <v>0</v>
+      </c>
+      <c r="I156" s="3">
+        <v>0</v>
+      </c>
+      <c r="J156" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K156" s="4">
+        <v>46977</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/invoice-product-missing.xlsx
+++ b/uploads/invoice-product-missing.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251114\Eksport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251202\fix\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB3BBA7-ED16-4F42-843F-99ABB3CA75D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Invoice Product" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="304">
   <si>
     <t>nomor_invoice</t>
   </si>
@@ -63,7 +64,31 @@
     <t>ex: 2025/08/01</t>
   </si>
   <si>
-    <t>07ASB24028161</t>
+    <t>02ASB25020598</t>
+  </si>
+  <si>
+    <t>014283</t>
+  </si>
+  <si>
+    <t>Y - RINS 2X12 ML ( MO )</t>
+  </si>
+  <si>
+    <t>2EE124</t>
+  </si>
+  <si>
+    <t>07ASB25031653</t>
+  </si>
+  <si>
+    <t>013010</t>
+  </si>
+  <si>
+    <t>NUTRIGARAM 300 GR</t>
+  </si>
+  <si>
+    <t>300623</t>
+  </si>
+  <si>
+    <t>07ASB25037346</t>
   </si>
   <si>
     <t>013008</t>
@@ -72,25 +97,22 @@
     <t>NUTRISALIN 200 GR</t>
   </si>
   <si>
-    <t>290708</t>
-  </si>
-  <si>
-    <t>013010</t>
-  </si>
-  <si>
-    <t>NUTRIGARAM 300 GR</t>
-  </si>
-  <si>
-    <t>290613</t>
-  </si>
-  <si>
-    <t>290714</t>
-  </si>
-  <si>
-    <t>290609</t>
-  </si>
-  <si>
-    <t>07ASB25034549</t>
+    <t>300904</t>
+  </si>
+  <si>
+    <t>013009</t>
+  </si>
+  <si>
+    <t>NUTRISALIN 400 GR</t>
+  </si>
+  <si>
+    <t>301013</t>
+  </si>
+  <si>
+    <t>301011</t>
+  </si>
+  <si>
+    <t>07ASB25037663</t>
   </si>
   <si>
     <t>012963</t>
@@ -102,13 +124,307 @@
     <t>A001</t>
   </si>
   <si>
-    <t>017544</t>
-  </si>
-  <si>
-    <t>SEROQUEL 25 MG</t>
-  </si>
-  <si>
-    <t>60049359</t>
+    <t>07ASB25037742</t>
+  </si>
+  <si>
+    <t>000026</t>
+  </si>
+  <si>
+    <t>ALKOHOL 70%</t>
+  </si>
+  <si>
+    <t>J25001P</t>
+  </si>
+  <si>
+    <t>07ASB25037908</t>
+  </si>
+  <si>
+    <t>015220</t>
+  </si>
+  <si>
+    <t>ACNES STARTER PACK</t>
+  </si>
+  <si>
+    <t>PGND003</t>
+  </si>
+  <si>
+    <t>015395</t>
+  </si>
+  <si>
+    <t>HL GOKUJYUN ULT MOIST MILK 100ML</t>
+  </si>
+  <si>
+    <t>PJQT08T</t>
+  </si>
+  <si>
+    <t>015392</t>
+  </si>
+  <si>
+    <t>HL GOKUJYUN ULT MOIST FW 100GR</t>
+  </si>
+  <si>
+    <t>PITJ201</t>
+  </si>
+  <si>
+    <t>07ASB25038078</t>
+  </si>
+  <si>
+    <t>000629</t>
+  </si>
+  <si>
+    <t>INPEPSA SUSPENSI</t>
+  </si>
+  <si>
+    <t>1EG203</t>
+  </si>
+  <si>
+    <t>013660</t>
+  </si>
+  <si>
+    <t>DUOXAL</t>
+  </si>
+  <si>
+    <t>X624</t>
+  </si>
+  <si>
+    <t>000689</t>
+  </si>
+  <si>
+    <t>LACTULAX SYRUP 120</t>
+  </si>
+  <si>
+    <t>J25003A</t>
+  </si>
+  <si>
+    <t>07ASB25038091</t>
+  </si>
+  <si>
+    <t>003482</t>
+  </si>
+  <si>
+    <t>BACTODERM CREAM</t>
+  </si>
+  <si>
+    <t>G25016G</t>
+  </si>
+  <si>
+    <t>07ASB25038512</t>
+  </si>
+  <si>
+    <t>014961</t>
+  </si>
+  <si>
+    <t>CALLUSOL ( MO )</t>
+  </si>
+  <si>
+    <t>1EH134</t>
+  </si>
+  <si>
+    <t>014962</t>
+  </si>
+  <si>
+    <t>Y - RINS 10 X 12 ML ( MO )</t>
+  </si>
+  <si>
+    <t>2EF123</t>
+  </si>
+  <si>
+    <t>2EH085</t>
+  </si>
+  <si>
+    <t>08ASB25017561</t>
+  </si>
+  <si>
+    <t>300624</t>
+  </si>
+  <si>
+    <t>08ASB25018184</t>
+  </si>
+  <si>
+    <t>000449</t>
+  </si>
+  <si>
+    <t>FARBION-5000 INJEKSI</t>
+  </si>
+  <si>
+    <t>3EG120</t>
+  </si>
+  <si>
+    <t>08ASB25018185</t>
+  </si>
+  <si>
+    <t>014714</t>
+  </si>
+  <si>
+    <t>PROFERRO</t>
+  </si>
+  <si>
+    <t>1EG235</t>
+  </si>
+  <si>
+    <t>08ASB25018186</t>
+  </si>
+  <si>
+    <t>014441</t>
+  </si>
+  <si>
+    <t>INVICLOT ( 5 VIAL )</t>
+  </si>
+  <si>
+    <t>3EG140</t>
+  </si>
+  <si>
+    <t>08ASB25018187</t>
+  </si>
+  <si>
+    <t>013453</t>
+  </si>
+  <si>
+    <t>METACOSFAR 100</t>
+  </si>
+  <si>
+    <t>3EG009</t>
+  </si>
+  <si>
+    <t>08ASB25018188</t>
+  </si>
+  <si>
+    <t>009216</t>
+  </si>
+  <si>
+    <t>FARMADOL INFUS</t>
+  </si>
+  <si>
+    <t>3EH063</t>
+  </si>
+  <si>
+    <t>08ASB25018191</t>
+  </si>
+  <si>
+    <t>013783</t>
+  </si>
+  <si>
+    <t>CALGAE</t>
+  </si>
+  <si>
+    <t>1EF003</t>
+  </si>
+  <si>
+    <t>010441</t>
+  </si>
+  <si>
+    <t>MONECTO 20 - TAB</t>
+  </si>
+  <si>
+    <t>1EG134</t>
+  </si>
+  <si>
+    <t>08ASB25018192</t>
+  </si>
+  <si>
+    <t>08ASB25018193</t>
+  </si>
+  <si>
+    <t>015618</t>
+  </si>
+  <si>
+    <t>CALITOZ</t>
+  </si>
+  <si>
+    <t>1EI146</t>
+  </si>
+  <si>
+    <t>004908</t>
+  </si>
+  <si>
+    <t>OBH IKA 200 ML</t>
+  </si>
+  <si>
+    <t>J25010A</t>
+  </si>
+  <si>
+    <t>08ASB25018195</t>
+  </si>
+  <si>
+    <t>000513</t>
+  </si>
+  <si>
+    <t>FUROSEMIDE 40 MG</t>
+  </si>
+  <si>
+    <t>A 00496 IC</t>
+  </si>
+  <si>
+    <t>016476</t>
+  </si>
+  <si>
+    <t>GLICLAZIDE MR</t>
+  </si>
+  <si>
+    <t>1EI102</t>
+  </si>
+  <si>
+    <t>015731</t>
+  </si>
+  <si>
+    <t>FEBUXOSTAT 40</t>
+  </si>
+  <si>
+    <t>1EH148</t>
+  </si>
+  <si>
+    <t>1EI099</t>
+  </si>
+  <si>
+    <t>08ASB25018250</t>
+  </si>
+  <si>
+    <t>000900</t>
+  </si>
+  <si>
+    <t>NOKOBA INJEKSI</t>
+  </si>
+  <si>
+    <t>3ED069</t>
+  </si>
+  <si>
+    <t>08ASB25018275</t>
+  </si>
+  <si>
+    <t>000578</t>
+  </si>
+  <si>
+    <t>IBUPROFEN 400 MG</t>
+  </si>
+  <si>
+    <t>A 02229 IC</t>
+  </si>
+  <si>
+    <t>004907</t>
+  </si>
+  <si>
+    <t>OBH IKA 100 ML</t>
+  </si>
+  <si>
+    <t>J25017A</t>
+  </si>
+  <si>
+    <t>08ASB25018276</t>
+  </si>
+  <si>
+    <t>08ASB25018277</t>
+  </si>
+  <si>
+    <t>08ASB25018286</t>
+  </si>
+  <si>
+    <t>000319</t>
+  </si>
+  <si>
+    <t>DIGOXIN 0.25 MG</t>
+  </si>
+  <si>
+    <t>A 08617 IC</t>
   </si>
   <si>
     <t>000999</t>
@@ -117,145 +433,52 @@
     <t>PHENYTOIN 100 CAP.</t>
   </si>
   <si>
-    <t>J25010D</t>
-  </si>
-  <si>
-    <t>000689</t>
-  </si>
-  <si>
-    <t>LACTULAX SYRUP 120</t>
-  </si>
-  <si>
-    <t>E25004A</t>
-  </si>
-  <si>
-    <t>003482</t>
-  </si>
-  <si>
-    <t>BACTODERM CREAM</t>
-  </si>
-  <si>
-    <t>G25016G</t>
-  </si>
-  <si>
-    <t>07ASB25034824</t>
-  </si>
-  <si>
-    <t>000112</t>
-  </si>
-  <si>
-    <t>BACTODERM OINTMENT</t>
-  </si>
-  <si>
-    <t>A25011G</t>
-  </si>
-  <si>
-    <t>015167</t>
-  </si>
-  <si>
-    <t>HP PRO PLUS.</t>
-  </si>
-  <si>
-    <t>07213111</t>
-  </si>
-  <si>
-    <t>004849</t>
-  </si>
-  <si>
-    <t>FERRIZ DROPS 15 ML</t>
-  </si>
-  <si>
-    <t>5G 1089</t>
-  </si>
-  <si>
-    <t>07ASB25034950</t>
-  </si>
-  <si>
-    <t>000629</t>
-  </si>
-  <si>
-    <t>INPEPSA SUSPENSI</t>
-  </si>
-  <si>
-    <t>1EG203</t>
-  </si>
-  <si>
-    <t>07ASB25034968</t>
-  </si>
-  <si>
-    <t>015026</t>
-  </si>
-  <si>
-    <t>PEINLOS 400</t>
-  </si>
-  <si>
-    <t>3EF089</t>
-  </si>
-  <si>
-    <t>07ASB25035316</t>
-  </si>
-  <si>
-    <t>015442</t>
-  </si>
-  <si>
-    <t>NEO HP PRO.</t>
-  </si>
-  <si>
-    <t>08343311</t>
-  </si>
-  <si>
-    <t>013660</t>
-  </si>
-  <si>
-    <t>DUOXAL</t>
-  </si>
-  <si>
-    <t>X624</t>
-  </si>
-  <si>
-    <t>07ASB25035953</t>
-  </si>
-  <si>
-    <t>010042</t>
-  </si>
-  <si>
-    <t>LIP ICE C ROSSY KISS</t>
-  </si>
-  <si>
-    <t>OKCR004</t>
-  </si>
-  <si>
-    <t>015406</t>
-  </si>
-  <si>
-    <t>HL SHIROJYUN STARTER PACK 20GR</t>
-  </si>
-  <si>
-    <t>PHJZ008</t>
-  </si>
-  <si>
-    <t>015392</t>
-  </si>
-  <si>
-    <t>HL GOKUJYUN ULT MOIST FW 100GR</t>
-  </si>
-  <si>
-    <t>PITJ201</t>
-  </si>
-  <si>
-    <t>12ASB25021890</t>
-  </si>
-  <si>
-    <t>016476</t>
-  </si>
-  <si>
-    <t>GLICLAZIDE MR</t>
-  </si>
-  <si>
-    <t>1EG159</t>
-  </si>
-  <si>
-    <t>12ASB25022059</t>
+    <t>K25003D</t>
+  </si>
+  <si>
+    <t>015193</t>
+  </si>
+  <si>
+    <t>SERTRALINE</t>
+  </si>
+  <si>
+    <t>1EI080</t>
+  </si>
+  <si>
+    <t>017431</t>
+  </si>
+  <si>
+    <t>IBUPROFEN 200</t>
+  </si>
+  <si>
+    <t>A 08502 JB</t>
+  </si>
+  <si>
+    <t>08ASB25018287</t>
+  </si>
+  <si>
+    <t>000839</t>
+  </si>
+  <si>
+    <t>NEO-MERCAZOLE TABLET</t>
+  </si>
+  <si>
+    <t>5H 1106</t>
+  </si>
+  <si>
+    <t>08ASB25018301</t>
+  </si>
+  <si>
+    <t>012704</t>
+  </si>
+  <si>
+    <t>FARMADOL INFUS 50 ML</t>
+  </si>
+  <si>
+    <t>3EG102</t>
+  </si>
+  <si>
+    <t>08ASB25018373</t>
   </si>
   <si>
     <t>003430</t>
@@ -264,19 +487,301 @@
     <t>AMITRIPTILINE 25 MG</t>
   </si>
   <si>
-    <t>A 12503 FC1</t>
-  </si>
-  <si>
-    <t>12ASB25022087</t>
-  </si>
-  <si>
-    <t>001196</t>
-  </si>
-  <si>
-    <t>SIMARC - 2</t>
-  </si>
-  <si>
-    <t>1EB196</t>
+    <t>A 12522 JC</t>
+  </si>
+  <si>
+    <t>08ASB25018387</t>
+  </si>
+  <si>
+    <t>08ASB25018388</t>
+  </si>
+  <si>
+    <t>011472</t>
+  </si>
+  <si>
+    <t>FIXACEP ORAL DROPS</t>
+  </si>
+  <si>
+    <t>8EG001 2</t>
+  </si>
+  <si>
+    <t>08ASB25018403</t>
+  </si>
+  <si>
+    <t>08ASB25018404</t>
+  </si>
+  <si>
+    <t>08ASB25018405</t>
+  </si>
+  <si>
+    <t>013454</t>
+  </si>
+  <si>
+    <t>XOLMETRAS 350 ( 100 ML )</t>
+  </si>
+  <si>
+    <t>3EF054</t>
+  </si>
+  <si>
+    <t>012739</t>
+  </si>
+  <si>
+    <t>XOLMETRAS 350 ( 50ML )</t>
+  </si>
+  <si>
+    <t>3RJ048</t>
+  </si>
+  <si>
+    <t>08ASB25018406</t>
+  </si>
+  <si>
+    <t>08ASB25018407</t>
+  </si>
+  <si>
+    <t>08ASB25018445</t>
+  </si>
+  <si>
+    <t>016627</t>
+  </si>
+  <si>
+    <t>TRAMADOL 50 MG ( GF )</t>
+  </si>
+  <si>
+    <t>B5I318</t>
+  </si>
+  <si>
+    <t>08ASB25018467</t>
+  </si>
+  <si>
+    <t>013683</t>
+  </si>
+  <si>
+    <t>RESFAR INFUS IV</t>
+  </si>
+  <si>
+    <t>3EG105 1</t>
+  </si>
+  <si>
+    <t>08ASB25018471</t>
+  </si>
+  <si>
+    <t>013640</t>
+  </si>
+  <si>
+    <t>UMARONE</t>
+  </si>
+  <si>
+    <t>3EE130</t>
+  </si>
+  <si>
+    <t>08ASB25018472</t>
+  </si>
+  <si>
+    <t>000780</t>
+  </si>
+  <si>
+    <t>MOLAGIT</t>
+  </si>
+  <si>
+    <t>M11HG038</t>
+  </si>
+  <si>
+    <t>08ASB25018515</t>
+  </si>
+  <si>
+    <t>08ASB25018521</t>
+  </si>
+  <si>
+    <t>08ASB25018522</t>
+  </si>
+  <si>
+    <t>A 00406 JC</t>
+  </si>
+  <si>
+    <t>015495</t>
+  </si>
+  <si>
+    <t>ROSUVASTATIN 10 MG</t>
+  </si>
+  <si>
+    <t>1EB063</t>
+  </si>
+  <si>
+    <t>08ASB25018524</t>
+  </si>
+  <si>
+    <t>004416</t>
+  </si>
+  <si>
+    <t>SALBUTAMOL 2 MG</t>
+  </si>
+  <si>
+    <t>A 08245 IC</t>
+  </si>
+  <si>
+    <t>08ASB25018586</t>
+  </si>
+  <si>
+    <t>08ASB25018596</t>
+  </si>
+  <si>
+    <t>08ASB25018597</t>
+  </si>
+  <si>
+    <t>000543</t>
+  </si>
+  <si>
+    <t>HALOPERIDOL 0.5 MG</t>
+  </si>
+  <si>
+    <t>A 01806 HC</t>
+  </si>
+  <si>
+    <t>08ASB25018622</t>
+  </si>
+  <si>
+    <t>1EI013</t>
+  </si>
+  <si>
+    <t>08ASB25018623</t>
+  </si>
+  <si>
+    <t>08ASB25018628</t>
+  </si>
+  <si>
+    <t>016768</t>
+  </si>
+  <si>
+    <t>AMIODARONE INJEKSI</t>
+  </si>
+  <si>
+    <t>3EG074</t>
+  </si>
+  <si>
+    <t>08ASB25018629</t>
+  </si>
+  <si>
+    <t>3EG148</t>
+  </si>
+  <si>
+    <t>K25006A</t>
+  </si>
+  <si>
+    <t>08ASB25018630</t>
+  </si>
+  <si>
+    <t>08ASB25018631</t>
+  </si>
+  <si>
+    <t>08ASB25018632</t>
+  </si>
+  <si>
+    <t>08ASB25018633</t>
+  </si>
+  <si>
+    <t>08ASB25018641</t>
+  </si>
+  <si>
+    <t>08ASB25018694</t>
+  </si>
+  <si>
+    <t>08ASB25018695</t>
+  </si>
+  <si>
+    <t>08ASB25018696</t>
+  </si>
+  <si>
+    <t>08ASB25018697</t>
+  </si>
+  <si>
+    <t>K25017D</t>
+  </si>
+  <si>
+    <t>08ASB25018698</t>
+  </si>
+  <si>
+    <t>08ASB25018699</t>
+  </si>
+  <si>
+    <t>1EI152</t>
+  </si>
+  <si>
+    <t>08BSB25001003</t>
+  </si>
+  <si>
+    <t>010325</t>
+  </si>
+  <si>
+    <t>TS50 SCRUBBRUSH W/CG4%&amp;SOAP</t>
+  </si>
+  <si>
+    <t>250720</t>
+  </si>
+  <si>
+    <t>16ASB25020042</t>
+  </si>
+  <si>
+    <t>016809</t>
+  </si>
+  <si>
+    <t>ZYMUNO 200 ML</t>
+  </si>
+  <si>
+    <t>L110725034</t>
+  </si>
+  <si>
+    <t>16ASB25020402</t>
+  </si>
+  <si>
+    <t>016806</t>
+  </si>
+  <si>
+    <t>ETAWALIN 200 GR</t>
+  </si>
+  <si>
+    <t>P110925019</t>
+  </si>
+  <si>
+    <t>23ASB25012778</t>
+  </si>
+  <si>
+    <t>25ASB25019194</t>
+  </si>
+  <si>
+    <t>2EE043</t>
+  </si>
+  <si>
+    <t>2EF096</t>
+  </si>
+  <si>
+    <t>2EH084</t>
+  </si>
+  <si>
+    <t>25ASB25019605</t>
+  </si>
+  <si>
+    <t>A 08615 IC</t>
+  </si>
+  <si>
+    <t>A 00493 IC</t>
+  </si>
+  <si>
+    <t>A 02237 JC</t>
+  </si>
+  <si>
+    <t>000652</t>
+  </si>
+  <si>
+    <t>ISOSORBIDE DINITRATE 5 MG</t>
+  </si>
+  <si>
+    <t>A 02313 IC</t>
+  </si>
+  <si>
+    <t>K25002D</t>
+  </si>
+  <si>
+    <t>A 08238 HC</t>
   </si>
   <si>
     <t>015563</t>
@@ -288,394 +793,40 @@
     <t>1EG173</t>
   </si>
   <si>
-    <t>12ASB25022431</t>
-  </si>
-  <si>
-    <t>5G 1096</t>
-  </si>
-  <si>
-    <t>004848</t>
-  </si>
-  <si>
-    <t>FERRIZ SIRUP 100 ML</t>
-  </si>
-  <si>
-    <t>5K 1213</t>
-  </si>
-  <si>
-    <t>008664</t>
-  </si>
-  <si>
-    <t>CALLUSOL</t>
-  </si>
-  <si>
-    <t>1EE150</t>
-  </si>
-  <si>
-    <t>011957</t>
-  </si>
-  <si>
-    <t>POLYCROL FORTE SUSP -BTL 100 ML</t>
-  </si>
-  <si>
-    <t>5G 1079</t>
-  </si>
-  <si>
-    <t>12ASB25022464</t>
-  </si>
-  <si>
-    <t>000654</t>
-  </si>
-  <si>
-    <t>ISOTIC ADRETOR 0,50 %</t>
-  </si>
-  <si>
-    <t>2EG027</t>
-  </si>
-  <si>
-    <t>012123</t>
-  </si>
-  <si>
-    <t>LAKTULOSA GENERIK 60ML</t>
-  </si>
-  <si>
-    <t>H25014A</t>
-  </si>
-  <si>
-    <t>001013</t>
-  </si>
-  <si>
-    <t>POLYCROL SUSPENSI - BTL 100 ML</t>
-  </si>
-  <si>
-    <t>5H 1135</t>
-  </si>
-  <si>
-    <t>13ASB25016823</t>
-  </si>
-  <si>
-    <t>014962</t>
-  </si>
-  <si>
-    <t>Y - RINS 10 X 12 ML ( MO )</t>
-  </si>
-  <si>
-    <t>2RJ114</t>
-  </si>
-  <si>
-    <t>18BSB25000214</t>
-  </si>
-  <si>
-    <t>017655</t>
-  </si>
-  <si>
-    <t>ACEMED REUSABLE BIPOLAR FORCEPS 200MM, TIP SIZE 0,</t>
-  </si>
-  <si>
-    <t>NZ20241234</t>
-  </si>
-  <si>
-    <t>25ASB24015854</t>
-  </si>
-  <si>
-    <t>290806</t>
-  </si>
-  <si>
-    <t>25ASB25014626</t>
-  </si>
-  <si>
-    <t>013009</t>
-  </si>
-  <si>
-    <t>NUTRISALIN 400 GR</t>
-  </si>
-  <si>
-    <t>300716</t>
-  </si>
-  <si>
-    <t>25ASB25016769</t>
-  </si>
-  <si>
-    <t>000652</t>
-  </si>
-  <si>
-    <t>ISOSORBIDE DINITRATE 5 MG</t>
-  </si>
-  <si>
-    <t>A 02380 GC</t>
-  </si>
-  <si>
-    <t>25ASB25017546</t>
-  </si>
-  <si>
-    <t>016627</t>
-  </si>
-  <si>
-    <t>TRAMADOL 50 MG ( GF )</t>
-  </si>
-  <si>
-    <t>B5I317</t>
-  </si>
-  <si>
-    <t>25ASB25017826</t>
-  </si>
-  <si>
-    <t>017181</t>
-  </si>
-  <si>
-    <t>EYEBOST 160 GRAM</t>
-  </si>
-  <si>
-    <t>EY0825083</t>
-  </si>
-  <si>
-    <t>H25006A</t>
-  </si>
-  <si>
-    <t>000596</t>
-  </si>
-  <si>
-    <t>IKADRYL SYR. 100 ML</t>
-  </si>
-  <si>
-    <t>F25008A</t>
-  </si>
-  <si>
-    <t>J25005A</t>
-  </si>
-  <si>
-    <t>25ASB25017911</t>
-  </si>
-  <si>
-    <t>000032</t>
-  </si>
-  <si>
-    <t>ALPARA KAPLET</t>
-  </si>
-  <si>
-    <t>A06HS218</t>
-  </si>
-  <si>
-    <t>25ASB25017920</t>
-  </si>
-  <si>
-    <t>25ASB25017934</t>
-  </si>
-  <si>
-    <t>011472</t>
-  </si>
-  <si>
-    <t>FIXACEP ORAL DROPS</t>
-  </si>
-  <si>
-    <t>8EG001 2</t>
-  </si>
-  <si>
-    <t>014714</t>
-  </si>
-  <si>
-    <t>PROFERRO</t>
-  </si>
-  <si>
-    <t>1EG099</t>
-  </si>
-  <si>
-    <t>25ASB25017970</t>
-  </si>
-  <si>
-    <t>000449</t>
-  </si>
-  <si>
-    <t>FARBION-5000 INJEKSI</t>
+    <t>25ASB25019606</t>
   </si>
   <si>
     <t>3EB075</t>
   </si>
   <si>
-    <t>000578</t>
-  </si>
-  <si>
-    <t>IBUPROFEN 400 MG</t>
-  </si>
-  <si>
-    <t>A 02225 IC</t>
-  </si>
-  <si>
-    <t>A 02392 HC</t>
-  </si>
-  <si>
-    <t>006978</t>
-  </si>
-  <si>
-    <t>SALBUTAMOL 4 MG</t>
-  </si>
-  <si>
-    <t>A 08362 JC</t>
-  </si>
-  <si>
-    <t>012139</t>
-  </si>
-  <si>
-    <t>TRACETATE SUSPENSI ORAL</t>
-  </si>
-  <si>
-    <t>1EF041T</t>
-  </si>
-  <si>
-    <t>25ASB25017971</t>
-  </si>
-  <si>
-    <t>014441</t>
-  </si>
-  <si>
-    <t>INVICLOT ( 5 VIAL )</t>
-  </si>
-  <si>
-    <t>3EE094</t>
-  </si>
-  <si>
-    <t>25ASB25017994</t>
-  </si>
-  <si>
-    <t>012704</t>
-  </si>
-  <si>
-    <t>FARMADOL INFUS 50 ML</t>
-  </si>
-  <si>
-    <t>3EG102</t>
-  </si>
-  <si>
-    <t>25ASB25017995</t>
-  </si>
-  <si>
-    <t>000513</t>
-  </si>
-  <si>
-    <t>FUROSEMIDE 40 MG</t>
-  </si>
-  <si>
-    <t>A 00496 IC</t>
-  </si>
-  <si>
-    <t>25ASB25017996</t>
-  </si>
-  <si>
-    <t>004416</t>
-  </si>
-  <si>
-    <t>SALBUTAMOL 2 MG</t>
-  </si>
-  <si>
-    <t>A 08238 HC</t>
-  </si>
-  <si>
-    <t>013640</t>
-  </si>
-  <si>
-    <t>UMARONE</t>
-  </si>
-  <si>
-    <t>3EE130</t>
-  </si>
-  <si>
-    <t>25ASB25018023</t>
-  </si>
-  <si>
-    <t>010198</t>
-  </si>
-  <si>
-    <t>BACTODERM CREAM 10 MG</t>
-  </si>
-  <si>
-    <t>G25014G</t>
-  </si>
-  <si>
-    <t>C25014G</t>
-  </si>
-  <si>
-    <t>25ASB25018077</t>
-  </si>
-  <si>
-    <t>001130</t>
-  </si>
-  <si>
-    <t>RENAQUIL TABLET</t>
-  </si>
-  <si>
-    <t>1EF033</t>
-  </si>
-  <si>
-    <t>25ASB25018110</t>
-  </si>
-  <si>
-    <t>000363</t>
-  </si>
-  <si>
-    <t>ERYTHROMYCIN 500 MG</t>
-  </si>
-  <si>
-    <t>B 02529 IC</t>
-  </si>
-  <si>
-    <t>25ASB25018190</t>
-  </si>
-  <si>
-    <t>25ASB25018235</t>
-  </si>
-  <si>
-    <t>015193</t>
-  </si>
-  <si>
-    <t>SERTRALINE</t>
-  </si>
-  <si>
-    <t>1EH161</t>
-  </si>
-  <si>
-    <t>25ASB25018247</t>
-  </si>
-  <si>
-    <t>3EG140</t>
-  </si>
-  <si>
-    <t>25ASB25018254</t>
-  </si>
-  <si>
-    <t>000026</t>
-  </si>
-  <si>
-    <t>ALKOHOL 70%</t>
-  </si>
-  <si>
-    <t>J25001P</t>
-  </si>
-  <si>
-    <t>25BSB25001513</t>
-  </si>
-  <si>
-    <t>010325</t>
-  </si>
-  <si>
-    <t>TS50 SCRUBBRUSH W/CG4%&amp;SOAP</t>
-  </si>
-  <si>
-    <t>250824</t>
-  </si>
-  <si>
-    <t>26ASB24021414</t>
-  </si>
-  <si>
-    <t>290805</t>
-  </si>
-  <si>
-    <t>26ASB24022295</t>
-  </si>
-  <si>
-    <t>290610</t>
-  </si>
-  <si>
-    <t>290910</t>
+    <t>3EH062</t>
+  </si>
+  <si>
+    <t>3EI069</t>
+  </si>
+  <si>
+    <t>25ASB25019608</t>
+  </si>
+  <si>
+    <t>25ASB25019647</t>
+  </si>
+  <si>
+    <t>25ASB25019664</t>
+  </si>
+  <si>
+    <t>25ASB25019692</t>
+  </si>
+  <si>
+    <t>017421</t>
+  </si>
+  <si>
+    <t>ETAWAKU LESS SUGAR</t>
+  </si>
+  <si>
+    <t>PEL2.141224</t>
+  </si>
+  <si>
+    <t>25ASB25019764</t>
   </si>
   <si>
     <t>26ASB25020250</t>
@@ -687,262 +838,91 @@
     <t>26ASB25020251</t>
   </si>
   <si>
-    <t>014283</t>
-  </si>
-  <si>
-    <t>Y - RINS 2X12 ML ( MO )</t>
-  </si>
-  <si>
     <t>2EC061</t>
   </si>
   <si>
     <t>26ASB25021228</t>
   </si>
   <si>
+    <t>26ASB25026401</t>
+  </si>
+  <si>
+    <t>P111025092</t>
+  </si>
+  <si>
     <t>27ASB25014375</t>
   </si>
   <si>
     <t>2ED090</t>
   </si>
   <si>
-    <t>27ASB25015642</t>
-  </si>
-  <si>
-    <t>300709</t>
-  </si>
-  <si>
-    <t>27ASB25017192</t>
-  </si>
-  <si>
-    <t>016806</t>
-  </si>
-  <si>
-    <t>ETAWALIN 200 GR</t>
-  </si>
-  <si>
-    <t>P110925025</t>
-  </si>
-  <si>
-    <t>27ASB25019812</t>
-  </si>
-  <si>
-    <t>014961</t>
-  </si>
-  <si>
-    <t>CALLUSOL ( MO )</t>
-  </si>
-  <si>
-    <t>1EF116</t>
-  </si>
-  <si>
-    <t>27ASB25019936</t>
-  </si>
-  <si>
-    <t>015618</t>
-  </si>
-  <si>
-    <t>CALITOZ</t>
-  </si>
-  <si>
-    <t>1EI086</t>
-  </si>
-  <si>
-    <t>27ASB25019937</t>
-  </si>
-  <si>
-    <t>1EF042T 2</t>
-  </si>
-  <si>
-    <t>27ASB25019949</t>
-  </si>
-  <si>
-    <t>3EG119</t>
-  </si>
-  <si>
-    <t>27ASB25019950</t>
-  </si>
-  <si>
-    <t>3EG138</t>
-  </si>
-  <si>
-    <t>27ASB25019951</t>
-  </si>
-  <si>
-    <t>3EG031</t>
-  </si>
-  <si>
-    <t>27ASB25019952</t>
-  </si>
-  <si>
-    <t>1EG097</t>
-  </si>
-  <si>
-    <t>27ASB25019953</t>
-  </si>
-  <si>
-    <t>013783</t>
-  </si>
-  <si>
-    <t>CALGAE</t>
-  </si>
-  <si>
-    <t>1EH001</t>
-  </si>
-  <si>
-    <t>004908</t>
-  </si>
-  <si>
-    <t>OBH IKA 200 ML</t>
-  </si>
-  <si>
-    <t>J25010A</t>
-  </si>
-  <si>
-    <t>27ASB25019954</t>
-  </si>
-  <si>
-    <t>27ASB25019955</t>
-  </si>
-  <si>
-    <t>27ASB25020020</t>
-  </si>
-  <si>
-    <t>27ASB25020038</t>
-  </si>
-  <si>
-    <t>016865</t>
-  </si>
-  <si>
-    <t>CLONASOL CREAM</t>
-  </si>
-  <si>
-    <t>4AR01</t>
-  </si>
-  <si>
-    <t>000305</t>
-  </si>
-  <si>
-    <t>DERMASOLON OINT.</t>
-  </si>
-  <si>
-    <t>J24011G</t>
-  </si>
-  <si>
-    <t>000517</t>
-  </si>
-  <si>
-    <t>GENTASOLON CREAM 5</t>
-  </si>
-  <si>
-    <t>G25009G</t>
-  </si>
-  <si>
-    <t>016884</t>
-  </si>
-  <si>
-    <t>NORTA BB SOOTH DIAPER RASH CREAM</t>
-  </si>
-  <si>
-    <t>4AO01</t>
-  </si>
-  <si>
-    <t>016879</t>
-  </si>
-  <si>
-    <t>NORTA DAY ADV MOIST LOTION</t>
-  </si>
-  <si>
-    <t>5AI01</t>
-  </si>
-  <si>
-    <t>016880</t>
-  </si>
-  <si>
-    <t>NORTA DAY MOIST RICH BODY WASH</t>
-  </si>
-  <si>
-    <t>4AL02</t>
-  </si>
-  <si>
-    <t>27ASB25020081</t>
-  </si>
-  <si>
-    <t>2ED091</t>
+    <t>27ASB25020868</t>
+  </si>
+  <si>
+    <t>1EH135</t>
   </si>
   <si>
     <t>2EF039</t>
   </si>
   <si>
-    <t>27ASB25020087</t>
-  </si>
-  <si>
-    <t>27ASB25020089</t>
-  </si>
-  <si>
-    <t>27ASB25020092</t>
+    <t>27ASB25020871</t>
+  </si>
+  <si>
+    <t>2ED079</t>
+  </si>
+  <si>
+    <t>27ASB25021039</t>
+  </si>
+  <si>
+    <t>300626</t>
+  </si>
+  <si>
+    <t>27ASB25021066</t>
   </si>
   <si>
     <t>P111025112</t>
   </si>
   <si>
-    <t>27ASB25020095</t>
-  </si>
-  <si>
-    <t>300815</t>
-  </si>
-  <si>
-    <t>27ASB25020128</t>
-  </si>
-  <si>
-    <t>27ASB25020129</t>
-  </si>
-  <si>
-    <t>27ASB25020143</t>
-  </si>
-  <si>
-    <t>300804</t>
-  </si>
-  <si>
-    <t>300906</t>
-  </si>
-  <si>
-    <t>27ASB25020179</t>
-  </si>
-  <si>
-    <t>27ASB25020216</t>
-  </si>
-  <si>
-    <t>27ASB25020217</t>
-  </si>
-  <si>
-    <t>009216</t>
-  </si>
-  <si>
-    <t>FARMADOL INFUS</t>
-  </si>
-  <si>
-    <t>3EG123</t>
-  </si>
-  <si>
-    <t>27ASB25020218</t>
-  </si>
-  <si>
-    <t>27ASB25020219</t>
-  </si>
-  <si>
-    <t>27ASB25020220</t>
-  </si>
-  <si>
-    <t>27ASB25020221</t>
-  </si>
-  <si>
-    <t>J25011D</t>
-  </si>
-  <si>
-    <t>27ASB25020222</t>
-  </si>
-  <si>
-    <t>27ASB25020253</t>
+    <t>27ASB25021282</t>
+  </si>
+  <si>
+    <t>017647</t>
+  </si>
+  <si>
+    <t>VITAMEAL</t>
+  </si>
+  <si>
+    <t>VM0925182</t>
+  </si>
+  <si>
+    <t>017648</t>
+  </si>
+  <si>
+    <t>VITAMEAL LESS SUGAR</t>
+  </si>
+  <si>
+    <t>VG0925029</t>
+  </si>
+  <si>
+    <t>017661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETAWALIN SEREAL </t>
+  </si>
+  <si>
+    <t>P14102501ER</t>
+  </si>
+  <si>
+    <t>27ASB25021376</t>
+  </si>
+  <si>
+    <t>2ED082</t>
+  </si>
+  <si>
+    <t>27ASB25021397</t>
+  </si>
+  <si>
+    <t>27ASB25021523</t>
   </si>
   <si>
     <t>015564</t>
@@ -952,105 +932,12 @@
   </si>
   <si>
     <t>25OV2001</t>
-  </si>
-  <si>
-    <t>27ASB25020265</t>
-  </si>
-  <si>
-    <t>012671</t>
-  </si>
-  <si>
-    <t>LUPRED TABLET</t>
-  </si>
-  <si>
-    <t>1EF169</t>
-  </si>
-  <si>
-    <t>27ASB25020284</t>
-  </si>
-  <si>
-    <t>27ASB25020285</t>
-  </si>
-  <si>
-    <t>27ASB25020299</t>
-  </si>
-  <si>
-    <t>300626</t>
-  </si>
-  <si>
-    <t>27ASB25020314</t>
-  </si>
-  <si>
-    <t>27ASB25020316</t>
-  </si>
-  <si>
-    <t>2ED082</t>
-  </si>
-  <si>
-    <t>27ASB25020419</t>
-  </si>
-  <si>
-    <t>000780</t>
-  </si>
-  <si>
-    <t>MOLAGIT</t>
-  </si>
-  <si>
-    <t>M11HG038</t>
-  </si>
-  <si>
-    <t>27ASB25020428</t>
-  </si>
-  <si>
-    <t>011970</t>
-  </si>
-  <si>
-    <t>DOTAREM 10 ML</t>
-  </si>
-  <si>
-    <t>24GD1199</t>
-  </si>
-  <si>
-    <t>27ASB25020451</t>
-  </si>
-  <si>
-    <t>3EH061</t>
-  </si>
-  <si>
-    <t>27ASB25020452</t>
-  </si>
-  <si>
-    <t>1EG235</t>
-  </si>
-  <si>
-    <t>27ASB25020453</t>
-  </si>
-  <si>
-    <t>27ASB25020454</t>
-  </si>
-  <si>
-    <t>3EG141</t>
-  </si>
-  <si>
-    <t>27ASB25020455</t>
-  </si>
-  <si>
-    <t>1EF042T 1</t>
-  </si>
-  <si>
-    <t>27ASB25020635</t>
-  </si>
-  <si>
-    <t>27BSB25000643</t>
-  </si>
-  <si>
-    <t>27BSB25000650</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -1320,11 +1207,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K156"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -1408,13 +1295,13 @@
         <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>41732</v>
+        <v>18150</v>
       </c>
       <c r="G4" s="3">
         <v>2</v>
@@ -1423,27 +1310,27 @@
         <v>0</v>
       </c>
       <c r="I4" s="3">
-        <v>5842</v>
+        <v>3630</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="4">
-        <v>47330</v>
+        <v>46904</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -1455,30 +1342,30 @@
         <v>2</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" s="3">
-        <v>8937</v>
+        <v>33515</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="4">
-        <v>47299</v>
+        <v>47664</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -1490,307 +1377,307 @@
         <v>2</v>
       </c>
       <c r="H6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3">
-        <v>14189</v>
+        <v>30047</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K6" s="4">
-        <v>47330</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>55858</v>
+        <v>72879</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
       </c>
       <c r="H7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3">
-        <v>4469</v>
+        <v>17491</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K7" s="4">
-        <v>47299</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>72879</v>
+      </c>
+      <c r="G8" s="3">
         <v>2</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>87846</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3">
-        <v>13177</v>
+        <v>8745</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K8" s="4">
-        <v>46752</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>1140119</v>
+        <v>87846</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>70277</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K9" s="4">
-        <v>46446</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>70000</v>
+        <v>16000</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I10" s="3">
-        <v>10500</v>
+        <v>28800</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K10" s="4">
-        <v>47003</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3">
-        <v>66400</v>
+        <v>32400</v>
       </c>
       <c r="G11" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H11" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3">
-        <v>49800</v>
+        <v>402408</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K11" s="4">
-        <v>46520</v>
+        <v>46937</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D12" s="3">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" s="3">
-        <v>41000</v>
+        <v>50850</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H12" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
-        <v>49200</v>
+        <v>631557</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K12" s="4">
-        <v>46596</v>
+        <v>47033</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D13" s="3">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="E13" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F13" s="3">
-        <v>56700</v>
+        <v>39870</v>
       </c>
       <c r="G13" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H13" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3">
-        <v>136080</v>
+        <v>1980742</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K13" s="4">
-        <v>46774</v>
+        <v>47013</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>850000</v>
+        <v>120000</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>144000</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K14" s="4">
-        <v>46996</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -1799,36 +1686,36 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>37500</v>
+        <v>114950</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>18392</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K15" s="4">
-        <v>46599</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D16" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
@@ -1843,10 +1730,10 @@
         <v>8</v>
       </c>
       <c r="I16" s="3">
-        <v>105415</v>
+        <v>42166</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K16" s="4">
         <v>46752</v>
@@ -1854,16 +1741,16 @@
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -1878,24 +1765,24 @@
         <v>15</v>
       </c>
       <c r="I17" s="3">
-        <v>49800</v>
+        <v>99600</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="K17" s="4">
-        <v>46520</v>
+        <v>46634</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D18" s="3">
         <v>12</v>
@@ -1904,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>120000</v>
+        <v>41000</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
@@ -1913,138 +1800,138 @@
         <v>10</v>
       </c>
       <c r="I18" s="3">
-        <v>144000</v>
+        <v>49200</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K18" s="4">
-        <v>46599</v>
+        <v>46596</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D19" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
       </c>
       <c r="F19" s="3">
-        <v>320000</v>
+        <v>30800</v>
       </c>
       <c r="G19" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H19" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3">
-        <v>128000</v>
+        <v>7392</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="K19" s="4">
-        <v>46568</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D20" s="3">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>120000</v>
+        <v>58300</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>432000</v>
+        <v>6996</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="K20" s="4">
-        <v>46599</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>87846</v>
+        <v>18150</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>84332</v>
+        <v>3630</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="K21" s="4">
-        <v>46752</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D22" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>905000</v>
+        <v>55858</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -2056,30 +1943,30 @@
         <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K22" s="4">
-        <v>46996</v>
+        <v>47664</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D23" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>850000</v>
+        <v>55858</v>
       </c>
       <c r="G23" s="3">
         <v>0</v>
@@ -2091,252 +1978,252 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="K23" s="4">
-        <v>46996</v>
+        <v>47664</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D24" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>56700</v>
+        <v>50000</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I24" s="3">
-        <v>68040</v>
+        <v>122500</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="K24" s="4">
-        <v>46774</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="D25" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>66400</v>
+        <v>240000</v>
       </c>
       <c r="G25" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H25" s="3">
         <v>15</v>
       </c>
       <c r="I25" s="3">
-        <v>49800</v>
+        <v>96000</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="K25" s="4">
-        <v>46520</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D26" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>114950</v>
+        <v>330000</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26" s="3">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="I26" s="3">
-        <v>18392</v>
+        <v>742500</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="K26" s="4">
-        <v>46477</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D27" s="3">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="E27" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>26100</v>
+        <v>1200000</v>
       </c>
       <c r="G27" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I27" s="3">
-        <v>324162</v>
+        <v>540000</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="K27" s="4">
-        <v>46713</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D28" s="3">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="E28" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3">
-        <v>41400</v>
+        <v>125000</v>
       </c>
       <c r="G28" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H28" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I28" s="3">
-        <v>1028376</v>
+        <v>3125000</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="K28" s="4">
-        <v>46978</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D29" s="3">
-        <v>138</v>
+        <v>3</v>
       </c>
       <c r="E29" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>39870</v>
+        <v>195000</v>
       </c>
       <c r="G29" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I29" s="3">
-        <v>990371</v>
+        <v>117000</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="K29" s="4">
-        <v>47013</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D30" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E30" s="3">
         <v>0</v>
       </c>
       <c r="F30" s="3">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="G30" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H30" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I30" s="3">
-        <v>135000</v>
+        <v>52500</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="K30" s="4">
         <v>46599</v>
@@ -2344,57 +2231,57 @@
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>240000</v>
+      </c>
+      <c r="G31" s="3">
+        <v>5</v>
+      </c>
+      <c r="H31" s="3">
+        <v>15</v>
+      </c>
+      <c r="I31" s="3">
+        <v>96000</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="3">
-        <v>10</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3">
-        <v>30000</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
-      <c r="H31" s="3">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="K31" s="4">
-        <v>46568</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D32" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>155000</v>
+        <v>57000</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -2403,129 +2290,129 @@
         <v>25</v>
       </c>
       <c r="I32" s="3">
-        <v>193750</v>
+        <v>28500</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="K32" s="4">
-        <v>46812</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D33" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>122000</v>
+        <v>19500</v>
       </c>
       <c r="G33" s="3">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>59.02</v>
+        <v>5</v>
       </c>
       <c r="I33" s="3">
-        <v>72004</v>
+        <v>10725</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="K33" s="4">
-        <v>46965</v>
+        <v>47012</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="D34" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>37500</v>
+        <v>25000</v>
       </c>
       <c r="G34" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I34" s="3">
-        <v>5625</v>
+        <v>10000</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="K34" s="4">
-        <v>46599</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D35" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>37500</v>
+        <v>90000</v>
       </c>
       <c r="G35" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I35" s="3">
-        <v>3750</v>
+        <v>81000</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="K35" s="4">
-        <v>47057</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D36" s="3">
         <v>3</v>
@@ -2534,208 +2421,208 @@
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>28000</v>
+        <v>105000</v>
       </c>
       <c r="G36" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I36" s="3">
-        <v>1680</v>
+        <v>47250</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="K36" s="4">
-        <v>46538</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D37" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="3">
         <v>0</v>
       </c>
       <c r="F37" s="3">
-        <v>25000</v>
+        <v>90000</v>
       </c>
       <c r="G37" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H37" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I37" s="3">
-        <v>3750</v>
+        <v>18000</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="K37" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D38" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" s="3">
         <v>0</v>
       </c>
       <c r="F38" s="3">
-        <v>26000</v>
+        <v>525000</v>
       </c>
       <c r="G38" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H38" s="3">
-        <v>58.07</v>
+        <v>16</v>
       </c>
       <c r="I38" s="3">
-        <v>45295</v>
+        <v>110250</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="K38" s="4">
-        <v>46599</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D39" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3">
         <v>0</v>
       </c>
       <c r="F39" s="3">
-        <v>28400</v>
+        <v>38000</v>
       </c>
       <c r="G39" s="3">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I39" s="3">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="K39" s="4">
-        <v>46621</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D40" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E40" s="3">
         <v>0</v>
       </c>
       <c r="F40" s="3">
-        <v>16500</v>
+        <v>12200</v>
       </c>
       <c r="G40" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I40" s="3">
-        <v>2475</v>
+        <v>4880</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="K40" s="4">
-        <v>46630</v>
+        <v>47021</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="D41" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>58300</v>
+        <v>50000</v>
       </c>
       <c r="G41" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I41" s="3">
-        <v>6996</v>
+        <v>17500</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="K41" s="4">
-        <v>46691</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D42" s="3">
         <v>1</v>
@@ -2744,421 +2631,421 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>2000000</v>
+        <v>330000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H42" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="I42" s="3">
-        <v>300000</v>
+        <v>148500</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="K42" s="4">
-        <v>55153</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="D43" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>41732</v>
+        <v>30000</v>
       </c>
       <c r="G43" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I43" s="3">
-        <v>30047</v>
+        <v>9000</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="K43" s="4">
-        <v>47361</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D44" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>72879</v>
+        <v>25000</v>
       </c>
       <c r="G44" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I44" s="3">
-        <v>43727</v>
+        <v>10000</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="K44" s="4">
-        <v>47695</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>2</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>38000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D45" s="3">
-        <v>7</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>25000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>9.91</v>
-      </c>
-      <c r="I45" s="3">
-        <v>17342</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="K45" s="4">
-        <v>46599</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" s="3">
+        <v>4</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2440</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D46" s="3">
-        <v>6</v>
-      </c>
-      <c r="E46" s="3">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3">
-        <v>24116</v>
-      </c>
-      <c r="G46" s="3">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3">
-        <v>10</v>
-      </c>
-      <c r="I46" s="3">
-        <v>14470</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="K46" s="4">
-        <v>46660</v>
+        <v>47021</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="D47" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>905000</v>
+        <v>70000</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="K47" s="4">
-        <v>46996</v>
+        <v>47029</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D48" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>81081</v>
+        <v>200000</v>
       </c>
       <c r="G48" s="3">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="I48" s="3">
-        <v>14595</v>
+        <v>80000</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K48" s="4">
-        <v>46630</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="D49" s="3">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>66400</v>
+        <v>25000</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I49" s="3">
-        <v>406368</v>
+        <v>12500</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="K49" s="4">
-        <v>46612</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D50" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" s="3">
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>19500</v>
+        <v>150000</v>
       </c>
       <c r="G50" s="3">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I50" s="3">
-        <v>9945</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="K50" s="4">
-        <v>46556</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="51" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D51" s="3">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E51" s="3">
         <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>19500</v>
+        <v>80000</v>
       </c>
       <c r="G51" s="3">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>17</v>
+        <v>40.625</v>
       </c>
       <c r="I51" s="3">
-        <v>29835</v>
+        <v>1235000</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="K51" s="4">
-        <v>46641</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D52" s="3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>120000</v>
+        <v>30000</v>
       </c>
       <c r="G52" s="3">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>22.93</v>
+        <v>5</v>
       </c>
       <c r="I52" s="3">
-        <v>1130112</v>
+        <v>4500</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="K52" s="4">
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D53" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53" s="3">
         <v>0</v>
       </c>
       <c r="F53" s="3">
-        <v>30000</v>
+        <v>125000</v>
       </c>
       <c r="G53" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H53" s="3">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="I53" s="3">
-        <v>6000</v>
+        <v>187500</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K53" s="4">
-        <v>46568</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="54" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D54" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" s="3">
         <v>0</v>
@@ -3173,10 +3060,10 @@
         <v>30</v>
       </c>
       <c r="I54" s="3">
-        <v>126000</v>
+        <v>157500</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="K54" s="4">
         <v>46418</v>
@@ -3184,13 +3071,13 @@
     </row>
     <row r="55" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="D55" s="3">
         <v>2</v>
@@ -3199,138 +3086,138 @@
         <v>0</v>
       </c>
       <c r="F55" s="3">
-        <v>240000</v>
+        <v>57000</v>
       </c>
       <c r="G55" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I55" s="3">
-        <v>96000</v>
+        <v>28500</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="K55" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="56" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="D56" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" s="3">
         <v>0</v>
       </c>
       <c r="F56" s="3">
-        <v>50000</v>
+        <v>330000</v>
       </c>
       <c r="G56" s="3">
         <v>5</v>
       </c>
       <c r="H56" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I56" s="3">
-        <v>35000</v>
+        <v>445500</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="K56" s="4">
-        <v>46265</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="D57" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
       </c>
       <c r="F57" s="3">
-        <v>38000</v>
+        <v>50000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H57" s="3">
-        <v>2.5</v>
+        <v>30</v>
       </c>
       <c r="I57" s="3">
-        <v>950</v>
+        <v>52500</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="K57" s="4">
-        <v>47026</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="58" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="D58" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>25000</v>
+        <v>580000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H58" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I58" s="3">
-        <v>2500</v>
+        <v>348000</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K58" s="4">
-        <v>46630</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
@@ -3339,208 +3226,208 @@
         <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>20000</v>
+        <v>315000</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="3">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="I59" s="3">
-        <v>1500</v>
+        <v>94500</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K59" s="4">
-        <v>46691</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="D60" s="3">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E60" s="3">
         <v>0</v>
       </c>
       <c r="F60" s="3">
-        <v>450000</v>
+        <v>125000</v>
       </c>
       <c r="G60" s="3">
         <v>5</v>
       </c>
       <c r="H60" s="3">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I60" s="3">
-        <v>189000</v>
+        <v>3000000</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="K60" s="4">
-        <v>46568</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>168</v>
+        <v>89</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="D61" s="3">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>330000</v>
+        <v>125000</v>
       </c>
       <c r="G61" s="3">
         <v>5</v>
       </c>
       <c r="H61" s="3">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I61" s="3">
-        <v>1039500</v>
+        <v>3750000</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="K61" s="4">
-        <v>46538</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D62" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>450000</v>
+        <v>24116</v>
       </c>
       <c r="G62" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
-        <v>94500</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="K62" s="4">
-        <v>46568</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="63" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="D63" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E63" s="3">
         <v>0</v>
       </c>
       <c r="F63" s="3">
-        <v>50000</v>
+        <v>199000</v>
       </c>
       <c r="G63" s="3">
         <v>5</v>
       </c>
       <c r="H63" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I63" s="3">
-        <v>35000</v>
+        <v>1641750</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="K63" s="4">
-        <v>46265</v>
+        <v>46965</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D64" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E64" s="3">
         <v>0</v>
       </c>
       <c r="F64" s="3">
-        <v>80000</v>
+        <v>183000</v>
       </c>
       <c r="G64" s="3">
         <v>5</v>
       </c>
       <c r="H64" s="3">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I64" s="3">
-        <v>1088000</v>
+        <v>36600</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="K64" s="4">
-        <v>46599</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D65" s="3">
         <v>1</v>
@@ -3549,112 +3436,112 @@
         <v>0</v>
       </c>
       <c r="F65" s="3">
-        <v>25000</v>
+        <v>85000</v>
       </c>
       <c r="G65" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H65" s="3">
-        <v>5</v>
+        <v>34.76</v>
       </c>
       <c r="I65" s="3">
-        <v>1250</v>
+        <v>35496</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="K65" s="4">
-        <v>47026</v>
+        <v>47726</v>
       </c>
     </row>
     <row r="66" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="D66" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E66" s="3">
         <v>0</v>
       </c>
       <c r="F66" s="3">
-        <v>330000</v>
+        <v>57000</v>
       </c>
       <c r="G66" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I66" s="3">
-        <v>1188000</v>
+        <v>39900</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="K66" s="4">
-        <v>46538</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="D67" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="3">
         <v>0</v>
       </c>
       <c r="F67" s="3">
-        <v>50000</v>
+        <v>330000</v>
       </c>
       <c r="G67" s="3">
         <v>5</v>
       </c>
       <c r="H67" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I67" s="3">
-        <v>17500</v>
+        <v>297000</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="K67" s="4">
-        <v>46265</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="D68" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E68" s="3">
         <v>0</v>
       </c>
       <c r="F68" s="3">
-        <v>25000</v>
+        <v>12200</v>
       </c>
       <c r="G68" s="3">
         <v>0</v>
@@ -3663,374 +3550,374 @@
         <v>5</v>
       </c>
       <c r="I68" s="3">
-        <v>2500</v>
+        <v>7320</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="K68" s="4">
-        <v>47026</v>
+        <v>47021</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="D69" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="3">
         <v>0</v>
       </c>
       <c r="F69" s="3">
-        <v>38000</v>
+        <v>330000</v>
       </c>
       <c r="G69" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H69" s="3">
-        <v>2.5</v>
+        <v>40</v>
       </c>
       <c r="I69" s="3">
-        <v>1900</v>
+        <v>148500</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="K69" s="4">
-        <v>47026</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="D70" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>240000</v>
+        <v>30000</v>
       </c>
       <c r="G70" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I70" s="3">
-        <v>96000</v>
+        <v>3000</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="K70" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="D71" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="3">
         <v>0</v>
       </c>
       <c r="F71" s="3">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="G71" s="3">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I71" s="3">
-        <v>1350</v>
+        <v>2500</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="K71" s="4">
-        <v>46996</v>
+        <v>47057</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="D72" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E72" s="3">
         <v>0</v>
       </c>
       <c r="F72" s="3">
-        <v>183000</v>
+        <v>90000</v>
       </c>
       <c r="G72" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I72" s="3">
-        <v>109800</v>
+        <v>81000</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="K72" s="4">
-        <v>46538</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="73" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="D73" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E73" s="3">
         <v>0</v>
       </c>
       <c r="F73" s="3">
-        <v>66900</v>
+        <v>200000</v>
       </c>
       <c r="G73" s="3">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I73" s="3">
-        <v>170595</v>
+        <v>800000</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="K73" s="4">
-        <v>46590</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="D74" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3">
         <v>0</v>
       </c>
       <c r="F74" s="3">
-        <v>56700</v>
+        <v>90000</v>
       </c>
       <c r="G74" s="3">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="I74" s="3">
-        <v>28917</v>
+        <v>40500</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K74" s="4">
-        <v>46836</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="75" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D75" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" s="3">
         <v>0</v>
       </c>
       <c r="F75" s="3">
-        <v>262000</v>
+        <v>18000</v>
       </c>
       <c r="G75" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>16.919</v>
+        <v>7.5</v>
       </c>
       <c r="I75" s="3">
-        <v>99136</v>
+        <v>4050</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K75" s="4">
-        <v>46568</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="D76" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E76" s="3">
         <v>0</v>
       </c>
       <c r="F76" s="3">
-        <v>144000</v>
+        <v>30000</v>
       </c>
       <c r="G76" s="3">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I76" s="3">
-        <v>14400</v>
+        <v>7500</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="K76" s="4">
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="D77" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E77" s="3">
         <v>0</v>
       </c>
       <c r="F77" s="3">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="G77" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="I77" s="3">
-        <v>1600000</v>
+        <v>1500</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="K77" s="4">
-        <v>46599</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D78" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="3">
         <v>0</v>
       </c>
       <c r="F78" s="3">
-        <v>25000</v>
+        <v>11000</v>
       </c>
       <c r="G78" s="3">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I78" s="3">
-        <v>3750</v>
+        <v>440</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="K78" s="4">
-        <v>47026</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="79" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="D79" s="3">
         <v>1</v>
@@ -4051,135 +3938,135 @@
         <v>48000</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="K79" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D80" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E80" s="3">
         <v>0</v>
       </c>
       <c r="F80" s="3">
-        <v>20000</v>
+        <v>90000</v>
       </c>
       <c r="G80" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H80" s="3">
-        <v>7.5</v>
+        <v>30</v>
       </c>
       <c r="I80" s="3">
-        <v>1500</v>
+        <v>220500</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K80" s="4">
-        <v>46691</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="81" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="D81" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
       </c>
       <c r="F81" s="3">
-        <v>183000</v>
+        <v>75000</v>
       </c>
       <c r="G81" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>15</v>
+        <v>29.14</v>
       </c>
       <c r="I81" s="3">
-        <v>1134600</v>
+        <v>43710</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="K81" s="4">
-        <v>46538</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="D82" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E82" s="3">
         <v>0</v>
       </c>
       <c r="F82" s="3">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="G82" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H82" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I82" s="3">
-        <v>1920000</v>
+        <v>52500</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="K82" s="4">
-        <v>46630</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D83" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>50000</v>
+        <v>90000</v>
       </c>
       <c r="G83" s="3">
         <v>5</v>
@@ -4188,293 +4075,293 @@
         <v>30</v>
       </c>
       <c r="I83" s="3">
-        <v>35000</v>
+        <v>31500</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K83" s="4">
-        <v>46265</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="D84" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="3">
         <v>0</v>
       </c>
       <c r="F84" s="3">
-        <v>18000</v>
+        <v>19500</v>
       </c>
       <c r="G84" s="3">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I84" s="3">
-        <v>1350</v>
+        <v>1950</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="K84" s="4">
-        <v>46996</v>
+        <v>47034</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3">
+        <v>3</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3">
+        <v>315000</v>
+      </c>
+      <c r="G85" s="3">
+        <v>5</v>
+      </c>
+      <c r="H85" s="3">
+        <v>25</v>
+      </c>
+      <c r="I85" s="3">
+        <v>283500</v>
+      </c>
+      <c r="J85" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D85" s="3">
-        <v>5</v>
-      </c>
-      <c r="E85" s="3">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3">
-        <v>330000</v>
-      </c>
-      <c r="G85" s="3">
-        <v>5</v>
-      </c>
-      <c r="H85" s="3">
-        <v>40</v>
-      </c>
-      <c r="I85" s="3">
-        <v>742500</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="K85" s="4">
-        <v>46599</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>207</v>
+        <v>89</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="D86" s="3">
-        <v>183</v>
+        <v>22</v>
       </c>
       <c r="E86" s="3">
         <v>0</v>
       </c>
       <c r="F86" s="3">
-        <v>16000</v>
+        <v>125000</v>
       </c>
       <c r="G86" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H86" s="3">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="I86" s="3">
-        <v>497760</v>
+        <v>1375000</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="K86" s="4">
-        <v>46998</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>212</v>
+        <v>86</v>
       </c>
       <c r="D87" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E87" s="3">
         <v>0</v>
       </c>
       <c r="F87" s="3">
-        <v>13500</v>
+        <v>1200000</v>
       </c>
       <c r="G87" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H87" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I87" s="3">
-        <v>0</v>
+        <v>720000</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>213</v>
+        <v>87</v>
       </c>
       <c r="K87" s="4">
-        <v>46977</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D88" s="3">
+        <v>1</v>
+      </c>
+      <c r="E88" s="3">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3">
+        <v>240000</v>
+      </c>
+      <c r="G88" s="3">
+        <v>5</v>
+      </c>
+      <c r="H88" s="3">
         <v>15</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D88" s="3">
-        <v>48</v>
-      </c>
-      <c r="E88" s="3">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3">
-        <v>41732</v>
-      </c>
-      <c r="G88" s="3">
-        <v>3</v>
-      </c>
-      <c r="H88" s="3">
-        <v>0</v>
-      </c>
       <c r="I88" s="3">
-        <v>60094</v>
+        <v>48000</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K88" s="4">
-        <v>47361</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="D89" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>55858</v>
+        <v>330000</v>
       </c>
       <c r="G89" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I89" s="3">
-        <v>20109</v>
+        <v>594000</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="K89" s="4">
-        <v>47299</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>16</v>
+        <v>178</v>
       </c>
       <c r="D90" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E90" s="3">
         <v>0</v>
       </c>
       <c r="F90" s="3">
-        <v>41732</v>
+        <v>199000</v>
       </c>
       <c r="G90" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H90" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I90" s="3">
-        <v>30047</v>
+        <v>1313400</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="K90" s="4">
-        <v>47391</v>
+        <v>46965</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D91" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>58300</v>
+        <v>80000</v>
       </c>
       <c r="G91" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I91" s="3">
-        <v>6996</v>
+        <v>160000</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>220</v>
+        <v>151</v>
       </c>
       <c r="K91" s="4">
-        <v>46873</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -4482,220 +4369,220 @@
         <v>221</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>223</v>
+        <v>74</v>
       </c>
       <c r="D92" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E92" s="3">
         <v>0</v>
       </c>
       <c r="F92" s="3">
-        <v>18150</v>
+        <v>50000</v>
       </c>
       <c r="G92" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H92" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I92" s="3">
-        <v>3630</v>
+        <v>35000</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="K92" s="4">
-        <v>46843</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D93" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E93" s="3">
         <v>0</v>
       </c>
       <c r="F93" s="3">
-        <v>58300</v>
+        <v>330000</v>
       </c>
       <c r="G93" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H93" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I93" s="3">
-        <v>6996</v>
+        <v>148500</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="K93" s="4">
-        <v>46873</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>223</v>
+        <v>136</v>
       </c>
       <c r="D94" s="3">
+        <v>1</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>70000</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>10</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>18150</v>
-      </c>
-      <c r="G94" s="3">
-        <v>2</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
-        <v>3630</v>
+        <v>7000</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K94" s="4">
-        <v>46873</v>
+        <v>47057</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>16</v>
+        <v>197</v>
       </c>
       <c r="D95" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E95" s="3">
         <v>0</v>
       </c>
       <c r="F95" s="3">
-        <v>41732</v>
+        <v>18000</v>
       </c>
       <c r="G95" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="I95" s="3">
-        <v>50078</v>
+        <v>2700</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="K95" s="4">
-        <v>47695</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="D96" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>81081</v>
+        <v>330000</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H96" s="3">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="I96" s="3">
-        <v>58378</v>
+        <v>148500</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="K96" s="4">
-        <v>46660</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>236</v>
+        <v>115</v>
       </c>
       <c r="D97" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E97" s="3">
         <v>0</v>
       </c>
       <c r="F97" s="3">
-        <v>30800</v>
+        <v>105000</v>
       </c>
       <c r="G97" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I97" s="3">
-        <v>7392</v>
+        <v>47250</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
       <c r="K97" s="4">
-        <v>46561</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>239</v>
+        <v>108</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>240</v>
+        <v>109</v>
       </c>
       <c r="D98" s="3">
         <v>1</v>
@@ -4704,33 +4591,33 @@
         <v>0</v>
       </c>
       <c r="F98" s="3">
-        <v>57000</v>
+        <v>25000</v>
       </c>
       <c r="G98" s="3">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I98" s="3">
-        <v>14250</v>
+        <v>1250</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>241</v>
+        <v>191</v>
       </c>
       <c r="K98" s="4">
-        <v>46660</v>
+        <v>47057</v>
       </c>
     </row>
     <row r="99" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="D99" s="3">
         <v>2</v>
@@ -4739,404 +4626,404 @@
         <v>0</v>
       </c>
       <c r="F99" s="3">
-        <v>450000</v>
+        <v>90000</v>
       </c>
       <c r="G99" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I99" s="3">
-        <v>189000</v>
+        <v>18000</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>243</v>
+        <v>117</v>
       </c>
       <c r="K99" s="4">
-        <v>46568</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="100" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D100" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="G100" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I100" s="3">
-        <v>52500</v>
+        <v>5000</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>245</v>
+        <v>143</v>
       </c>
       <c r="K100" s="4">
-        <v>46418</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="D101" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>330000</v>
+        <v>200000</v>
       </c>
       <c r="G101" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H101" s="3">
         <v>40</v>
       </c>
       <c r="I101" s="3">
-        <v>148500</v>
+        <v>240000</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="K101" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="D102" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>320000</v>
+        <v>90000</v>
       </c>
       <c r="G102" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I102" s="3">
-        <v>560000</v>
+        <v>72000</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="K102" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="103" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="D103" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E103" s="3">
         <v>0</v>
       </c>
       <c r="F103" s="3">
-        <v>240000</v>
+        <v>13500</v>
       </c>
       <c r="G103" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H103" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I103" s="3">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="K103" s="4">
-        <v>46599</v>
+        <v>46935</v>
       </c>
     </row>
     <row r="104" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="D104" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E104" s="3">
         <v>0</v>
       </c>
       <c r="F104" s="3">
-        <v>195000</v>
+        <v>126126</v>
       </c>
       <c r="G104" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H104" s="3">
-        <v>15</v>
+        <v>3.57</v>
       </c>
       <c r="I104" s="3">
-        <v>195000</v>
+        <v>9005</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="K104" s="4">
-        <v>46630</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="105" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="D105" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105" s="3">
         <v>0</v>
       </c>
       <c r="F105" s="3">
-        <v>50000</v>
+        <v>81081</v>
       </c>
       <c r="G105" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H105" s="3">
-        <v>30</v>
+        <v>3.33</v>
       </c>
       <c r="I105" s="3">
-        <v>35000</v>
+        <v>8100</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="K105" s="4">
-        <v>46418</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="106" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>256</v>
+        <v>15</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
       <c r="D106" s="3">
+        <v>10</v>
+      </c>
+      <c r="E106" s="3">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3">
+        <v>18150</v>
+      </c>
+      <c r="G106" s="3">
         <v>2</v>
       </c>
-      <c r="E106" s="3">
-        <v>0</v>
-      </c>
-      <c r="F106" s="3">
-        <v>19500</v>
-      </c>
-      <c r="G106" s="3">
-        <v>0</v>
-      </c>
       <c r="H106" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I106" s="3">
-        <v>1950</v>
+        <v>3630</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>258</v>
+        <v>17</v>
       </c>
       <c r="K106" s="4">
-        <v>47012</v>
+        <v>46904</v>
       </c>
     </row>
     <row r="107" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D107" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E107" s="3">
         <v>0</v>
       </c>
       <c r="F107" s="3">
-        <v>320000</v>
+        <v>58300</v>
       </c>
       <c r="G107" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H107" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I107" s="3">
-        <v>80000</v>
+        <v>27984</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="K107" s="4">
-        <v>46599</v>
+        <v>46904</v>
       </c>
     </row>
     <row r="108" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="D108" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E108" s="3">
         <v>0</v>
       </c>
       <c r="F108" s="3">
-        <v>240000</v>
+        <v>18150</v>
       </c>
       <c r="G108" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H108" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I108" s="3">
-        <v>240000</v>
+        <v>3993</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="K108" s="4">
-        <v>46599</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="D109" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E109" s="3">
         <v>0</v>
       </c>
       <c r="F109" s="3">
-        <v>30000</v>
+        <v>18150</v>
       </c>
       <c r="G109" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H109" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I109" s="3">
-        <v>1500</v>
+        <v>3267</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="K109" s="4">
-        <v>46568</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="110" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>263</v>
+        <v>132</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>264</v>
+        <v>133</v>
       </c>
       <c r="D110" s="3">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E110" s="3">
         <v>0</v>
       </c>
       <c r="F110" s="3">
-        <v>33000</v>
+        <v>30000</v>
       </c>
       <c r="G110" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I110" s="3">
-        <v>51150</v>
+        <v>18000</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="K110" s="4">
         <v>46660</v>
@@ -5144,34 +5031,34 @@
     </row>
     <row r="111" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>266</v>
+        <v>108</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>267</v>
+        <v>109</v>
       </c>
       <c r="D111" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E111" s="3">
         <v>0</v>
       </c>
       <c r="F111" s="3">
-        <v>24200</v>
+        <v>25000</v>
       </c>
       <c r="G111" s="3">
         <v>0</v>
       </c>
       <c r="H111" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I111" s="3">
-        <v>0</v>
+        <v>13750</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="K111" s="4">
         <v>47026</v>
@@ -5179,293 +5066,293 @@
     </row>
     <row r="112" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>269</v>
+        <v>123</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>270</v>
+        <v>124</v>
       </c>
       <c r="D112" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E112" s="3">
         <v>0</v>
       </c>
       <c r="F112" s="3">
-        <v>25000</v>
+        <v>38000</v>
       </c>
       <c r="G112" s="3">
         <v>0</v>
       </c>
       <c r="H112" s="3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I112" s="3">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="K112" s="4">
-        <v>47133</v>
+        <v>47057</v>
       </c>
     </row>
     <row r="113" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D113" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E113" s="3">
         <v>0</v>
       </c>
       <c r="F113" s="3">
-        <v>140000</v>
+        <v>25000</v>
       </c>
       <c r="G113" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I113" s="3">
-        <v>21000</v>
+        <v>2500</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="K113" s="4">
-        <v>46752</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="114" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>275</v>
+        <v>126</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>276</v>
+        <v>127</v>
       </c>
       <c r="D114" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E114" s="3">
         <v>0</v>
       </c>
       <c r="F114" s="3">
-        <v>380000</v>
+        <v>12200</v>
       </c>
       <c r="G114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I114" s="3">
-        <v>247000</v>
+        <v>12200</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>277</v>
+        <v>128</v>
       </c>
       <c r="K114" s="4">
-        <v>46783</v>
+        <v>47021</v>
       </c>
     </row>
     <row r="115" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>278</v>
+        <v>135</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="D115" s="3">
+        <v>4</v>
+      </c>
+      <c r="E115" s="3">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3">
+        <v>70000</v>
+      </c>
+      <c r="G115" s="3">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3">
         <v>10</v>
       </c>
-      <c r="E115" s="3">
-        <v>0</v>
-      </c>
-      <c r="F115" s="3">
-        <v>230000</v>
-      </c>
-      <c r="G115" s="3">
-        <v>1</v>
-      </c>
-      <c r="H115" s="3">
-        <v>4</v>
-      </c>
       <c r="I115" s="3">
-        <v>115000</v>
+        <v>28000</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="K115" s="4">
-        <v>46721</v>
+        <v>47028</v>
       </c>
     </row>
     <row r="116" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="D116" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E116" s="3">
         <v>0</v>
       </c>
       <c r="F116" s="3">
-        <v>18150</v>
+        <v>18000</v>
       </c>
       <c r="G116" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H116" s="3">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I116" s="3">
-        <v>2904</v>
+        <v>2700</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="K116" s="4">
-        <v>46873</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="117" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>223</v>
+        <v>139</v>
       </c>
       <c r="D117" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="E117" s="3">
         <v>0</v>
       </c>
       <c r="F117" s="3">
-        <v>18150</v>
+        <v>200000</v>
       </c>
       <c r="G117" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H117" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I117" s="3">
-        <v>726</v>
+        <v>3360000</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>283</v>
+        <v>140</v>
       </c>
       <c r="K117" s="4">
-        <v>46934</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="118" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="D118" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E118" s="3">
         <v>0</v>
       </c>
       <c r="F118" s="3">
-        <v>18150</v>
+        <v>122000</v>
       </c>
       <c r="G118" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H118" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I118" s="3">
-        <v>3630</v>
+        <v>219600</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="K118" s="4">
-        <v>46934</v>
+        <v>46965</v>
       </c>
     </row>
     <row r="119" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>223</v>
+        <v>74</v>
       </c>
       <c r="D119" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E119" s="3">
         <v>0</v>
       </c>
       <c r="F119" s="3">
-        <v>18150</v>
+        <v>50000</v>
       </c>
       <c r="G119" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H119" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I119" s="3">
-        <v>3630</v>
+        <v>17500</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="K119" s="4">
-        <v>46934</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="120" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>231</v>
+        <v>89</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="D120" s="3">
         <v>24</v>
@@ -5474,138 +5361,138 @@
         <v>0</v>
       </c>
       <c r="F120" s="3">
-        <v>81081</v>
+        <v>125000</v>
       </c>
       <c r="G120" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H120" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="I120" s="3">
-        <v>58378</v>
+        <v>1500000</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="K120" s="4">
-        <v>46691</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="121" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="D121" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E121" s="3">
         <v>0</v>
       </c>
       <c r="F121" s="3">
-        <v>72879</v>
+        <v>330000</v>
       </c>
       <c r="G121" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H121" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="I121" s="3">
-        <v>26236</v>
+        <v>1188000</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="K121" s="4">
-        <v>47726</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="122" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>239</v>
+        <v>66</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>240</v>
+        <v>67</v>
       </c>
       <c r="D122" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E122" s="3">
         <v>0</v>
       </c>
       <c r="F122" s="3">
-        <v>57000</v>
+        <v>58300</v>
       </c>
       <c r="G122" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H122" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I122" s="3">
-        <v>14250</v>
+        <v>6996</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K122" s="4">
-        <v>46660</v>
+        <v>46904</v>
       </c>
     </row>
     <row r="123" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="3">
+        <v>18</v>
+      </c>
+      <c r="E123" s="3">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3">
+        <v>30000</v>
+      </c>
+      <c r="G123" s="3">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3">
+        <v>5</v>
+      </c>
+      <c r="I123" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J123" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D123" s="3">
-        <v>2</v>
-      </c>
-      <c r="E123" s="3">
-        <v>0</v>
-      </c>
-      <c r="F123" s="3">
-        <v>50000</v>
-      </c>
-      <c r="G123" s="3">
-        <v>5</v>
-      </c>
-      <c r="H123" s="3">
-        <v>30</v>
-      </c>
-      <c r="I123" s="3">
-        <v>35000</v>
-      </c>
-      <c r="J123" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="K123" s="4">
-        <v>46418</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="124" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D124" s="3">
         <v>1</v>
@@ -5614,147 +5501,147 @@
         <v>0</v>
       </c>
       <c r="F124" s="3">
-        <v>90000</v>
+        <v>30000</v>
       </c>
       <c r="G124" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H124" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I124" s="3">
-        <v>31500</v>
+        <v>1500</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K124" s="4">
-        <v>46418</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="D125" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E125" s="3">
         <v>0</v>
       </c>
       <c r="F125" s="3">
-        <v>450000</v>
+        <v>85586</v>
       </c>
       <c r="G125" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H125" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I125" s="3">
-        <v>189000</v>
+        <v>41081</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="K125" s="4">
-        <v>46568</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="126" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>16</v>
+        <v>178</v>
       </c>
       <c r="D126" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E126" s="3">
         <v>0</v>
       </c>
       <c r="F126" s="3">
-        <v>41732</v>
+        <v>199000</v>
       </c>
       <c r="G126" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H126" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I126" s="3">
-        <v>10016</v>
+        <v>547250</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>293</v>
+        <v>179</v>
       </c>
       <c r="K126" s="4">
-        <v>47726</v>
+        <v>46965</v>
       </c>
     </row>
     <row r="127" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D127" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E127" s="3">
         <v>0</v>
       </c>
       <c r="F127" s="3">
-        <v>41732</v>
+        <v>58300</v>
       </c>
       <c r="G127" s="3">
         <v>2</v>
       </c>
       <c r="H127" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" s="3">
-        <v>20031</v>
+        <v>6996</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="K127" s="4">
-        <v>47756</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>235</v>
+        <v>15</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="D128" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E128" s="3">
         <v>0</v>
       </c>
       <c r="F128" s="3">
-        <v>30800</v>
+        <v>18150</v>
       </c>
       <c r="G128" s="3">
         <v>2</v>
@@ -5763,150 +5650,150 @@
         <v>0</v>
       </c>
       <c r="I128" s="3">
-        <v>7392</v>
+        <v>3630</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="K128" s="4">
-        <v>46561</v>
+        <v>46843</v>
       </c>
     </row>
     <row r="129" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D129" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E129" s="3">
         <v>0</v>
       </c>
       <c r="F129" s="3">
-        <v>320000</v>
+        <v>58300</v>
       </c>
       <c r="G129" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H129" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I129" s="3">
-        <v>560000</v>
+        <v>6996</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="K129" s="4">
-        <v>46599</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="130" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="D130" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E130" s="3">
         <v>0</v>
       </c>
       <c r="F130" s="3">
-        <v>125000</v>
+        <v>81081</v>
       </c>
       <c r="G130" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H130" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I130" s="3">
-        <v>500000</v>
+        <v>58378</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="K130" s="4">
-        <v>46599</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="131" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D131" s="3">
+        <v>10</v>
+      </c>
+      <c r="E131" s="3">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3">
+        <v>18150</v>
+      </c>
+      <c r="G131" s="3">
         <v>2</v>
       </c>
-      <c r="E131" s="3">
-        <v>0</v>
-      </c>
-      <c r="F131" s="3">
-        <v>320000</v>
-      </c>
-      <c r="G131" s="3">
-        <v>5</v>
-      </c>
       <c r="H131" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I131" s="3">
-        <v>160000</v>
+        <v>3630</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="K131" s="4">
-        <v>46599</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="132" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>254</v>
+        <v>64</v>
       </c>
       <c r="D132" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E132" s="3">
         <v>0</v>
       </c>
       <c r="F132" s="3">
-        <v>195000</v>
+        <v>30800</v>
       </c>
       <c r="G132" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H132" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I132" s="3">
-        <v>195000</v>
+        <v>7392</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="K132" s="4">
         <v>46630</v>
@@ -5914,267 +5801,267 @@
     </row>
     <row r="133" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>155</v>
+        <v>16</v>
       </c>
       <c r="D133" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E133" s="3">
         <v>0</v>
       </c>
       <c r="F133" s="3">
-        <v>50000</v>
+        <v>18150</v>
       </c>
       <c r="G133" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H133" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I133" s="3">
-        <v>70000</v>
+        <v>3630</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="K133" s="4">
-        <v>46418</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="134" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>298</v>
+        <v>66</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>299</v>
+        <v>67</v>
       </c>
       <c r="D134" s="3">
+        <v>6</v>
+      </c>
+      <c r="E134" s="3">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3">
+        <v>58300</v>
+      </c>
+      <c r="G134" s="3">
         <v>2</v>
       </c>
-      <c r="E134" s="3">
-        <v>0</v>
-      </c>
-      <c r="F134" s="3">
-        <v>125000</v>
-      </c>
-      <c r="G134" s="3">
-        <v>5</v>
-      </c>
       <c r="H134" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I134" s="3">
-        <v>125000</v>
+        <v>6996</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="K134" s="4">
-        <v>46599</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="135" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>256</v>
+        <v>19</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="D135" s="3">
+        <v>12</v>
+      </c>
+      <c r="E135" s="3">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3">
+        <v>55858</v>
+      </c>
+      <c r="G135" s="3">
         <v>2</v>
       </c>
-      <c r="E135" s="3">
-        <v>0</v>
-      </c>
-      <c r="F135" s="3">
-        <v>19500</v>
-      </c>
-      <c r="G135" s="3">
-        <v>0</v>
-      </c>
       <c r="H135" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I135" s="3">
-        <v>1950</v>
+        <v>33515</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="K135" s="4">
-        <v>47012</v>
+        <v>47664</v>
       </c>
     </row>
     <row r="136" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>30</v>
+        <v>237</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>31</v>
+        <v>238</v>
       </c>
       <c r="D136" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E136" s="3">
         <v>0</v>
       </c>
       <c r="F136" s="3">
-        <v>70000</v>
+        <v>81081</v>
       </c>
       <c r="G136" s="3">
         <v>0</v>
       </c>
       <c r="H136" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I136" s="3">
-        <v>7000</v>
+        <v>116757</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="K136" s="4">
-        <v>47008</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="137" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>154</v>
+        <v>288</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>155</v>
+        <v>289</v>
       </c>
       <c r="D137" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E137" s="3">
         <v>0</v>
       </c>
       <c r="F137" s="3">
-        <v>50000</v>
+        <v>78379</v>
       </c>
       <c r="G137" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H137" s="3">
-        <v>30</v>
+        <v>3.0003000000000002</v>
       </c>
       <c r="I137" s="3">
-        <v>70000</v>
+        <v>112877</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="K137" s="4">
-        <v>46418</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="138" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="D138" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E138" s="3">
         <v>0</v>
       </c>
       <c r="F138" s="3">
-        <v>160000</v>
+        <v>87388</v>
       </c>
       <c r="G138" s="3">
         <v>0</v>
       </c>
       <c r="H138" s="3">
-        <v>5</v>
+        <v>3.0019999999999998</v>
       </c>
       <c r="I138" s="3">
-        <v>96000</v>
+        <v>125923</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="K138" s="4">
-        <v>47422</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="139" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="D139" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E139" s="3">
         <v>0</v>
       </c>
       <c r="F139" s="3">
-        <v>120000</v>
+        <v>85586</v>
       </c>
       <c r="G139" s="3">
         <v>0</v>
       </c>
       <c r="H139" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I139" s="3">
-        <v>0</v>
+        <v>123244</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="K139" s="4">
-        <v>46568</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="140" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>222</v>
+        <v>66</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>223</v>
+        <v>67</v>
       </c>
       <c r="D140" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E140" s="3">
         <v>0</v>
       </c>
       <c r="F140" s="3">
-        <v>18150</v>
+        <v>58300</v>
       </c>
       <c r="G140" s="3">
         <v>2</v>
@@ -6183,33 +6070,33 @@
         <v>0</v>
       </c>
       <c r="I140" s="3">
-        <v>3630</v>
+        <v>2332</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="K140" s="4">
-        <v>46934</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="141" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>222</v>
+        <v>66</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>223</v>
+        <v>67</v>
       </c>
       <c r="D141" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E141" s="3">
         <v>0</v>
       </c>
       <c r="F141" s="3">
-        <v>18150</v>
+        <v>58300</v>
       </c>
       <c r="G141" s="3">
         <v>2</v>
@@ -6218,18 +6105,18 @@
         <v>0</v>
       </c>
       <c r="I141" s="3">
-        <v>3630</v>
+        <v>4664</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K141" s="4">
-        <v>46934</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="142" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>15</v>
@@ -6238,39 +6125,39 @@
         <v>16</v>
       </c>
       <c r="D142" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E142" s="3">
         <v>0</v>
       </c>
       <c r="F142" s="3">
-        <v>41732</v>
+        <v>18150</v>
       </c>
       <c r="G142" s="3">
         <v>2</v>
       </c>
       <c r="H142" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I142" s="3">
-        <v>6260</v>
+        <v>3630</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="K142" s="4">
-        <v>47756</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="143" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>18</v>
+        <v>301</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>19</v>
+        <v>302</v>
       </c>
       <c r="D143" s="3">
         <v>3</v>
@@ -6279,477 +6166,22 @@
         <v>0</v>
       </c>
       <c r="F143" s="3">
-        <v>55858</v>
+        <v>160000</v>
       </c>
       <c r="G143" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I143" s="3">
-        <v>8378</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="K143" s="4">
-        <v>47664</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A144" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D144" s="3">
-        <v>1</v>
-      </c>
-      <c r="E144" s="3">
-        <v>0</v>
-      </c>
-      <c r="F144" s="3">
-        <v>30000</v>
-      </c>
-      <c r="G144" s="3">
-        <v>0</v>
-      </c>
-      <c r="H144" s="3">
-        <v>5</v>
-      </c>
-      <c r="I144" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J144" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K144" s="4">
-        <v>46568</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A145" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D145" s="3">
-        <v>6</v>
-      </c>
-      <c r="E145" s="3">
-        <v>0</v>
-      </c>
-      <c r="F145" s="3">
-        <v>58300</v>
-      </c>
-      <c r="G145" s="3">
-        <v>2</v>
-      </c>
-      <c r="H145" s="3">
-        <v>0</v>
-      </c>
-      <c r="I145" s="3">
-        <v>6996</v>
-      </c>
-      <c r="J145" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="K145" s="4">
-        <v>46873</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D146" s="3">
-        <v>2</v>
-      </c>
-      <c r="E146" s="3">
-        <v>0</v>
-      </c>
-      <c r="F146" s="3">
-        <v>85000</v>
-      </c>
-      <c r="G146" s="3">
-        <v>7</v>
-      </c>
-      <c r="H146" s="3">
-        <v>34.764699999999998</v>
-      </c>
-      <c r="I146" s="3">
-        <v>71000</v>
-      </c>
-      <c r="J146" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="K146" s="4">
-        <v>47726</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A147" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D147" s="3">
-        <v>1</v>
-      </c>
-      <c r="E147" s="3">
-        <v>0</v>
-      </c>
-      <c r="F147" s="3">
-        <v>553430</v>
-      </c>
-      <c r="G147" s="3">
-        <v>2</v>
-      </c>
-      <c r="H147" s="3">
-        <v>28</v>
-      </c>
-      <c r="I147" s="3">
-        <v>166029</v>
-      </c>
-      <c r="J147" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="K147" s="4">
-        <v>46691</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A148" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D148" s="3">
-        <v>2</v>
-      </c>
-      <c r="E148" s="3">
-        <v>0</v>
-      </c>
-      <c r="F148" s="3">
-        <v>125000</v>
-      </c>
-      <c r="G148" s="3">
-        <v>5</v>
-      </c>
-      <c r="H148" s="3">
-        <v>45</v>
-      </c>
-      <c r="I148" s="3">
-        <v>125000</v>
-      </c>
-      <c r="J148" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="K148" s="4">
-        <v>46630</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A149" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D149" s="3">
-        <v>3</v>
-      </c>
-      <c r="E149" s="3">
-        <v>0</v>
-      </c>
-      <c r="F149" s="3">
-        <v>240000</v>
-      </c>
-      <c r="G149" s="3">
-        <v>5</v>
-      </c>
-      <c r="H149" s="3">
-        <v>15</v>
-      </c>
-      <c r="I149" s="3">
-        <v>144000</v>
-      </c>
-      <c r="J149" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K149" s="4">
-        <v>46599</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A150" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D150" s="3">
-        <v>31</v>
-      </c>
-      <c r="E150" s="3">
-        <v>0</v>
-      </c>
-      <c r="F150" s="3">
-        <v>125000</v>
-      </c>
-      <c r="G150" s="3">
-        <v>5</v>
-      </c>
-      <c r="H150" s="3">
-        <v>45</v>
-      </c>
-      <c r="I150" s="3">
-        <v>1937500</v>
-      </c>
-      <c r="J150" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="K150" s="4">
-        <v>46630</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A151" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D151" s="3">
-        <v>1</v>
-      </c>
-      <c r="E151" s="3">
-        <v>0</v>
-      </c>
-      <c r="F151" s="3">
-        <v>330000</v>
-      </c>
-      <c r="G151" s="3">
-        <v>5</v>
-      </c>
-      <c r="H151" s="3">
-        <v>40</v>
-      </c>
-      <c r="I151" s="3">
-        <v>148500</v>
-      </c>
-      <c r="J151" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="K151" s="4">
-        <v>46599</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A152" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D152" s="3">
-        <v>1</v>
-      </c>
-      <c r="E152" s="3">
-        <v>0</v>
-      </c>
-      <c r="F152" s="3">
-        <v>19500</v>
-      </c>
-      <c r="G152" s="3">
-        <v>0</v>
-      </c>
-      <c r="H152" s="3">
-        <v>5</v>
-      </c>
-      <c r="I152" s="3">
-        <v>975</v>
-      </c>
-      <c r="J152" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="K152" s="4">
-        <v>47012</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A153" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D153" s="3">
-        <v>1</v>
-      </c>
-      <c r="E153" s="3">
-        <v>0</v>
-      </c>
-      <c r="F153" s="3">
-        <v>450000</v>
-      </c>
-      <c r="G153" s="3">
-        <v>5</v>
-      </c>
-      <c r="H153" s="3">
-        <v>16</v>
-      </c>
-      <c r="I153" s="3">
-        <v>94500</v>
-      </c>
-      <c r="J153" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="K153" s="4">
-        <v>46568</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A154" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D154" s="3">
-        <v>2</v>
-      </c>
-      <c r="E154" s="3">
-        <v>0</v>
-      </c>
-      <c r="F154" s="3">
-        <v>160000</v>
-      </c>
-      <c r="G154" s="3">
-        <v>0</v>
-      </c>
-      <c r="H154" s="3">
-        <v>0</v>
-      </c>
-      <c r="I154" s="3">
-        <v>0</v>
-      </c>
-      <c r="J154" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K154" s="4">
         <v>47422</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A155" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D155" s="3">
-        <v>7</v>
-      </c>
-      <c r="E155" s="3">
-        <v>0</v>
-      </c>
-      <c r="F155" s="3">
-        <v>13500</v>
-      </c>
-      <c r="G155" s="3">
-        <v>0</v>
-      </c>
-      <c r="H155" s="3">
-        <v>0</v>
-      </c>
-      <c r="I155" s="3">
-        <v>0</v>
-      </c>
-      <c r="J155" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K155" s="4">
-        <v>46977</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A156" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D156" s="3">
-        <v>15</v>
-      </c>
-      <c r="E156" s="3">
-        <v>0</v>
-      </c>
-      <c r="F156" s="3">
-        <v>13500</v>
-      </c>
-      <c r="G156" s="3">
-        <v>0</v>
-      </c>
-      <c r="H156" s="3">
-        <v>0</v>
-      </c>
-      <c r="I156" s="3">
-        <v>0</v>
-      </c>
-      <c r="J156" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K156" s="4">
-        <v>46977</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/invoice-product-missing.xlsx
+++ b/uploads/invoice-product-missing.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251202\fix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251215\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB3BBA7-ED16-4F42-843F-99ABB3CA75D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Invoice Product" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="264">
   <si>
     <t>nomor_invoice</t>
   </si>
@@ -64,7 +63,115 @@
     <t>ex: 2025/08/01</t>
   </si>
   <si>
-    <t>02ASB25020598</t>
+    <t>04ASB25011832</t>
+  </si>
+  <si>
+    <t>016809</t>
+  </si>
+  <si>
+    <t>ZYMUNO 200 ML</t>
+  </si>
+  <si>
+    <t>L110725012</t>
+  </si>
+  <si>
+    <t>07ASB25037678</t>
+  </si>
+  <si>
+    <t>017207</t>
+  </si>
+  <si>
+    <t>MENTHOLATUM AD LOTION</t>
+  </si>
+  <si>
+    <t>PDFV01T</t>
+  </si>
+  <si>
+    <t>07ASB25039702</t>
+  </si>
+  <si>
+    <t>013010</t>
+  </si>
+  <si>
+    <t>NUTRIGARAM 300 GR</t>
+  </si>
+  <si>
+    <t>300916</t>
+  </si>
+  <si>
+    <t>301001</t>
+  </si>
+  <si>
+    <t>07ASB25039766</t>
+  </si>
+  <si>
+    <t>013008</t>
+  </si>
+  <si>
+    <t>NUTRISALIN 200 GR</t>
+  </si>
+  <si>
+    <t>301028</t>
+  </si>
+  <si>
+    <t>07ASB25039840</t>
+  </si>
+  <si>
+    <t>07ASB25039862</t>
+  </si>
+  <si>
+    <t>016806</t>
+  </si>
+  <si>
+    <t>ETAWALIN 200 GR</t>
+  </si>
+  <si>
+    <t>P111025098</t>
+  </si>
+  <si>
+    <t>017278</t>
+  </si>
+  <si>
+    <t>ETAWALIN SACHET</t>
+  </si>
+  <si>
+    <t>P210225004</t>
+  </si>
+  <si>
+    <t>016998</t>
+  </si>
+  <si>
+    <t>ETAWAKU PLATINUM 200 GR</t>
+  </si>
+  <si>
+    <t>111025003B</t>
+  </si>
+  <si>
+    <t>017290</t>
+  </si>
+  <si>
+    <t>ETAWALIN DELICATE 200 GR</t>
+  </si>
+  <si>
+    <t>P311025003</t>
+  </si>
+  <si>
+    <t>P111025009</t>
+  </si>
+  <si>
+    <t>P210225057</t>
+  </si>
+  <si>
+    <t>P311125001</t>
+  </si>
+  <si>
+    <t>P111025149</t>
+  </si>
+  <si>
+    <t>P311125002</t>
+  </si>
+  <si>
+    <t>07ASB25039974</t>
   </si>
   <si>
     <t>014283</t>
@@ -73,748 +180,586 @@
     <t>Y - RINS 2X12 ML ( MO )</t>
   </si>
   <si>
-    <t>2EE124</t>
-  </si>
-  <si>
-    <t>07ASB25031653</t>
-  </si>
-  <si>
-    <t>013010</t>
-  </si>
-  <si>
-    <t>NUTRIGARAM 300 GR</t>
+    <t>2EH085</t>
+  </si>
+  <si>
+    <t>07ASB25039976</t>
+  </si>
+  <si>
+    <t>07ASB25039977</t>
+  </si>
+  <si>
+    <t>014962</t>
+  </si>
+  <si>
+    <t>Y - RINS 10 X 12 ML ( MO )</t>
+  </si>
+  <si>
+    <t>2EF124</t>
+  </si>
+  <si>
+    <t>07ASB25039978</t>
+  </si>
+  <si>
+    <t>07ASB25040010</t>
+  </si>
+  <si>
+    <t>014961</t>
+  </si>
+  <si>
+    <t>CALLUSOL ( MO )</t>
+  </si>
+  <si>
+    <t>1EI046</t>
+  </si>
+  <si>
+    <t>07ASB25040025</t>
+  </si>
+  <si>
+    <t>07ASB25040026</t>
+  </si>
+  <si>
+    <t>07ASB25040033</t>
+  </si>
+  <si>
+    <t>08ASB25017561</t>
+  </si>
+  <si>
+    <t>300624</t>
   </si>
   <si>
     <t>300623</t>
   </si>
   <si>
-    <t>07ASB25037346</t>
-  </si>
-  <si>
-    <t>013008</t>
-  </si>
-  <si>
-    <t>NUTRISALIN 200 GR</t>
+    <t>08ASB25019373</t>
+  </si>
+  <si>
+    <t>2RL057</t>
+  </si>
+  <si>
+    <t>08ASB25019665</t>
+  </si>
+  <si>
+    <t>2EF096</t>
+  </si>
+  <si>
+    <t>08ASB25019737</t>
+  </si>
+  <si>
+    <t>08ASB25019845</t>
+  </si>
+  <si>
+    <t>P111025147</t>
+  </si>
+  <si>
+    <t>08ASB25019889</t>
+  </si>
+  <si>
+    <t>300821</t>
   </si>
   <si>
     <t>300904</t>
   </si>
   <si>
+    <t>08ASB25019908</t>
+  </si>
+  <si>
+    <t>09ASB25024418</t>
+  </si>
+  <si>
+    <t>1EH139</t>
+  </si>
+  <si>
+    <t>11ASB25036258</t>
+  </si>
+  <si>
+    <t>12ASB25024851</t>
+  </si>
+  <si>
+    <t>2EA142</t>
+  </si>
+  <si>
+    <t>16ASB25023355</t>
+  </si>
+  <si>
+    <t>2EF095</t>
+  </si>
+  <si>
+    <t>16ASB25023788</t>
+  </si>
+  <si>
+    <t>1EH175</t>
+  </si>
+  <si>
+    <t>18BSB25000217</t>
+  </si>
+  <si>
+    <t>015150</t>
+  </si>
+  <si>
+    <t>6060 ACEMED CONNECTING CABLE</t>
+  </si>
+  <si>
+    <t>20230703</t>
+  </si>
+  <si>
+    <t>015151</t>
+  </si>
+  <si>
+    <t>6070 ACEMED CONNECTING CABLE</t>
+  </si>
+  <si>
+    <t>20240228</t>
+  </si>
+  <si>
+    <t>25ASB25017112</t>
+  </si>
+  <si>
+    <t>015442</t>
+  </si>
+  <si>
+    <t>NEO HP PRO.</t>
+  </si>
+  <si>
+    <t>08413011</t>
+  </si>
+  <si>
+    <t>25ASB25020055</t>
+  </si>
+  <si>
+    <t>1EH135</t>
+  </si>
+  <si>
+    <t>25ASB25020312</t>
+  </si>
+  <si>
+    <t>017667</t>
+  </si>
+  <si>
+    <t>DOTAREM 10 ML.</t>
+  </si>
+  <si>
+    <t>25GD0460</t>
+  </si>
+  <si>
+    <t>016476</t>
+  </si>
+  <si>
+    <t>GLICLAZIDE MR</t>
+  </si>
+  <si>
+    <t>1EI158</t>
+  </si>
+  <si>
+    <t>017431</t>
+  </si>
+  <si>
+    <t>IBUPROFEN 200</t>
+  </si>
+  <si>
+    <t>A 08502 JB</t>
+  </si>
+  <si>
+    <t>25ASB25020313</t>
+  </si>
+  <si>
+    <t>006773</t>
+  </si>
+  <si>
+    <t>FARGOXIN INJ</t>
+  </si>
+  <si>
+    <t>3EF043</t>
+  </si>
+  <si>
+    <t>25ASB25020314</t>
+  </si>
+  <si>
+    <t>014441</t>
+  </si>
+  <si>
+    <t>INVICLOT ( 5 VIAL )</t>
+  </si>
+  <si>
+    <t>3EI069</t>
+  </si>
+  <si>
+    <t>25ASB25020315</t>
+  </si>
+  <si>
+    <t>000652</t>
+  </si>
+  <si>
+    <t>ISOSORBIDE DINITRATE 5 MG</t>
+  </si>
+  <si>
+    <t>A 02313 IC</t>
+  </si>
+  <si>
+    <t>004416</t>
+  </si>
+  <si>
+    <t>SALBUTAMOL 2 MG</t>
+  </si>
+  <si>
+    <t>A 08238 HC</t>
+  </si>
+  <si>
+    <t>25ASB25020440</t>
+  </si>
+  <si>
+    <t>P111025096</t>
+  </si>
+  <si>
+    <t>25ASB25020493</t>
+  </si>
+  <si>
+    <t>300807</t>
+  </si>
+  <si>
+    <t>25ASB25020506</t>
+  </si>
+  <si>
+    <t>P211124008</t>
+  </si>
+  <si>
+    <t>P210225056</t>
+  </si>
+  <si>
+    <t>25ASB25020517</t>
+  </si>
+  <si>
     <t>013009</t>
   </si>
   <si>
     <t>NUTRISALIN 400 GR</t>
   </si>
   <si>
-    <t>301013</t>
+    <t>300820</t>
+  </si>
+  <si>
+    <t>26ASB25020250</t>
+  </si>
+  <si>
+    <t>2ED043</t>
+  </si>
+  <si>
+    <t>26ASB25020251</t>
+  </si>
+  <si>
+    <t>2EC061</t>
+  </si>
+  <si>
+    <t>26ASB25026652</t>
+  </si>
+  <si>
+    <t>015400</t>
+  </si>
+  <si>
+    <t>HL SHIROJYUN ULT WHITE FW 50GR</t>
+  </si>
+  <si>
+    <t>PHTK120</t>
+  </si>
+  <si>
+    <t>015401</t>
+  </si>
+  <si>
+    <t>HL SHIROJYUN ULT WHITE FW 100GR</t>
+  </si>
+  <si>
+    <t>PHTM125</t>
+  </si>
+  <si>
+    <t>015391</t>
+  </si>
+  <si>
+    <t>HL GOKUJYUN ULT MOIST FW 50GR</t>
+  </si>
+  <si>
+    <t>PHTI111</t>
+  </si>
+  <si>
+    <t>015392</t>
+  </si>
+  <si>
+    <t>HL GOKUJYUN ULT MOIST FW 100GR</t>
+  </si>
+  <si>
+    <t>PHTJ175</t>
+  </si>
+  <si>
+    <t>009921</t>
+  </si>
+  <si>
+    <t>SHAMPO SELSUN BLUE 60ML</t>
+  </si>
+  <si>
+    <t>PIIN010</t>
+  </si>
+  <si>
+    <t>009922</t>
+  </si>
+  <si>
+    <t>SHAMPO SELSUN BLUE 120ML</t>
+  </si>
+  <si>
+    <t>PIIP022</t>
+  </si>
+  <si>
+    <t>009927</t>
+  </si>
+  <si>
+    <t>SHAMPO S.YELLOW DOUBLEIMPACT 50ML</t>
+  </si>
+  <si>
+    <t>PIOL014</t>
+  </si>
+  <si>
+    <t>009928</t>
+  </si>
+  <si>
+    <t>SHAMPO S.YELLOW DOUBLEIMPACT 100ML</t>
+  </si>
+  <si>
+    <t>PHOM039</t>
+  </si>
+  <si>
+    <t>PITM126</t>
+  </si>
+  <si>
+    <t>PITI134</t>
+  </si>
+  <si>
+    <t>PITJ201</t>
+  </si>
+  <si>
+    <t>PIIN011</t>
+  </si>
+  <si>
+    <t>PJOL017</t>
+  </si>
+  <si>
+    <t>PIOM042</t>
+  </si>
+  <si>
+    <t>26ASB25028423</t>
+  </si>
+  <si>
+    <t>P311224005</t>
+  </si>
+  <si>
+    <t>016999</t>
+  </si>
+  <si>
+    <t>WEIGHT HERBA 200 GR</t>
+  </si>
+  <si>
+    <t>P0080725A069</t>
+  </si>
+  <si>
+    <t>26ASB25028424</t>
+  </si>
+  <si>
+    <t>300909</t>
+  </si>
+  <si>
+    <t>26ASB25028425</t>
+  </si>
+  <si>
+    <t>26ASB25028475</t>
+  </si>
+  <si>
+    <t>2ED091</t>
+  </si>
+  <si>
+    <t>26ASB25028617</t>
+  </si>
+  <si>
+    <t>017647</t>
+  </si>
+  <si>
+    <t>VITAMEAL</t>
+  </si>
+  <si>
+    <t>VM0925181</t>
+  </si>
+  <si>
+    <t>017648</t>
+  </si>
+  <si>
+    <t>VITAMEAL LESS SUGAR</t>
+  </si>
+  <si>
+    <t>VG0925029</t>
+  </si>
+  <si>
+    <t>017661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETAWALIN SEREAL </t>
+  </si>
+  <si>
+    <t>P31102502ER</t>
+  </si>
+  <si>
+    <t>26ASB25028735</t>
+  </si>
+  <si>
+    <t>26ASB25028736</t>
+  </si>
+  <si>
+    <t>1EE150</t>
+  </si>
+  <si>
+    <t>26ASB25028737</t>
+  </si>
+  <si>
+    <t>2EE039</t>
+  </si>
+  <si>
+    <t>26ASB25029099</t>
+  </si>
+  <si>
+    <t>P111025142</t>
+  </si>
+  <si>
+    <t>26ASB25029100</t>
+  </si>
+  <si>
+    <t>26ASB25029101</t>
+  </si>
+  <si>
+    <t>281203</t>
+  </si>
+  <si>
+    <t>281208</t>
+  </si>
+  <si>
+    <t>26ASB25029102</t>
+  </si>
+  <si>
+    <t>280304</t>
+  </si>
+  <si>
+    <t>26ASB25029103</t>
+  </si>
+  <si>
+    <t>280911</t>
+  </si>
+  <si>
+    <t>300811</t>
   </si>
   <si>
     <t>301011</t>
   </si>
   <si>
-    <t>07ASB25037663</t>
-  </si>
-  <si>
-    <t>012963</t>
-  </si>
-  <si>
-    <t>RUPAFIN</t>
-  </si>
-  <si>
-    <t>A001</t>
-  </si>
-  <si>
-    <t>07ASB25037742</t>
-  </si>
-  <si>
-    <t>000026</t>
-  </si>
-  <si>
-    <t>ALKOHOL 70%</t>
-  </si>
-  <si>
-    <t>J25001P</t>
-  </si>
-  <si>
-    <t>07ASB25037908</t>
-  </si>
-  <si>
-    <t>015220</t>
-  </si>
-  <si>
-    <t>ACNES STARTER PACK</t>
-  </si>
-  <si>
-    <t>PGND003</t>
-  </si>
-  <si>
-    <t>015395</t>
-  </si>
-  <si>
-    <t>HL GOKUJYUN ULT MOIST MILK 100ML</t>
-  </si>
-  <si>
-    <t>PJQT08T</t>
-  </si>
-  <si>
-    <t>015392</t>
-  </si>
-  <si>
-    <t>HL GOKUJYUN ULT MOIST FW 100GR</t>
-  </si>
-  <si>
-    <t>PITJ201</t>
-  </si>
-  <si>
-    <t>07ASB25038078</t>
-  </si>
-  <si>
-    <t>000629</t>
-  </si>
-  <si>
-    <t>INPEPSA SUSPENSI</t>
-  </si>
-  <si>
-    <t>1EG203</t>
-  </si>
-  <si>
-    <t>013660</t>
-  </si>
-  <si>
-    <t>DUOXAL</t>
-  </si>
-  <si>
-    <t>X624</t>
-  </si>
-  <si>
-    <t>000689</t>
-  </si>
-  <si>
-    <t>LACTULAX SYRUP 120</t>
-  </si>
-  <si>
-    <t>J25003A</t>
-  </si>
-  <si>
-    <t>07ASB25038091</t>
-  </si>
-  <si>
-    <t>003482</t>
-  </si>
-  <si>
-    <t>BACTODERM CREAM</t>
-  </si>
-  <si>
-    <t>G25016G</t>
-  </si>
-  <si>
-    <t>07ASB25038512</t>
-  </si>
-  <si>
-    <t>014961</t>
-  </si>
-  <si>
-    <t>CALLUSOL ( MO )</t>
-  </si>
-  <si>
-    <t>1EH134</t>
-  </si>
-  <si>
-    <t>014962</t>
-  </si>
-  <si>
-    <t>Y - RINS 10 X 12 ML ( MO )</t>
-  </si>
-  <si>
-    <t>2EF123</t>
-  </si>
-  <si>
-    <t>2EH085</t>
-  </si>
-  <si>
-    <t>08ASB25017561</t>
-  </si>
-  <si>
-    <t>300624</t>
-  </si>
-  <si>
-    <t>08ASB25018184</t>
-  </si>
-  <si>
-    <t>000449</t>
-  </si>
-  <si>
-    <t>FARBION-5000 INJEKSI</t>
-  </si>
-  <si>
-    <t>3EG120</t>
-  </si>
-  <si>
-    <t>08ASB25018185</t>
-  </si>
-  <si>
-    <t>014714</t>
-  </si>
-  <si>
-    <t>PROFERRO</t>
-  </si>
-  <si>
-    <t>1EG235</t>
-  </si>
-  <si>
-    <t>08ASB25018186</t>
-  </si>
-  <si>
-    <t>014441</t>
-  </si>
-  <si>
-    <t>INVICLOT ( 5 VIAL )</t>
-  </si>
-  <si>
-    <t>3EG140</t>
-  </si>
-  <si>
-    <t>08ASB25018187</t>
-  </si>
-  <si>
-    <t>013453</t>
-  </si>
-  <si>
-    <t>METACOSFAR 100</t>
-  </si>
-  <si>
-    <t>3EG009</t>
-  </si>
-  <si>
-    <t>08ASB25018188</t>
-  </si>
-  <si>
-    <t>009216</t>
-  </si>
-  <si>
-    <t>FARMADOL INFUS</t>
-  </si>
-  <si>
-    <t>3EH063</t>
-  </si>
-  <si>
-    <t>08ASB25018191</t>
-  </si>
-  <si>
-    <t>013783</t>
-  </si>
-  <si>
-    <t>CALGAE</t>
-  </si>
-  <si>
-    <t>1EF003</t>
-  </si>
-  <si>
-    <t>010441</t>
-  </si>
-  <si>
-    <t>MONECTO 20 - TAB</t>
-  </si>
-  <si>
-    <t>1EG134</t>
-  </si>
-  <si>
-    <t>08ASB25018192</t>
-  </si>
-  <si>
-    <t>08ASB25018193</t>
-  </si>
-  <si>
-    <t>015618</t>
-  </si>
-  <si>
-    <t>CALITOZ</t>
-  </si>
-  <si>
-    <t>1EI146</t>
-  </si>
-  <si>
-    <t>004908</t>
-  </si>
-  <si>
-    <t>OBH IKA 200 ML</t>
-  </si>
-  <si>
-    <t>J25010A</t>
-  </si>
-  <si>
-    <t>08ASB25018195</t>
-  </si>
-  <si>
-    <t>000513</t>
-  </si>
-  <si>
-    <t>FUROSEMIDE 40 MG</t>
-  </si>
-  <si>
-    <t>A 00496 IC</t>
-  </si>
-  <si>
-    <t>016476</t>
-  </si>
-  <si>
-    <t>GLICLAZIDE MR</t>
-  </si>
-  <si>
-    <t>1EI102</t>
-  </si>
-  <si>
-    <t>015731</t>
-  </si>
-  <si>
-    <t>FEBUXOSTAT 40</t>
-  </si>
-  <si>
-    <t>1EH148</t>
-  </si>
-  <si>
-    <t>1EI099</t>
-  </si>
-  <si>
-    <t>08ASB25018250</t>
-  </si>
-  <si>
-    <t>000900</t>
-  </si>
-  <si>
-    <t>NOKOBA INJEKSI</t>
-  </si>
-  <si>
-    <t>3ED069</t>
-  </si>
-  <si>
-    <t>08ASB25018275</t>
-  </si>
-  <si>
-    <t>000578</t>
-  </si>
-  <si>
-    <t>IBUPROFEN 400 MG</t>
-  </si>
-  <si>
-    <t>A 02229 IC</t>
-  </si>
-  <si>
-    <t>004907</t>
-  </si>
-  <si>
-    <t>OBH IKA 100 ML</t>
-  </si>
-  <si>
-    <t>J25017A</t>
-  </si>
-  <si>
-    <t>08ASB25018276</t>
-  </si>
-  <si>
-    <t>08ASB25018277</t>
-  </si>
-  <si>
-    <t>08ASB25018286</t>
-  </si>
-  <si>
-    <t>000319</t>
-  </si>
-  <si>
-    <t>DIGOXIN 0.25 MG</t>
-  </si>
-  <si>
-    <t>A 08617 IC</t>
-  </si>
-  <si>
-    <t>000999</t>
-  </si>
-  <si>
-    <t>PHENYTOIN 100 CAP.</t>
-  </si>
-  <si>
-    <t>K25003D</t>
-  </si>
-  <si>
-    <t>015193</t>
-  </si>
-  <si>
-    <t>SERTRALINE</t>
-  </si>
-  <si>
-    <t>1EI080</t>
-  </si>
-  <si>
-    <t>017431</t>
-  </si>
-  <si>
-    <t>IBUPROFEN 200</t>
-  </si>
-  <si>
-    <t>A 08502 JB</t>
-  </si>
-  <si>
-    <t>08ASB25018287</t>
-  </si>
-  <si>
-    <t>000839</t>
-  </si>
-  <si>
-    <t>NEO-MERCAZOLE TABLET</t>
-  </si>
-  <si>
-    <t>5H 1106</t>
-  </si>
-  <si>
-    <t>08ASB25018301</t>
-  </si>
-  <si>
-    <t>012704</t>
-  </si>
-  <si>
-    <t>FARMADOL INFUS 50 ML</t>
-  </si>
-  <si>
-    <t>3EG102</t>
-  </si>
-  <si>
-    <t>08ASB25018373</t>
-  </si>
-  <si>
-    <t>003430</t>
-  </si>
-  <si>
-    <t>AMITRIPTILINE 25 MG</t>
-  </si>
-  <si>
-    <t>A 12522 JC</t>
-  </si>
-  <si>
-    <t>08ASB25018387</t>
-  </si>
-  <si>
-    <t>08ASB25018388</t>
-  </si>
-  <si>
-    <t>011472</t>
-  </si>
-  <si>
-    <t>FIXACEP ORAL DROPS</t>
-  </si>
-  <si>
-    <t>8EG001 2</t>
-  </si>
-  <si>
-    <t>08ASB25018403</t>
-  </si>
-  <si>
-    <t>08ASB25018404</t>
-  </si>
-  <si>
-    <t>08ASB25018405</t>
-  </si>
-  <si>
-    <t>013454</t>
-  </si>
-  <si>
-    <t>XOLMETRAS 350 ( 100 ML )</t>
-  </si>
-  <si>
-    <t>3EF054</t>
-  </si>
-  <si>
-    <t>012739</t>
-  </si>
-  <si>
-    <t>XOLMETRAS 350 ( 50ML )</t>
-  </si>
-  <si>
-    <t>3RJ048</t>
-  </si>
-  <si>
-    <t>08ASB25018406</t>
-  </si>
-  <si>
-    <t>08ASB25018407</t>
-  </si>
-  <si>
-    <t>08ASB25018445</t>
-  </si>
-  <si>
-    <t>016627</t>
-  </si>
-  <si>
-    <t>TRAMADOL 50 MG ( GF )</t>
-  </si>
-  <si>
-    <t>B5I318</t>
-  </si>
-  <si>
-    <t>08ASB25018467</t>
-  </si>
-  <si>
-    <t>013683</t>
-  </si>
-  <si>
-    <t>RESFAR INFUS IV</t>
-  </si>
-  <si>
-    <t>3EG105 1</t>
-  </si>
-  <si>
-    <t>08ASB25018471</t>
-  </si>
-  <si>
-    <t>013640</t>
-  </si>
-  <si>
-    <t>UMARONE</t>
-  </si>
-  <si>
-    <t>3EE130</t>
-  </si>
-  <si>
-    <t>08ASB25018472</t>
-  </si>
-  <si>
-    <t>000780</t>
-  </si>
-  <si>
-    <t>MOLAGIT</t>
-  </si>
-  <si>
-    <t>M11HG038</t>
-  </si>
-  <si>
-    <t>08ASB25018515</t>
-  </si>
-  <si>
-    <t>08ASB25018521</t>
-  </si>
-  <si>
-    <t>08ASB25018522</t>
-  </si>
-  <si>
-    <t>A 00406 JC</t>
-  </si>
-  <si>
-    <t>015495</t>
-  </si>
-  <si>
-    <t>ROSUVASTATIN 10 MG</t>
-  </si>
-  <si>
-    <t>1EB063</t>
-  </si>
-  <si>
-    <t>08ASB25018524</t>
-  </si>
-  <si>
-    <t>004416</t>
-  </si>
-  <si>
-    <t>SALBUTAMOL 2 MG</t>
-  </si>
-  <si>
-    <t>A 08245 IC</t>
-  </si>
-  <si>
-    <t>08ASB25018586</t>
-  </si>
-  <si>
-    <t>08ASB25018596</t>
-  </si>
-  <si>
-    <t>08ASB25018597</t>
-  </si>
-  <si>
-    <t>000543</t>
-  </si>
-  <si>
-    <t>HALOPERIDOL 0.5 MG</t>
-  </si>
-  <si>
-    <t>A 01806 HC</t>
-  </si>
-  <si>
-    <t>08ASB25018622</t>
-  </si>
-  <si>
-    <t>1EI013</t>
-  </si>
-  <si>
-    <t>08ASB25018623</t>
-  </si>
-  <si>
-    <t>08ASB25018628</t>
-  </si>
-  <si>
-    <t>016768</t>
-  </si>
-  <si>
-    <t>AMIODARONE INJEKSI</t>
-  </si>
-  <si>
-    <t>3EG074</t>
-  </si>
-  <si>
-    <t>08ASB25018629</t>
-  </si>
-  <si>
-    <t>3EG148</t>
-  </si>
-  <si>
-    <t>K25006A</t>
-  </si>
-  <si>
-    <t>08ASB25018630</t>
-  </si>
-  <si>
-    <t>08ASB25018631</t>
-  </si>
-  <si>
-    <t>08ASB25018632</t>
-  </si>
-  <si>
-    <t>08ASB25018633</t>
-  </si>
-  <si>
-    <t>08ASB25018641</t>
-  </si>
-  <si>
-    <t>08ASB25018694</t>
-  </si>
-  <si>
-    <t>08ASB25018695</t>
-  </si>
-  <si>
-    <t>08ASB25018696</t>
-  </si>
-  <si>
-    <t>08ASB25018697</t>
-  </si>
-  <si>
-    <t>K25017D</t>
-  </si>
-  <si>
-    <t>08ASB25018698</t>
-  </si>
-  <si>
-    <t>08ASB25018699</t>
-  </si>
-  <si>
-    <t>1EI152</t>
-  </si>
-  <si>
-    <t>08BSB25001003</t>
-  </si>
-  <si>
-    <t>010325</t>
-  </si>
-  <si>
-    <t>TS50 SCRUBBRUSH W/CG4%&amp;SOAP</t>
-  </si>
-  <si>
-    <t>250720</t>
-  </si>
-  <si>
-    <t>16ASB25020042</t>
-  </si>
-  <si>
-    <t>016809</t>
-  </si>
-  <si>
-    <t>ZYMUNO 200 ML</t>
-  </si>
-  <si>
-    <t>L110725034</t>
-  </si>
-  <si>
-    <t>16ASB25020402</t>
-  </si>
-  <si>
-    <t>016806</t>
-  </si>
-  <si>
-    <t>ETAWALIN 200 GR</t>
-  </si>
-  <si>
-    <t>P110925019</t>
-  </si>
-  <si>
-    <t>23ASB25012778</t>
-  </si>
-  <si>
-    <t>25ASB25019194</t>
-  </si>
-  <si>
-    <t>2EE043</t>
-  </si>
-  <si>
-    <t>2EF096</t>
-  </si>
-  <si>
-    <t>2EH084</t>
-  </si>
-  <si>
-    <t>25ASB25019605</t>
-  </si>
-  <si>
-    <t>A 08615 IC</t>
-  </si>
-  <si>
-    <t>A 00493 IC</t>
-  </si>
-  <si>
-    <t>A 02237 JC</t>
-  </si>
-  <si>
-    <t>000652</t>
-  </si>
-  <si>
-    <t>ISOSORBIDE DINITRATE 5 MG</t>
-  </si>
-  <si>
-    <t>A 02313 IC</t>
-  </si>
-  <si>
-    <t>K25002D</t>
-  </si>
-  <si>
-    <t>A 08238 HC</t>
-  </si>
-  <si>
-    <t>015563</t>
-  </si>
-  <si>
-    <t>WARFARIN SODIUM CLATHRATE</t>
-  </si>
-  <si>
-    <t>1EG173</t>
-  </si>
-  <si>
-    <t>25ASB25019606</t>
-  </si>
-  <si>
-    <t>3EB075</t>
-  </si>
-  <si>
-    <t>3EH062</t>
-  </si>
-  <si>
-    <t>3EI069</t>
-  </si>
-  <si>
-    <t>25ASB25019608</t>
-  </si>
-  <si>
-    <t>25ASB25019647</t>
-  </si>
-  <si>
-    <t>25ASB25019664</t>
-  </si>
-  <si>
-    <t>25ASB25019692</t>
+    <t>26ASB25029392</t>
+  </si>
+  <si>
+    <t>26ASB25029396</t>
+  </si>
+  <si>
+    <t>26ASB25029576</t>
+  </si>
+  <si>
+    <t>26ASB25029593</t>
+  </si>
+  <si>
+    <t>300911</t>
+  </si>
+  <si>
+    <t>300917</t>
+  </si>
+  <si>
+    <t>300910</t>
+  </si>
+  <si>
+    <t>301002</t>
+  </si>
+  <si>
+    <t>301023</t>
+  </si>
+  <si>
+    <t>301003</t>
+  </si>
+  <si>
+    <t>301030</t>
+  </si>
+  <si>
+    <t>301025</t>
+  </si>
+  <si>
+    <t>301004</t>
+  </si>
+  <si>
+    <t>301026</t>
+  </si>
+  <si>
+    <t>301005</t>
+  </si>
+  <si>
+    <t>301027</t>
+  </si>
+  <si>
+    <t>301006</t>
+  </si>
+  <si>
+    <t>301007</t>
+  </si>
+  <si>
+    <t>301008</t>
+  </si>
+  <si>
+    <t>301115</t>
+  </si>
+  <si>
+    <t>301116</t>
+  </si>
+  <si>
+    <t>301117</t>
+  </si>
+  <si>
+    <t>301118</t>
+  </si>
+  <si>
+    <t>301119</t>
+  </si>
+  <si>
+    <t>301120</t>
+  </si>
+  <si>
+    <t>301202</t>
+  </si>
+  <si>
+    <t>301201</t>
+  </si>
+  <si>
+    <t>26ASB25029651</t>
+  </si>
+  <si>
+    <t>26ASB25029652</t>
+  </si>
+  <si>
+    <t>26ASB25029653</t>
+  </si>
+  <si>
+    <t>26ASB25029654</t>
+  </si>
+  <si>
+    <t>26ASB25029658</t>
+  </si>
+  <si>
+    <t>26ASB25029753</t>
+  </si>
+  <si>
+    <t>26ASB25029754</t>
+  </si>
+  <si>
+    <t>26ASB25029755</t>
+  </si>
+  <si>
+    <t>26ASB25029836</t>
   </si>
   <si>
     <t>017421</t>
@@ -823,31 +768,37 @@
     <t>ETAWAKU LESS SUGAR</t>
   </si>
   <si>
-    <t>PEL2.141224</t>
-  </si>
-  <si>
-    <t>25ASB25019764</t>
-  </si>
-  <si>
-    <t>26ASB25020250</t>
-  </si>
-  <si>
-    <t>2ED043</t>
-  </si>
-  <si>
-    <t>26ASB25020251</t>
-  </si>
-  <si>
-    <t>2EC061</t>
-  </si>
-  <si>
-    <t>26ASB25021228</t>
-  </si>
-  <si>
-    <t>26ASB25026401</t>
-  </si>
-  <si>
-    <t>P111025092</t>
+    <t>PEL1.201224</t>
+  </si>
+  <si>
+    <t>017420</t>
+  </si>
+  <si>
+    <t>ETAWAKU SACHET</t>
+  </si>
+  <si>
+    <t>PES1.240125</t>
+  </si>
+  <si>
+    <t>26ASB25029868</t>
+  </si>
+  <si>
+    <t>301012</t>
+  </si>
+  <si>
+    <t>26ASB25030030</t>
+  </si>
+  <si>
+    <t>26ASB25030243</t>
+  </si>
+  <si>
+    <t>000617</t>
+  </si>
+  <si>
+    <t>IKAPHEN CAPSUL</t>
+  </si>
+  <si>
+    <t>G25004D</t>
   </si>
   <si>
     <t>27ASB25014375</t>
@@ -856,88 +807,16 @@
     <t>2ED090</t>
   </si>
   <si>
-    <t>27ASB25020868</t>
-  </si>
-  <si>
-    <t>1EH135</t>
-  </si>
-  <si>
-    <t>2EF039</t>
-  </si>
-  <si>
-    <t>27ASB25020871</t>
-  </si>
-  <si>
-    <t>2ED079</t>
-  </si>
-  <si>
-    <t>27ASB25021039</t>
+    <t>27ASB25019462</t>
   </si>
   <si>
     <t>300626</t>
-  </si>
-  <si>
-    <t>27ASB25021066</t>
-  </si>
-  <si>
-    <t>P111025112</t>
-  </si>
-  <si>
-    <t>27ASB25021282</t>
-  </si>
-  <si>
-    <t>017647</t>
-  </si>
-  <si>
-    <t>VITAMEAL</t>
-  </si>
-  <si>
-    <t>VM0925182</t>
-  </si>
-  <si>
-    <t>017648</t>
-  </si>
-  <si>
-    <t>VITAMEAL LESS SUGAR</t>
-  </si>
-  <si>
-    <t>VG0925029</t>
-  </si>
-  <si>
-    <t>017661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETAWALIN SEREAL </t>
-  </si>
-  <si>
-    <t>P14102501ER</t>
-  </si>
-  <si>
-    <t>27ASB25021376</t>
-  </si>
-  <si>
-    <t>2ED082</t>
-  </si>
-  <si>
-    <t>27ASB25021397</t>
-  </si>
-  <si>
-    <t>27ASB25021523</t>
-  </si>
-  <si>
-    <t>015564</t>
-  </si>
-  <si>
-    <t>OSELTAMIVIR 75 MG 10`S</t>
-  </si>
-  <si>
-    <t>25OV2001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -1207,11 +1086,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K143"/>
+  <dimension ref="A1:K150"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -1295,28 +1174,28 @@
         <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>18150</v>
+        <v>126126</v>
       </c>
       <c r="G4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="I4" s="3">
-        <v>3630</v>
+        <v>256667</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="4">
-        <v>46904</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -1330,28 +1209,28 @@
         <v>20</v>
       </c>
       <c r="D5" s="3">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3">
-        <v>55858</v>
+        <v>95400</v>
       </c>
       <c r="G5" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H5" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>33515</v>
+        <v>1184868</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="K5" s="4">
-        <v>47664</v>
+        <v>46867</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -1365,22 +1244,22 @@
         <v>24</v>
       </c>
       <c r="D6" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>41732</v>
+        <v>55858</v>
       </c>
       <c r="G6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>30047</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>25</v>
@@ -1394,31 +1273,31 @@
         <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>55858</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="3">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>72879</v>
-      </c>
-      <c r="G7" s="3">
-        <v>2</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3">
-        <v>17491</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="K7" s="4">
         <v>47787</v>
@@ -1426,22 +1305,22 @@
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>72879</v>
+        <v>41732</v>
       </c>
       <c r="G8" s="3">
         <v>2</v>
@@ -1450,10 +1329,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="3">
-        <v>8745</v>
+        <v>90141</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="4">
         <v>47787</v>
@@ -1461,372 +1340,372 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>87846</v>
+        <v>55858</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>70277</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K9" s="4">
-        <v>46752</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>81081</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2432</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="3">
-        <v>36</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>16000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>28800</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="K10" s="4">
-        <v>46998</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>58559</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3</v>
+      </c>
+      <c r="I11" s="3">
+        <v>10541</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="3">
-        <v>69</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3</v>
-      </c>
-      <c r="F11" s="3">
-        <v>32400</v>
-      </c>
-      <c r="G11" s="3">
-        <v>18</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>402408</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="K11" s="4">
-        <v>46937</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>50850</v>
+        <v>76577</v>
       </c>
       <c r="G12" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>3.0001000000000002</v>
       </c>
       <c r="I12" s="3">
-        <v>631557</v>
+        <v>114869</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K12" s="4">
-        <v>47033</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" s="3">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="E13" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3">
-        <v>39870</v>
+        <v>94595</v>
       </c>
       <c r="G13" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="I13" s="3">
-        <v>1980742</v>
+        <v>53937</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K13" s="4">
-        <v>47013</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D14" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>120000</v>
+        <v>81081</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I14" s="3">
-        <v>144000</v>
+        <v>58378</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="K14" s="4">
-        <v>46599</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>114950</v>
+        <v>58559</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3">
-        <v>18392</v>
+        <v>73784</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="K15" s="4">
-        <v>46477</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="3">
         <v>32</v>
       </c>
-      <c r="D16" s="3">
-        <v>6</v>
-      </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>87846</v>
+        <v>94595</v>
       </c>
       <c r="G16" s="3">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>8</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="I16" s="3">
-        <v>42166</v>
+        <v>90841</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="K16" s="4">
-        <v>46752</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="3">
+        <v>167</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>81081</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
+        <v>406216</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="3">
-        <v>10</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>66400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>15</v>
-      </c>
-      <c r="I17" s="3">
-        <v>99600</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="K17" s="4">
-        <v>46634</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D18" s="3">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>41000</v>
+        <v>94595</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>10</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="I18" s="3">
-        <v>49200</v>
+        <v>127746</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K18" s="4">
-        <v>46596</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D19" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
       </c>
       <c r="F19" s="3">
-        <v>30800</v>
+        <v>18150</v>
       </c>
       <c r="G19" s="3">
         <v>2</v>
@@ -1835,33 +1714,33 @@
         <v>0</v>
       </c>
       <c r="I19" s="3">
-        <v>7392</v>
+        <v>3630</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="K19" s="4">
-        <v>46630</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D20" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>58300</v>
+        <v>18150</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -1870,33 +1749,33 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>6996</v>
+        <v>3630</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="K20" s="4">
-        <v>46934</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>18150</v>
+        <v>58300</v>
       </c>
       <c r="G21" s="3">
         <v>2</v>
@@ -1905,514 +1784,514 @@
         <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>3630</v>
+        <v>6996</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="K21" s="4">
-        <v>46996</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D22" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>55858</v>
+        <v>58300</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>6996</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="K22" s="4">
-        <v>47664</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D23" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>55858</v>
+        <v>30800</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" s="3">
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>7392</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="K23" s="4">
-        <v>47664</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D24" s="3">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>50000</v>
+        <v>81081</v>
       </c>
       <c r="G24" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>30</v>
+        <v>3.0001000000000002</v>
       </c>
       <c r="I24" s="3">
-        <v>122500</v>
+        <v>116761</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="K24" s="4">
-        <v>46418</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="D25" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>240000</v>
+        <v>94595</v>
       </c>
       <c r="G25" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>15</v>
+        <v>3.0011000000000001</v>
       </c>
       <c r="I25" s="3">
-        <v>96000</v>
+        <v>68133</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="K25" s="4">
-        <v>46599</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="D26" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>330000</v>
+        <v>81081</v>
       </c>
       <c r="G26" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>40</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="I26" s="3">
-        <v>742500</v>
+        <v>58398</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="K26" s="4">
-        <v>46599</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="D27" s="3">
+        <v>120</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>81081</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>3</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1200000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>5</v>
-      </c>
-      <c r="H27" s="3">
-        <v>10</v>
-      </c>
       <c r="I27" s="3">
-        <v>540000</v>
+        <v>291892</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="K27" s="4">
-        <v>46599</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="D28" s="3">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E28" s="3">
         <v>0</v>
       </c>
       <c r="F28" s="3">
-        <v>125000</v>
+        <v>94595</v>
       </c>
       <c r="G28" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>45</v>
+        <v>3.0011000000000001</v>
       </c>
       <c r="I28" s="3">
-        <v>3125000</v>
+        <v>204400</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="K28" s="4">
-        <v>46630</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>195000</v>
+        <v>55858</v>
       </c>
       <c r="G29" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="K29" s="4">
-        <v>46568</v>
+        <v>47664</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="D30" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" s="3">
         <v>0</v>
       </c>
       <c r="F30" s="3">
-        <v>150000</v>
+        <v>55858</v>
       </c>
       <c r="G30" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3">
-        <v>52500</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="K30" s="4">
-        <v>46599</v>
+        <v>47664</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D31" s="3">
+        <v>6</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>58300</v>
+      </c>
+      <c r="G31" s="3">
         <v>2</v>
       </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3">
-        <v>240000</v>
-      </c>
-      <c r="G31" s="3">
-        <v>5</v>
-      </c>
       <c r="H31" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3">
-        <v>96000</v>
+        <v>6996</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K31" s="4">
-        <v>46599</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D32" s="3">
+        <v>6</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>58300</v>
+      </c>
+      <c r="G32" s="3">
         <v>2</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>57000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>28500</v>
+        <v>6996</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="K32" s="4">
-        <v>46660</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="D33" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>19500</v>
+        <v>18150</v>
       </c>
       <c r="G33" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>10725</v>
+        <v>3630</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="K33" s="4">
-        <v>47012</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="D34" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>25000</v>
+        <v>18150</v>
       </c>
       <c r="G34" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>10000</v>
+        <v>3630</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="K34" s="4">
-        <v>47026</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="D35" s="3">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>90000</v>
+        <v>81081</v>
       </c>
       <c r="G35" s="3">
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I35" s="3">
-        <v>81000</v>
+        <v>175135</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="K35" s="4">
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="D36" s="3">
         <v>3</v>
@@ -2421,287 +2300,287 @@
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>105000</v>
+        <v>41732</v>
       </c>
       <c r="G36" s="3">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I36" s="3">
-        <v>47250</v>
+        <v>6260</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="K36" s="4">
-        <v>46630</v>
+        <v>47726</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="D37" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E37" s="3">
         <v>0</v>
       </c>
       <c r="F37" s="3">
-        <v>90000</v>
+        <v>41732</v>
       </c>
       <c r="G37" s="3">
         <v>0</v>
       </c>
       <c r="H37" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I37" s="3">
-        <v>18000</v>
+        <v>43819</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="K37" s="4">
-        <v>46660</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="D38" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E38" s="3">
         <v>0</v>
       </c>
       <c r="F38" s="3">
-        <v>525000</v>
+        <v>81081</v>
       </c>
       <c r="G38" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I38" s="3">
-        <v>110250</v>
+        <v>58378</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="K38" s="4">
-        <v>46507</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="D39" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E39" s="3">
         <v>0</v>
       </c>
       <c r="F39" s="3">
-        <v>38000</v>
+        <v>30800</v>
       </c>
       <c r="G39" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" s="3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3">
-        <v>950</v>
+        <v>7392</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="K39" s="4">
-        <v>47026</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="D40" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E40" s="3">
         <v>0</v>
       </c>
       <c r="F40" s="3">
-        <v>12200</v>
+        <v>18150</v>
       </c>
       <c r="G40" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3">
-        <v>4880</v>
+        <v>7260</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="K40" s="4">
-        <v>47021</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D41" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>50000</v>
+        <v>58300</v>
       </c>
       <c r="G41" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H41" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>17500</v>
+        <v>6996</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K41" s="4">
-        <v>46418</v>
+        <v>46783</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D42" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>330000</v>
+        <v>18150</v>
       </c>
       <c r="G42" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H42" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>148500</v>
+        <v>3630</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K42" s="4">
-        <v>46599</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="D43" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>30000</v>
+        <v>30800</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
-        <v>9000</v>
+        <v>7392</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="K43" s="4">
-        <v>46660</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D44" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>25000</v>
+        <v>350000</v>
       </c>
       <c r="G44" s="3">
         <v>0</v>
@@ -2710,24 +2589,24 @@
         <v>5</v>
       </c>
       <c r="I44" s="3">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="K44" s="4">
-        <v>47026</v>
+        <v>55153</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="D45" s="3">
         <v>2</v>
@@ -2736,369 +2615,369 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>38000</v>
+        <v>350000</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="I45" s="3">
-        <v>1900</v>
+        <v>35000</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="K45" s="4">
-        <v>47026</v>
+        <v>55153</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D46" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>12200</v>
+        <v>905000</v>
       </c>
       <c r="G46" s="3">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I46" s="3">
-        <v>2440</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="K46" s="4">
-        <v>47021</v>
+        <v>46965</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D47" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>70000</v>
+        <v>30800</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>21000</v>
+        <v>12320</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="K47" s="4">
-        <v>47029</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="D48" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>200000</v>
+        <v>18150</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
-        <v>80000</v>
+        <v>10890</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="K48" s="4">
-        <v>46660</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="D49" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>25000</v>
+        <v>30800</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>12500</v>
+        <v>2464</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="K49" s="4">
-        <v>46326</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="D50" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" s="3">
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>150000</v>
+        <v>553430</v>
       </c>
       <c r="G50" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I50" s="3">
-        <v>0</v>
+        <v>498087</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="K50" s="4">
-        <v>46996</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="51" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="D51" s="3">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E51" s="3">
         <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>80000</v>
+        <v>90000</v>
       </c>
       <c r="G51" s="3">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>40.625</v>
+        <v>10</v>
       </c>
       <c r="I51" s="3">
-        <v>1235000</v>
+        <v>9000</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="K51" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="D52" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I52" s="3">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="K52" s="4">
-        <v>46691</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="D53" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" s="3">
         <v>0</v>
       </c>
       <c r="F53" s="3">
-        <v>125000</v>
+        <v>450000</v>
       </c>
       <c r="G53" s="3">
         <v>5</v>
       </c>
       <c r="H53" s="3">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="I53" s="3">
-        <v>187500</v>
+        <v>45000</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="K53" s="4">
-        <v>46630</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="54" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="D54" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E54" s="3">
         <v>0</v>
       </c>
       <c r="F54" s="3">
-        <v>90000</v>
+        <v>330000</v>
       </c>
       <c r="G54" s="3">
         <v>5</v>
       </c>
       <c r="H54" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I54" s="3">
-        <v>157500</v>
+        <v>1039500</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="K54" s="4">
-        <v>46418</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="55" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D55" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E55" s="3">
         <v>0</v>
       </c>
       <c r="F55" s="3">
-        <v>57000</v>
+        <v>90000</v>
       </c>
       <c r="G55" s="3">
         <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I55" s="3">
-        <v>28500</v>
+        <v>189000</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K55" s="4">
         <v>46660</v>
@@ -3106,13 +2985,13 @@
     </row>
     <row r="56" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="D56" s="3">
         <v>3</v>
@@ -3121,334 +3000,334 @@
         <v>0</v>
       </c>
       <c r="F56" s="3">
-        <v>330000</v>
+        <v>25000</v>
       </c>
       <c r="G56" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I56" s="3">
-        <v>445500</v>
+        <v>7500</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="K56" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="D57" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
       </c>
       <c r="F57" s="3">
-        <v>50000</v>
+        <v>18000</v>
       </c>
       <c r="G57" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>30</v>
+        <v>7.5</v>
       </c>
       <c r="I57" s="3">
-        <v>52500</v>
+        <v>2700</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="K57" s="4">
-        <v>46418</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="58" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>164</v>
+        <v>33</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="D58" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>580000</v>
+        <v>81081</v>
       </c>
       <c r="G58" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I58" s="3">
-        <v>348000</v>
+        <v>58378</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="K58" s="4">
-        <v>46568</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="D59" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>315000</v>
+        <v>55858</v>
       </c>
       <c r="G59" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H59" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I59" s="3">
-        <v>94500</v>
+        <v>16757</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="K59" s="4">
-        <v>46326</v>
+        <v>47664</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="D60" s="3">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E60" s="3">
         <v>0</v>
       </c>
       <c r="F60" s="3">
-        <v>125000</v>
+        <v>41732</v>
       </c>
       <c r="G60" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H60" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I60" s="3">
-        <v>3000000</v>
+        <v>50078</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="K60" s="4">
-        <v>46630</v>
+        <v>47726</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="D61" s="3">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>125000</v>
+        <v>55858</v>
       </c>
       <c r="G61" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H61" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I61" s="3">
-        <v>3750000</v>
+        <v>16757</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="K61" s="4">
-        <v>46630</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="D62" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>24116</v>
+        <v>81081</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>58378</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="K62" s="4">
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="63" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>177</v>
+        <v>36</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>178</v>
+        <v>37</v>
       </c>
       <c r="D63" s="3">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E63" s="3">
         <v>0</v>
       </c>
       <c r="F63" s="3">
-        <v>199000</v>
+        <v>58559</v>
       </c>
       <c r="G63" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I63" s="3">
-        <v>1641750</v>
+        <v>63244</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="K63" s="4">
-        <v>46965</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>182</v>
+        <v>37</v>
       </c>
       <c r="D64" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E64" s="3">
         <v>0</v>
       </c>
       <c r="F64" s="3">
-        <v>183000</v>
+        <v>58559</v>
       </c>
       <c r="G64" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I64" s="3">
-        <v>36600</v>
+        <v>21081</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="K64" s="4">
-        <v>46538</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="D65" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E65" s="3">
         <v>0</v>
       </c>
       <c r="F65" s="3">
-        <v>85000</v>
+        <v>72879</v>
       </c>
       <c r="G65" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H65" s="3">
-        <v>34.76</v>
+        <v>3</v>
       </c>
       <c r="I65" s="3">
-        <v>35496</v>
+        <v>43727</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="K65" s="4">
         <v>47726</v>
@@ -3456,804 +3335,804 @@
     </row>
     <row r="66" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E66" s="3">
         <v>0</v>
       </c>
       <c r="F66" s="3">
-        <v>57000</v>
+        <v>58300</v>
       </c>
       <c r="G66" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I66" s="3">
-        <v>39900</v>
+        <v>6996</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="K66" s="4">
-        <v>46660</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D67" s="3">
+        <v>10</v>
+      </c>
+      <c r="E67" s="3">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3">
+        <v>18150</v>
+      </c>
+      <c r="G67" s="3">
         <v>2</v>
       </c>
-      <c r="E67" s="3">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3">
-        <v>330000</v>
-      </c>
-      <c r="G67" s="3">
-        <v>5</v>
-      </c>
       <c r="H67" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I67" s="3">
-        <v>297000</v>
+        <v>3630</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="K67" s="4">
-        <v>46599</v>
+        <v>46843</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D68" s="3">
-        <v>12</v>
+        <v>414</v>
       </c>
       <c r="E68" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F68" s="3">
-        <v>12200</v>
+        <v>24300</v>
       </c>
       <c r="G68" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H68" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I68" s="3">
-        <v>7320</v>
+        <v>1810836</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="K68" s="4">
-        <v>47021</v>
+        <v>46991</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="D69" s="3">
-        <v>1</v>
+        <v>286</v>
       </c>
       <c r="E69" s="3">
         <v>0</v>
       </c>
       <c r="F69" s="3">
-        <v>330000</v>
+        <v>39870</v>
       </c>
       <c r="G69" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H69" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I69" s="3">
-        <v>148500</v>
+        <v>2052508</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="K69" s="4">
-        <v>46599</v>
+        <v>46985</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D70" s="3">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>30000</v>
+        <v>24300</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H70" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>3000</v>
+        <v>839808</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="K70" s="4">
-        <v>46660</v>
+        <v>46987</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="D71" s="3">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="E71" s="3">
         <v>0</v>
       </c>
       <c r="F71" s="3">
-        <v>25000</v>
+        <v>39870</v>
       </c>
       <c r="G71" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H71" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I71" s="3">
-        <v>2500</v>
+        <v>882722</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="K71" s="4">
-        <v>47057</v>
+        <v>46994</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="D72" s="3">
-        <v>9</v>
+        <v>404</v>
       </c>
       <c r="E72" s="3">
         <v>0</v>
       </c>
       <c r="F72" s="3">
-        <v>90000</v>
+        <v>25200</v>
       </c>
       <c r="G72" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H72" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3">
-        <v>81000</v>
+        <v>1832544</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="K72" s="4">
-        <v>46660</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="73" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D73" s="3">
-        <v>10</v>
+        <v>552</v>
       </c>
       <c r="E73" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F73" s="3">
-        <v>200000</v>
+        <v>42750</v>
       </c>
       <c r="G73" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H73" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I73" s="3">
-        <v>800000</v>
+        <v>4247640</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="K73" s="4">
-        <v>46660</v>
+        <v>46997</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="D74" s="3">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="E74" s="3">
         <v>0</v>
       </c>
       <c r="F74" s="3">
-        <v>90000</v>
+        <v>23850</v>
       </c>
       <c r="G74" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H74" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I74" s="3">
-        <v>40500</v>
+        <v>1073250</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="K74" s="4">
-        <v>46446</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="75" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D75" s="3">
-        <v>3</v>
+        <v>322</v>
       </c>
       <c r="E75" s="3">
         <v>0</v>
       </c>
       <c r="F75" s="3">
-        <v>18000</v>
+        <v>40500</v>
       </c>
       <c r="G75" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H75" s="3">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3">
-        <v>4050</v>
+        <v>2347380</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="K75" s="4">
-        <v>47026</v>
+        <v>46987</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>199</v>
+        <v>143</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D76" s="3">
-        <v>5</v>
+        <v>266</v>
       </c>
       <c r="E76" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F76" s="3">
-        <v>30000</v>
+        <v>39870</v>
       </c>
       <c r="G76" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H76" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I76" s="3">
-        <v>7500</v>
+        <v>1908976</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="K76" s="4">
-        <v>46691</v>
+        <v>46997</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D77" s="3">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="E77" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F77" s="3">
-        <v>30000</v>
+        <v>24300</v>
       </c>
       <c r="G77" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H77" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I77" s="3">
-        <v>1500</v>
+        <v>1272834</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K77" s="4">
-        <v>46691</v>
+        <v>47013</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="D78" s="3">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="E78" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F78" s="3">
-        <v>11000</v>
+        <v>39870</v>
       </c>
       <c r="G78" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H78" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I78" s="3">
-        <v>440</v>
+        <v>2088391</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="K78" s="4">
-        <v>46996</v>
+        <v>47013</v>
       </c>
     </row>
     <row r="79" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="D79" s="3">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="E79" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F79" s="3">
-        <v>240000</v>
+        <v>25200</v>
       </c>
       <c r="G79" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H79" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I79" s="3">
-        <v>48000</v>
+        <v>671328</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="K79" s="4">
-        <v>46660</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D80" s="3">
-        <v>7</v>
+        <v>302</v>
       </c>
       <c r="E80" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F80" s="3">
-        <v>90000</v>
+        <v>23850</v>
       </c>
       <c r="G80" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H80" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I80" s="3">
-        <v>220500</v>
+        <v>1296486</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="K80" s="4">
-        <v>46418</v>
+        <v>47027</v>
       </c>
     </row>
     <row r="81" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="D81" s="3">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F81" s="3">
-        <v>75000</v>
+        <v>40500</v>
       </c>
       <c r="G81" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H81" s="3">
-        <v>29.14</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
-        <v>43710</v>
+        <v>1676700</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="K81" s="4">
-        <v>46599</v>
+        <v>47008</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D82" s="3">
+        <v>24</v>
+      </c>
+      <c r="E82" s="3">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3">
+        <v>94595</v>
+      </c>
+      <c r="G82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
         <v>3</v>
       </c>
-      <c r="E82" s="3">
-        <v>0</v>
-      </c>
-      <c r="F82" s="3">
-        <v>50000</v>
-      </c>
-      <c r="G82" s="3">
-        <v>5</v>
-      </c>
-      <c r="H82" s="3">
-        <v>30</v>
-      </c>
       <c r="I82" s="3">
-        <v>52500</v>
+        <v>68108</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="K82" s="4">
-        <v>46418</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="D83" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>90000</v>
+        <v>117117</v>
       </c>
       <c r="G83" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>30</v>
+        <v>7.69</v>
       </c>
       <c r="I83" s="3">
-        <v>31500</v>
+        <v>54038</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="K83" s="4">
-        <v>46418</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="D84" s="3">
+        <v>24</v>
+      </c>
+      <c r="E84" s="3">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3">
+        <v>41732</v>
+      </c>
+      <c r="G84" s="3">
         <v>2</v>
       </c>
-      <c r="E84" s="3">
-        <v>0</v>
-      </c>
-      <c r="F84" s="3">
-        <v>19500</v>
-      </c>
-      <c r="G84" s="3">
-        <v>0</v>
-      </c>
       <c r="H84" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I84" s="3">
-        <v>1950</v>
+        <v>50078</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="K84" s="4">
-        <v>47034</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>167</v>
+        <v>33</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="D85" s="3">
+        <v>48</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3">
+        <v>81081</v>
+      </c>
+      <c r="G85" s="3">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3">
         <v>3</v>
       </c>
-      <c r="E85" s="3">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3">
-        <v>315000</v>
-      </c>
-      <c r="G85" s="3">
-        <v>5</v>
-      </c>
-      <c r="H85" s="3">
-        <v>25</v>
-      </c>
       <c r="I85" s="3">
-        <v>283500</v>
+        <v>116757</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="K85" s="4">
-        <v>46326</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="D86" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E86" s="3">
         <v>0</v>
       </c>
       <c r="F86" s="3">
-        <v>125000</v>
+        <v>94595</v>
       </c>
       <c r="G86" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I86" s="3">
-        <v>1375000</v>
+        <v>68108</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="K86" s="4">
-        <v>46630</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="D87" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E87" s="3">
         <v>0</v>
       </c>
       <c r="F87" s="3">
-        <v>1200000</v>
+        <v>18150</v>
       </c>
       <c r="G87" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H87" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I87" s="3">
-        <v>720000</v>
+        <v>3630</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="K87" s="4">
-        <v>46599</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D88" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E88" s="3">
         <v>0</v>
       </c>
       <c r="F88" s="3">
-        <v>240000</v>
+        <v>78379</v>
       </c>
       <c r="G88" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I88" s="3">
-        <v>48000</v>
+        <v>112866</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="K88" s="4">
         <v>46660</v>
@@ -4261,512 +4140,512 @@
     </row>
     <row r="89" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>81</v>
+        <v>188</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="D89" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>330000</v>
+        <v>87388</v>
       </c>
       <c r="G89" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="I89" s="3">
-        <v>594000</v>
+        <v>125839</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="K89" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D90" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E90" s="3">
         <v>0</v>
       </c>
       <c r="F90" s="3">
-        <v>199000</v>
+        <v>85586</v>
       </c>
       <c r="G90" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I90" s="3">
-        <v>1313400</v>
+        <v>123244</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="K90" s="4">
-        <v>46965</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="D91" s="3">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>80000</v>
+        <v>78379</v>
       </c>
       <c r="G91" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I91" s="3">
-        <v>160000</v>
+        <v>112866</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K91" s="4">
-        <v>46599</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>74</v>
+        <v>189</v>
       </c>
       <c r="D92" s="3">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E92" s="3">
         <v>0</v>
       </c>
       <c r="F92" s="3">
-        <v>50000</v>
+        <v>87388</v>
       </c>
       <c r="G92" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I92" s="3">
-        <v>35000</v>
+        <v>125839</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="K92" s="4">
-        <v>46418</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="D93" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E93" s="3">
         <v>0</v>
       </c>
       <c r="F93" s="3">
-        <v>330000</v>
+        <v>85586</v>
       </c>
       <c r="G93" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="I93" s="3">
-        <v>148500</v>
+        <v>123244</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="K93" s="4">
-        <v>46599</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D94" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>70000</v>
+        <v>30800</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>7000</v>
+        <v>1232</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="K94" s="4">
-        <v>47057</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>197</v>
+        <v>62</v>
       </c>
       <c r="D95" s="3">
+        <v>10</v>
+      </c>
+      <c r="E95" s="3">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3">
+        <v>30800</v>
+      </c>
+      <c r="G95" s="3">
         <v>2</v>
       </c>
-      <c r="E95" s="3">
-        <v>0</v>
-      </c>
-      <c r="F95" s="3">
-        <v>18000</v>
-      </c>
-      <c r="G95" s="3">
-        <v>0</v>
-      </c>
       <c r="H95" s="3">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I95" s="3">
-        <v>2700</v>
+        <v>6160</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>198</v>
+        <v>102</v>
       </c>
       <c r="K95" s="4">
-        <v>47026</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D96" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>330000</v>
+        <v>18150</v>
       </c>
       <c r="G96" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H96" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>148500</v>
+        <v>3630</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="K96" s="4">
-        <v>46599</v>
+        <v>46904</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="D97" s="3">
+        <v>24</v>
+      </c>
+      <c r="E97" s="3">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3">
+        <v>81081</v>
+      </c>
+      <c r="G97" s="3">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3">
         <v>3</v>
       </c>
-      <c r="E97" s="3">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3">
-        <v>105000</v>
-      </c>
-      <c r="G97" s="3">
-        <v>0</v>
-      </c>
-      <c r="H97" s="3">
-        <v>15</v>
-      </c>
       <c r="I97" s="3">
-        <v>47250</v>
+        <v>58378</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="K97" s="4">
-        <v>46630</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="D98" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E98" s="3">
         <v>0</v>
       </c>
       <c r="F98" s="3">
-        <v>25000</v>
+        <v>81081</v>
       </c>
       <c r="G98" s="3">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I98" s="3">
-        <v>1250</v>
+        <v>58378</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K98" s="4">
-        <v>47057</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="99" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="D99" s="3">
+        <v>11</v>
+      </c>
+      <c r="E99" s="3">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3">
+        <v>41732</v>
+      </c>
+      <c r="G99" s="3">
         <v>2</v>
       </c>
-      <c r="E99" s="3">
-        <v>0</v>
-      </c>
-      <c r="F99" s="3">
-        <v>90000</v>
-      </c>
-      <c r="G99" s="3">
-        <v>0</v>
-      </c>
       <c r="H99" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I99" s="3">
-        <v>18000</v>
+        <v>22953</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="K99" s="4">
-        <v>46660</v>
+        <v>47118</v>
       </c>
     </row>
     <row r="100" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="D100" s="3">
+        <v>13</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>41732</v>
+      </c>
+      <c r="G100" s="3">
         <v>2</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>25000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I100" s="3">
-        <v>5000</v>
+        <v>27125</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="K100" s="4">
-        <v>46326</v>
+        <v>47118</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="D101" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>200000</v>
+        <v>55858</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
-        <v>240000</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="K101" s="4">
-        <v>46660</v>
+        <v>46843</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="D102" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>90000</v>
+        <v>72879</v>
       </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="K102" s="4">
-        <v>46660</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="103" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>229</v>
+        <v>28</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>230</v>
+        <v>29</v>
       </c>
       <c r="D103" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E103" s="3">
         <v>0</v>
       </c>
       <c r="F103" s="3">
-        <v>13500</v>
+        <v>41732</v>
       </c>
       <c r="G103" s="3">
         <v>0</v>
@@ -4778,100 +4657,100 @@
         <v>0</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="K103" s="4">
-        <v>46935</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="104" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>233</v>
+        <v>136</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>234</v>
+        <v>137</v>
       </c>
       <c r="D104" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E104" s="3">
         <v>0</v>
       </c>
       <c r="F104" s="3">
-        <v>126126</v>
+        <v>72879</v>
       </c>
       <c r="G104" s="3">
         <v>0</v>
       </c>
       <c r="H104" s="3">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="I104" s="3">
-        <v>9005</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="K104" s="4">
-        <v>46599</v>
+        <v>47726</v>
       </c>
     </row>
     <row r="105" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="D105" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E105" s="3">
         <v>0</v>
       </c>
       <c r="F105" s="3">
-        <v>81081</v>
+        <v>72879</v>
       </c>
       <c r="G105" s="3">
         <v>0</v>
       </c>
       <c r="H105" s="3">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="I105" s="3">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="K105" s="4">
-        <v>46660</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="106" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D106" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E106" s="3">
         <v>0</v>
       </c>
       <c r="F106" s="3">
-        <v>18150</v>
+        <v>58300</v>
       </c>
       <c r="G106" s="3">
         <v>2</v>
@@ -4880,33 +4759,33 @@
         <v>0</v>
       </c>
       <c r="I106" s="3">
-        <v>3630</v>
+        <v>6996</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="K106" s="4">
-        <v>46904</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="107" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D107" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E107" s="3">
         <v>0</v>
       </c>
       <c r="F107" s="3">
-        <v>58300</v>
+        <v>30800</v>
       </c>
       <c r="G107" s="3">
         <v>2</v>
@@ -4915,972 +4794,972 @@
         <v>0</v>
       </c>
       <c r="I107" s="3">
-        <v>27984</v>
+        <v>7392</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>242</v>
+        <v>102</v>
       </c>
       <c r="K107" s="4">
-        <v>46904</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="108" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D108" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E108" s="3">
         <v>0</v>
       </c>
       <c r="F108" s="3">
-        <v>18150</v>
+        <v>55858</v>
       </c>
       <c r="G108" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" s="3">
         <v>0</v>
       </c>
       <c r="I108" s="3">
-        <v>3993</v>
+        <v>0</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="K108" s="4">
-        <v>46934</v>
+        <v>46843</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D109" s="3">
-        <v>9</v>
+        <v>138</v>
       </c>
       <c r="E109" s="3">
         <v>0</v>
       </c>
       <c r="F109" s="3">
-        <v>18150</v>
+        <v>41732</v>
       </c>
       <c r="G109" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H109" s="3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="I109" s="3">
-        <v>3267</v>
+        <v>413498</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>244</v>
+        <v>180</v>
       </c>
       <c r="K109" s="4">
-        <v>46996</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="110" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="D110" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E110" s="3">
         <v>0</v>
       </c>
       <c r="F110" s="3">
-        <v>30000</v>
+        <v>55858</v>
       </c>
       <c r="G110" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H110" s="3">
-        <v>10</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I110" s="3">
-        <v>18000</v>
+        <v>4013</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="K110" s="4">
-        <v>46660</v>
+        <v>46843</v>
       </c>
     </row>
     <row r="111" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="D111" s="3">
-        <v>11</v>
+        <v>288</v>
       </c>
       <c r="E111" s="3">
         <v>0</v>
       </c>
       <c r="F111" s="3">
-        <v>25000</v>
+        <v>41732</v>
       </c>
       <c r="G111" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H111" s="3">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="I111" s="3">
-        <v>13750</v>
+        <v>862951</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="K111" s="4">
-        <v>47026</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="112" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="D112" s="3">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="E112" s="3">
         <v>0</v>
       </c>
       <c r="F112" s="3">
-        <v>38000</v>
+        <v>55858</v>
       </c>
       <c r="G112" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H112" s="3">
-        <v>2.5</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I112" s="3">
-        <v>950</v>
+        <v>674166</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="K112" s="4">
-        <v>47057</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="113" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="D113" s="3">
-        <v>1</v>
+        <v>312</v>
       </c>
       <c r="E113" s="3">
         <v>0</v>
       </c>
       <c r="F113" s="3">
-        <v>25000</v>
+        <v>41732</v>
       </c>
       <c r="G113" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H113" s="3">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="I113" s="3">
-        <v>2500</v>
+        <v>934864</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="K113" s="4">
-        <v>46660</v>
+        <v>47756</v>
       </c>
     </row>
     <row r="114" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="D114" s="3">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E114" s="3">
         <v>0</v>
       </c>
       <c r="F114" s="3">
-        <v>12200</v>
+        <v>55858</v>
       </c>
       <c r="G114" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H114" s="3">
-        <v>5</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I114" s="3">
-        <v>12200</v>
+        <v>188606</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="K114" s="4">
-        <v>47021</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="115" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="D115" s="3">
-        <v>4</v>
+        <v>192</v>
       </c>
       <c r="E115" s="3">
         <v>0</v>
       </c>
       <c r="F115" s="3">
-        <v>70000</v>
+        <v>41732</v>
       </c>
       <c r="G115" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H115" s="3">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="I115" s="3">
-        <v>28000</v>
+        <v>575300</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="K115" s="4">
-        <v>47028</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="116" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>197</v>
+        <v>24</v>
       </c>
       <c r="D116" s="3">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="E116" s="3">
         <v>0</v>
       </c>
       <c r="F116" s="3">
-        <v>18000</v>
+        <v>55858</v>
       </c>
       <c r="G116" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H116" s="3">
-        <v>7.5</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I116" s="3">
-        <v>2700</v>
+        <v>337083</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="K116" s="4">
-        <v>46996</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="117" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="D117" s="3">
-        <v>42</v>
+        <v>288</v>
       </c>
       <c r="E117" s="3">
         <v>0</v>
       </c>
       <c r="F117" s="3">
-        <v>200000</v>
+        <v>41732</v>
       </c>
       <c r="G117" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H117" s="3">
-        <v>40</v>
+        <v>2.88</v>
       </c>
       <c r="I117" s="3">
-        <v>3360000</v>
+        <v>862951</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>140</v>
+        <v>221</v>
       </c>
       <c r="K117" s="4">
-        <v>46660</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="118" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>254</v>
+        <v>23</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="D118" s="3">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="E118" s="3">
         <v>0</v>
       </c>
       <c r="F118" s="3">
-        <v>122000</v>
+        <v>55858</v>
       </c>
       <c r="G118" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H118" s="3">
-        <v>45</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I118" s="3">
-        <v>219600</v>
+        <v>481547</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="K118" s="4">
-        <v>46965</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="119" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="D119" s="3">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="E119" s="3">
         <v>0</v>
       </c>
       <c r="F119" s="3">
-        <v>50000</v>
+        <v>41732</v>
       </c>
       <c r="G119" s="3">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="H119" s="3">
-        <v>30</v>
+        <v>2.88</v>
       </c>
       <c r="I119" s="3">
-        <v>17500</v>
+        <v>1150602</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="K119" s="4">
-        <v>46265</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="120" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="D120" s="3">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="E120" s="3">
         <v>0</v>
       </c>
       <c r="F120" s="3">
-        <v>125000</v>
+        <v>55858</v>
       </c>
       <c r="G120" s="3">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="H120" s="3">
-        <v>45</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I120" s="3">
-        <v>1500000</v>
+        <v>577857</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="K120" s="4">
-        <v>46630</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="121" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="D121" s="3">
-        <v>8</v>
+        <v>384</v>
       </c>
       <c r="E121" s="3">
         <v>0</v>
       </c>
       <c r="F121" s="3">
-        <v>330000</v>
+        <v>41732</v>
       </c>
       <c r="G121" s="3">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="H121" s="3">
-        <v>40</v>
+        <v>2.88</v>
       </c>
       <c r="I121" s="3">
-        <v>1188000</v>
+        <v>1150602</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="K121" s="4">
-        <v>46660</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="122" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D122" s="3">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="E122" s="3">
         <v>0</v>
       </c>
       <c r="F122" s="3">
-        <v>58300</v>
+        <v>55858</v>
       </c>
       <c r="G122" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H122" s="3">
-        <v>0</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I122" s="3">
-        <v>6996</v>
+        <v>1059404</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="K122" s="4">
-        <v>46904</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="123" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="D123" s="3">
-        <v>18</v>
+        <v>384</v>
       </c>
       <c r="E123" s="3">
         <v>0</v>
       </c>
       <c r="F123" s="3">
-        <v>30000</v>
+        <v>41732</v>
       </c>
       <c r="G123" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H123" s="3">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="I123" s="3">
-        <v>27000</v>
+        <v>1150602</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="K123" s="4">
-        <v>46691</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="124" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="D124" s="3">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="E124" s="3">
         <v>0</v>
       </c>
       <c r="F124" s="3">
-        <v>30000</v>
+        <v>55858</v>
       </c>
       <c r="G124" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H124" s="3">
-        <v>5</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I124" s="3">
-        <v>1500</v>
+        <v>1059404</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="K124" s="4">
-        <v>46691</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>265</v>
+        <v>28</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>266</v>
+        <v>29</v>
       </c>
       <c r="D125" s="3">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="E125" s="3">
         <v>0</v>
       </c>
       <c r="F125" s="3">
-        <v>85586</v>
+        <v>41732</v>
       </c>
       <c r="G125" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H125" s="3">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="I125" s="3">
-        <v>41081</v>
+        <v>593279</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>267</v>
+        <v>30</v>
       </c>
       <c r="K125" s="4">
-        <v>46387</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="126" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="D126" s="3">
-        <v>5</v>
+        <v>264</v>
       </c>
       <c r="E126" s="3">
         <v>0</v>
       </c>
       <c r="F126" s="3">
-        <v>199000</v>
+        <v>55858</v>
       </c>
       <c r="G126" s="3">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="H126" s="3">
-        <v>50</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I126" s="3">
-        <v>547250</v>
+        <v>1059404</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="K126" s="4">
-        <v>46965</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="127" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D127" s="3">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="E127" s="3">
         <v>0</v>
       </c>
       <c r="F127" s="3">
-        <v>58300</v>
+        <v>55858</v>
       </c>
       <c r="G127" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H127" s="3">
-        <v>0</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I127" s="3">
-        <v>6996</v>
+        <v>1059404</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="K127" s="4">
-        <v>46873</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>271</v>
+        <v>214</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D128" s="3">
-        <v>10</v>
+        <v>264</v>
       </c>
       <c r="E128" s="3">
         <v>0</v>
       </c>
       <c r="F128" s="3">
-        <v>18150</v>
+        <v>55858</v>
       </c>
       <c r="G128" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H128" s="3">
-        <v>0</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I128" s="3">
-        <v>3630</v>
+        <v>1059404</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>272</v>
+        <v>230</v>
       </c>
       <c r="K128" s="4">
-        <v>46843</v>
+        <v>47817</v>
       </c>
     </row>
     <row r="129" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D129" s="3">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="E129" s="3">
         <v>0</v>
       </c>
       <c r="F129" s="3">
-        <v>58300</v>
+        <v>55858</v>
       </c>
       <c r="G129" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H129" s="3">
-        <v>0</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I129" s="3">
-        <v>6996</v>
+        <v>1059404</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>270</v>
+        <v>231</v>
       </c>
       <c r="K129" s="4">
-        <v>46873</v>
+        <v>47817</v>
       </c>
     </row>
     <row r="130" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>274</v>
+        <v>214</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>237</v>
+        <v>23</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="D130" s="3">
-        <v>24</v>
+        <v>264</v>
       </c>
       <c r="E130" s="3">
         <v>0</v>
       </c>
       <c r="F130" s="3">
-        <v>81081</v>
+        <v>55858</v>
       </c>
       <c r="G130" s="3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H130" s="3">
-        <v>3</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I130" s="3">
-        <v>58378</v>
+        <v>1059404</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="K130" s="4">
-        <v>46691</v>
+        <v>47817</v>
       </c>
     </row>
     <row r="131" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>276</v>
+        <v>214</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D131" s="3">
-        <v>10</v>
+        <v>264</v>
       </c>
       <c r="E131" s="3">
         <v>0</v>
       </c>
       <c r="F131" s="3">
-        <v>18150</v>
+        <v>55858</v>
       </c>
       <c r="G131" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H131" s="3">
-        <v>0</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I131" s="3">
-        <v>3630</v>
+        <v>1059404</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="K131" s="4">
-        <v>46873</v>
+        <v>47817</v>
       </c>
     </row>
     <row r="132" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>278</v>
+        <v>214</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D132" s="3">
-        <v>12</v>
+        <v>264</v>
       </c>
       <c r="E132" s="3">
         <v>0</v>
       </c>
       <c r="F132" s="3">
-        <v>30800</v>
+        <v>55858</v>
       </c>
       <c r="G132" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H132" s="3">
-        <v>0</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I132" s="3">
-        <v>7392</v>
+        <v>1059404</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="K132" s="4">
-        <v>46630</v>
+        <v>47817</v>
       </c>
     </row>
     <row r="133" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>278</v>
+        <v>214</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D133" s="3">
-        <v>10</v>
+        <v>264</v>
       </c>
       <c r="E133" s="3">
         <v>0</v>
       </c>
       <c r="F133" s="3">
-        <v>18150</v>
+        <v>55858</v>
       </c>
       <c r="G133" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H133" s="3">
-        <v>0</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I133" s="3">
-        <v>3630</v>
+        <v>1059404</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="K133" s="4">
-        <v>46934</v>
+        <v>47817</v>
       </c>
     </row>
     <row r="134" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>281</v>
+        <v>214</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D134" s="3">
-        <v>6</v>
+        <v>228</v>
       </c>
       <c r="E134" s="3">
         <v>0</v>
       </c>
       <c r="F134" s="3">
-        <v>58300</v>
+        <v>55858</v>
       </c>
       <c r="G134" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H134" s="3">
-        <v>0</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I134" s="3">
-        <v>6996</v>
+        <v>914940</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="K134" s="4">
-        <v>46873</v>
+        <v>47848</v>
       </c>
     </row>
     <row r="135" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>283</v>
+        <v>214</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D135" s="3">
-        <v>12</v>
+        <v>264</v>
       </c>
       <c r="E135" s="3">
         <v>0</v>
@@ -5889,173 +5768,173 @@
         <v>55858</v>
       </c>
       <c r="G135" s="3">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="H135" s="3">
-        <v>3</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="I135" s="3">
-        <v>33515</v>
+        <v>1059404</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="K135" s="4">
-        <v>47664</v>
+        <v>47848</v>
       </c>
     </row>
     <row r="136" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>237</v>
+        <v>51</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>238</v>
+        <v>52</v>
       </c>
       <c r="D136" s="3">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E136" s="3">
         <v>0</v>
       </c>
       <c r="F136" s="3">
-        <v>81081</v>
+        <v>18150</v>
       </c>
       <c r="G136" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H136" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I136" s="3">
-        <v>116757</v>
+        <v>3630</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>286</v>
+        <v>198</v>
       </c>
       <c r="K136" s="4">
-        <v>46691</v>
+        <v>46904</v>
       </c>
     </row>
     <row r="137" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>288</v>
+        <v>56</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>289</v>
+        <v>57</v>
       </c>
       <c r="D137" s="3">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="E137" s="3">
         <v>0</v>
       </c>
       <c r="F137" s="3">
-        <v>78379</v>
+        <v>58300</v>
       </c>
       <c r="G137" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137" s="3">
-        <v>3.0003000000000002</v>
+        <v>0</v>
       </c>
       <c r="I137" s="3">
-        <v>112877</v>
+        <v>6996</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="K137" s="4">
-        <v>46660</v>
+        <v>46873</v>
       </c>
     </row>
     <row r="138" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>291</v>
+        <v>51</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>292</v>
+        <v>52</v>
       </c>
       <c r="D138" s="3">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E138" s="3">
         <v>0</v>
       </c>
       <c r="F138" s="3">
-        <v>87388</v>
+        <v>18150</v>
       </c>
       <c r="G138" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H138" s="3">
-        <v>3.0019999999999998</v>
+        <v>0</v>
       </c>
       <c r="I138" s="3">
-        <v>125923</v>
+        <v>3630</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>293</v>
+        <v>198</v>
       </c>
       <c r="K138" s="4">
-        <v>46660</v>
+        <v>46904</v>
       </c>
     </row>
     <row r="139" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>294</v>
+        <v>136</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>295</v>
+        <v>137</v>
       </c>
       <c r="D139" s="3">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="E139" s="3">
         <v>0</v>
       </c>
       <c r="F139" s="3">
-        <v>85586</v>
+        <v>72879</v>
       </c>
       <c r="G139" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H139" s="3">
         <v>3</v>
       </c>
       <c r="I139" s="3">
-        <v>123244</v>
+        <v>43727</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="K139" s="4">
-        <v>46691</v>
+        <v>47787</v>
       </c>
     </row>
     <row r="140" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>297</v>
+        <v>242</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D140" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E140" s="3">
         <v>0</v>
@@ -6070,10 +5949,10 @@
         <v>0</v>
       </c>
       <c r="I140" s="3">
-        <v>2332</v>
+        <v>6996</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>298</v>
+        <v>140</v>
       </c>
       <c r="K140" s="4">
         <v>46873</v>
@@ -6081,48 +5960,48 @@
     </row>
     <row r="141" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="D141" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E141" s="3">
         <v>0</v>
       </c>
       <c r="F141" s="3">
-        <v>58300</v>
+        <v>94595</v>
       </c>
       <c r="G141" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H141" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I141" s="3">
-        <v>4664</v>
+        <v>68108</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>282</v>
+        <v>175</v>
       </c>
       <c r="K141" s="4">
-        <v>46873</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="142" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>299</v>
+        <v>244</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="D142" s="3">
         <v>10</v>
@@ -6143,45 +6022,290 @@
         <v>3630</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>280</v>
+        <v>198</v>
       </c>
       <c r="K142" s="4">
-        <v>46934</v>
+        <v>46904</v>
       </c>
     </row>
     <row r="143" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>302</v>
+        <v>52</v>
       </c>
       <c r="D143" s="3">
+        <v>10</v>
+      </c>
+      <c r="E143" s="3">
+        <v>0</v>
+      </c>
+      <c r="F143" s="3">
+        <v>18150</v>
+      </c>
+      <c r="G143" s="3">
+        <v>2</v>
+      </c>
+      <c r="H143" s="3">
+        <v>0</v>
+      </c>
+      <c r="I143" s="3">
+        <v>3630</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K143" s="4">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D144" s="3">
+        <v>50</v>
+      </c>
+      <c r="E144" s="3">
+        <v>0</v>
+      </c>
+      <c r="F144" s="3">
+        <v>85586</v>
+      </c>
+      <c r="G144" s="3">
+        <v>0</v>
+      </c>
+      <c r="H144" s="3">
         <v>3</v>
       </c>
-      <c r="E143" s="3">
-        <v>0</v>
-      </c>
-      <c r="F143" s="3">
-        <v>160000</v>
-      </c>
-      <c r="G143" s="3">
-        <v>0</v>
-      </c>
-      <c r="H143" s="3">
-        <v>0</v>
-      </c>
-      <c r="I143" s="3">
-        <v>0</v>
-      </c>
-      <c r="J143" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="K143" s="4">
-        <v>47422</v>
+      <c r="I144" s="3">
+        <v>128379</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="K144" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D145" s="3">
+        <v>50</v>
+      </c>
+      <c r="E145" s="3">
+        <v>0</v>
+      </c>
+      <c r="F145" s="3">
+        <v>54055</v>
+      </c>
+      <c r="G145" s="3">
+        <v>0</v>
+      </c>
+      <c r="H145" s="3">
+        <v>3</v>
+      </c>
+      <c r="I145" s="3">
+        <v>81083</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="K145" s="4">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D146" s="3">
+        <v>12</v>
+      </c>
+      <c r="E146" s="3">
+        <v>0</v>
+      </c>
+      <c r="F146" s="3">
+        <v>72879</v>
+      </c>
+      <c r="G146" s="3">
+        <v>0</v>
+      </c>
+      <c r="H146" s="3">
+        <v>0</v>
+      </c>
+      <c r="I146" s="3">
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K146" s="4">
+        <v>47787</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147" s="3">
+        <v>12</v>
+      </c>
+      <c r="E147" s="3">
+        <v>0</v>
+      </c>
+      <c r="F147" s="3">
+        <v>55858</v>
+      </c>
+      <c r="G147" s="3">
+        <v>0</v>
+      </c>
+      <c r="H147" s="3">
+        <v>0</v>
+      </c>
+      <c r="I147" s="3">
+        <v>0</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K147" s="4">
+        <v>47756</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D148" s="3">
+        <v>2</v>
+      </c>
+      <c r="E148" s="3">
+        <v>0</v>
+      </c>
+      <c r="F148" s="3">
+        <v>132300</v>
+      </c>
+      <c r="G148" s="3">
+        <v>0</v>
+      </c>
+      <c r="H148" s="3">
+        <v>10</v>
+      </c>
+      <c r="I148" s="3">
+        <v>26460</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="K148" s="4">
+        <v>46943</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D149" s="3">
+        <v>10</v>
+      </c>
+      <c r="E149" s="3">
+        <v>0</v>
+      </c>
+      <c r="F149" s="3">
+        <v>18150</v>
+      </c>
+      <c r="G149" s="3">
+        <v>2</v>
+      </c>
+      <c r="H149" s="3">
+        <v>0</v>
+      </c>
+      <c r="I149" s="3">
+        <v>3630</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="K149" s="4">
+        <v>46873</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D150" s="3">
+        <v>24</v>
+      </c>
+      <c r="E150" s="3">
+        <v>0</v>
+      </c>
+      <c r="F150" s="3">
+        <v>55858</v>
+      </c>
+      <c r="G150" s="3">
+        <v>0</v>
+      </c>
+      <c r="H150" s="3">
+        <v>0</v>
+      </c>
+      <c r="I150" s="3">
+        <v>0</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K150" s="4">
+        <v>47664</v>
       </c>
     </row>
   </sheetData>
